--- a/data/exports/validation_study/packets/week-2/packet-1.xlsx
+++ b/data/exports/validation_study/packets/week-2/packet-1.xlsx
@@ -544,7 +544,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2. 'techniques' sheet - the 16 attacks, mechanisms and defenses we recorded from your papers.</t>
+          <t>2. 'techniques' sheet - the 8 attacks, mechanisms and defenses we recorded from your papers.</t>
         </is>
       </c>
     </row>
@@ -2284,19 +2284,23 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>From Untrusted Input to Trusted Memory: A Systematic Study of Memory Poisoning Attacks in LLM Agents</t>
+          <t>SecInfer: Preventing Prompt Injection via Inference-time Scaling</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D2" s="2" t="n"/>
+        <v>2025</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
       <c r="E2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>data/papers/From Untrusted Input to Trusted Memory - A Systematic Study of Memory Poisoning Attacks in LLM Agents.pdf</t>
+          <t>data/papers/SecInfer - Preventing Prompt Injection via Inference-time Scaling.pdf</t>
         </is>
       </c>
       <c r="G2" s="5" t="n"/>
@@ -2308,19 +2312,23 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Repair the Amplifier, Not the Symptom: Stable World-Model Correction for Agent Rollouts</t>
+          <t>A Framework for Formalizing LLM Agent Security</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v>2026</v>
       </c>
-      <c r="D3" s="2" t="n"/>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
       <c r="E3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Repair the Amplifier, Not the Symptom - Stable World-Model Correction for Agent Rollouts.pdf</t>
+          <t>data/papers/A Framework for Formalizing LLM Agent Security.pdf</t>
         </is>
       </c>
       <c r="G3" s="5" t="n"/>
@@ -2332,15 +2340,15 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Enhancing Retrieval-Augmented Large Vision Language Models via Knowledge Conflict Mitigation</t>
+          <t>Tensor Trust: Interpretable Prompt Injection Attacks from an Online Game</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>AAAI</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
@@ -2348,7 +2356,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Enhancing Retrieval-Augmented Large Vision Language Models via Knowledge Conflict Mitigation.pdf</t>
+          <t>data/papers/Tensor Trust - Interpretable Prompt Injection Attacks from an Online Game.pdf</t>
         </is>
       </c>
       <c r="G4" s="5" t="n"/>
@@ -2360,11 +2368,11 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Uncovering Security Threats and Architecting Defenses in Autonomous Agents: A Case Study of OpenClaw</t>
+          <t>Manipulating LLM Web Agents with Indirect Prompt Injection Attack via HTML Accessibility Tree</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -2376,7 +2384,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Uncovering Security Threats and Architecting Defenses in Autonomous Agents - A Case Study of OpenClaw.pdf</t>
+          <t>data/papers/Manipulating LLM Web Agents with Indirect Prompt Injection Attack via HTML Accessibility Tree.pdf</t>
         </is>
       </c>
       <c r="G5" s="5" t="n"/>
@@ -2388,7 +2396,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Agent Skills in the Wild: An Empirical Study of Security Vulnerabilities at Scale</t>
+          <t>Context Cartography: Toward Structured Governance of Contextual Space in Large Language Model Systems</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -2400,11 +2408,11 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Agent Skills in the Wild - An Empirical Study of Security Vulnerabilities at Scale.pdf</t>
+          <t>data/papers/Context Cartography - Toward Structured Governance of Contextual Space in Large Language Model Systems.pdf</t>
         </is>
       </c>
       <c r="G6" s="5" t="n"/>
@@ -2416,23 +2424,23 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Overcoming the Retrieval Barrier: Indirect Prompt Injection in the Wild for LLM Systems</t>
+          <t>Bridging AI and Software Security: A Comparative Vulnerability Assessment of LLM Agent Deployment Paradigms</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>Information Sciences</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Overcoming the Retrieval Barrier - Indirect Prompt Injection in the Wild for LLM Systems.pdf</t>
+          <t>data/papers/Bridging AI and Software Security - A Comparative Vulnerability Assessment of LLM Agent Deployment Paradigms.pdf</t>
         </is>
       </c>
       <c r="G7" s="5" t="n"/>
@@ -2444,11 +2452,11 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Manipulating LLM Web Agents with Indirect Prompt Injection Attack via HTML Accessibility Tree</t>
+          <t>LivePI: More Realistic Benchmarking of Agents Against Indirect Prompt Injection</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -2456,11 +2464,11 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Manipulating LLM Web Agents with Indirect Prompt Injection Attack via HTML Accessibility Tree.pdf</t>
+          <t>data/papers/LivePI - More Realistic Benchmarking of Agents Against Indirect Prompt Injection.pdf</t>
         </is>
       </c>
       <c r="G8" s="5" t="n"/>
@@ -2472,7 +2480,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Meta SecAlign: A Secure Foundation LLM Against Prompt Injection Attacks</t>
+          <t>Memory as Action: Autonomous Context Curation for Long-Horizon Agentic Tasks</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -2480,7 +2488,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>ACL</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
@@ -2488,7 +2496,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Meta SecAlign - A Secure Foundation LLM Against Prompt Injection Attacks.pdf</t>
+          <t>data/papers/Memory as Action - Autonomous Context Curation for Long-Horizon Agentic Tasks.pdf</t>
         </is>
       </c>
       <c r="G9" s="5" t="n"/>
@@ -2500,15 +2508,15 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>RAG-Induced Failures in Multi-Agent Large Language Model Debate</t>
+          <t>PhantomLint: Principled Detection of Hidden LLM Prompts in Structured Documents</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2026 1st International Conference on Emerging Technologies and Engineering Systems (ICETES)</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
@@ -2516,7 +2524,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>data/papers/RAG-Induced Failures in Multi-Agent Large Language Model Debate.pdf</t>
+          <t>data/papers/PhantomLint - Principled Detection of Hidden LLM Prompts in Structured Documents.pdf</t>
         </is>
       </c>
       <c r="G10" s="5" t="n"/>
@@ -2528,23 +2536,23 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>A Novel Evaluation Framework for Assessing Resilience Against Prompt Injection Attacks in Large Language Models</t>
+          <t>Can Indirect Prompt Injection Attacks Be Detected and Removed?</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> (CSDE) 2023 IEEE Asia-Pacific Conference on Computer Science and Data Engineering</t>
+          <t>ACL</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>data/papers/A Novel Evaluation Framework for Assessing Resilience Against Prompt Injection Attacks in Large Language Models.pdf</t>
+          <t>data/papers/Can Indirect Prompt Injection Attacks Be Detected and Removed.pdf</t>
         </is>
       </c>
       <c r="G11" s="5" t="n"/>
@@ -2556,19 +2564,23 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>PlanFlip: Attacking Multi-Agent LLM Systems via Planning-Phase Prompt Injection</t>
+          <t>Adaptive Chameleon or Stubborn Sloth: Revealing the Behavior of Large Language Models in Knowledge Conflicts</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D12" s="2" t="n"/>
+        <v>2023</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>ICLR</t>
+        </is>
+      </c>
       <c r="E12" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>data/papers/PlanFlip - Attacking Multi-Agent LLM Systems via Planning-Phase Prompt Injection.pdf</t>
+          <t>data/papers/Adaptive Chameleon or Stubborn Sloth - Revealing the Behavior of Large Language Models in Knowledge Conflicts.pdf</t>
         </is>
       </c>
       <c r="G12" s="5" t="n"/>
@@ -2580,19 +2592,23 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>SecureClaw: Clawing Back Control of LLM Agents</t>
+          <t>Secure Prompt Engineering Patterns for Cloud LLM Agents</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v>2026</v>
       </c>
-      <c r="D13" s="2" t="n"/>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>International Conference on Applied Informatics and Communication</t>
+        </is>
+      </c>
       <c r="E13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>data/papers/SecureClaw - Clawing Back Control of LLM Agents.pdf</t>
+          <t>data/papers/Secure Prompt Engineering Patterns for Cloud LLM Agents.pdf</t>
         </is>
       </c>
       <c r="G13" s="5" t="n"/>
@@ -2604,23 +2620,23 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>The Instruction Hierarchy: Training LLMs to Prioritize Privileged Instructions</t>
+          <t>Benchmarking Serverless AI Architectures: Modular RAG, Serverless RAG, and Long Context Inference</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>Distributed Event-Based Systems</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>data/papers/The Instruction Hierarchy - Training LLMs to Prioritize Privileged Instructions.pdf</t>
+          <t>data/papers/Benchmarking Serverless AI Architectures - Modular RAG, Serverless RAG, and Long Context Inference.pdf</t>
         </is>
       </c>
       <c r="G14" s="5" t="n"/>
@@ -2632,23 +2648,23 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Enhancing reliability in LLM-integrated robotic systems: A unified approach to security and safety</t>
+          <t>LUMINA: Long-horizon Understanding for Multi-turn Interactive Agents</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Journal of Systems and Software</t>
+          <t>ACL</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Enhancing reliability in LLM-integrated robotic systems - A unified approach to security and safety.pdf</t>
+          <t>data/papers/LUMINA - Long-horizon Understanding for Multi-turn Interactive Agents.pdf</t>
         </is>
       </c>
       <c r="G15" s="5" t="n"/>
@@ -2660,23 +2676,19 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>SkillVetBench: LLM-as-Judge for Multi-Dimensional Security Risk Evaluation in Open-Source LLM Agent Skills</t>
+          <t>Beware of Agentic Botnets: Scalable Untargeted Promptware Attacks via Universal and Transferable Adversarial HalluSquatting</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v>2026</v>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>data/papers/SkillVetBench - LLM-as-Judge for Multi-Dimensional Security Risk Evaluation in Open-Source LLM Agent Skills.pdf</t>
+          <t>data/papers/Beware of Agentic Botnets - Scalable Untargeted Promptware Attacks via Universal and Transferable Adversarial HalluSquatting.pdf</t>
         </is>
       </c>
       <c r="G16" s="5" t="n"/>
@@ -2688,7 +2700,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Cross-Agent Multimodal Provenance-Aware Framework for Robust Prompt Injection Defense in Large Language and Vision-Language Models</t>
+          <t>ToLeaP: Rethinking Development of Tool Learning with Large Language Models</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -2696,15 +2708,15 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>International Conferences on Computing Advancements</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Cross-Agent Multimodal Provenance-Aware Framework for Robust Prompt Injection Defense in Large Language and Vision-Language Models.pdf</t>
+          <t>data/papers/ToLeaP - Rethinking Development of Tool Learning with Large Language Models.pdf</t>
         </is>
       </c>
       <c r="G17" s="5" t="n"/>
@@ -2788,7 +2800,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>From Untrusted Input to Trusted Memory: A Systematic Study of Memory Poisoning Attacks in LLM Agents</t>
+          <t>SecInfer: Preventing Prompt Injection via Inference-time Scaling</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -2811,7 +2823,7 @@
       <c r="H2" s="5" t="n"/>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>469d4b8f7660de4bf1651a92bbc1ced997e631ec</t>
+          <t>5b3f710d1923323a0113f6db056aa712a04b0f13</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2833,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>From Untrusted Input to Trusted Memory: A Systematic Study of Memory Poisoning Attacks in LLM Agents</t>
+          <t>SecInfer: Preventing Prompt Injection via Inference-time Scaling</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -2844,7 +2856,7 @@
       <c r="H3" s="5" t="n"/>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>469d4b8f7660de4bf1651a92bbc1ced997e631ec</t>
+          <t>5b3f710d1923323a0113f6db056aa712a04b0f13</t>
         </is>
       </c>
     </row>
@@ -2854,7 +2866,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>From Untrusted Input to Trusted Memory: A Systematic Study of Memory Poisoning Attacks in LLM Agents</t>
+          <t>SecInfer: Preventing Prompt Injection via Inference-time Scaling</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -2877,7 +2889,7 @@
       <c r="H4" s="5" t="n"/>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>469d4b8f7660de4bf1651a92bbc1ced997e631ec</t>
+          <t>5b3f710d1923323a0113f6db056aa712a04b0f13</t>
         </is>
       </c>
     </row>
@@ -2887,7 +2899,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>From Untrusted Input to Trusted Memory: A Systematic Study of Memory Poisoning Attacks in LLM Agents</t>
+          <t>SecInfer: Preventing Prompt Injection via Inference-time Scaling</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -2902,7 +2914,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>attack</t>
+          <t>defense</t>
         </is>
       </c>
       <c r="F5" s="5" t="n"/>
@@ -2910,7 +2922,7 @@
       <c r="H5" s="5" t="n"/>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>469d4b8f7660de4bf1651a92bbc1ced997e631ec</t>
+          <t>5b3f710d1923323a0113f6db056aa712a04b0f13</t>
         </is>
       </c>
     </row>
@@ -2920,7 +2932,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>From Untrusted Input to Trusted Memory: A Systematic Study of Memory Poisoning Attacks in LLM Agents</t>
+          <t>SecInfer: Preventing Prompt Injection via Inference-time Scaling</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -2935,7 +2947,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>memory</t>
+          <t>direct-input</t>
         </is>
       </c>
       <c r="F6" s="5" t="n"/>
@@ -2943,7 +2955,7 @@
       <c r="H6" s="5" t="n"/>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>469d4b8f7660de4bf1651a92bbc1ced997e631ec</t>
+          <t>5b3f710d1923323a0113f6db056aa712a04b0f13</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2965,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>From Untrusted Input to Trusted Memory: A Systematic Study of Memory Poisoning Attacks in LLM Agents</t>
+          <t>SecInfer: Preventing Prompt Injection via Inference-time Scaling</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -2968,7 +2980,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>persistence-backdoor</t>
+          <t>goal-hijack</t>
         </is>
       </c>
       <c r="F7" s="5" t="n"/>
@@ -2976,7 +2988,7 @@
       <c r="H7" s="5" t="n"/>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>469d4b8f7660de4bf1651a92bbc1ced997e631ec</t>
+          <t>5b3f710d1923323a0113f6db056aa712a04b0f13</t>
         </is>
       </c>
     </row>
@@ -2986,7 +2998,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>From Untrusted Input to Trusted Memory: A Systematic Study of Memory Poisoning Attacks in LLM Agents</t>
+          <t>SecInfer: Preventing Prompt Injection via Inference-time Scaling</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -3009,7 +3021,7 @@
       <c r="H8" s="5" t="n"/>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>469d4b8f7660de4bf1651a92bbc1ced997e631ec</t>
+          <t>5b3f710d1923323a0113f6db056aa712a04b0f13</t>
         </is>
       </c>
     </row>
@@ -3019,7 +3031,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>From Untrusted Input to Trusted Memory: A Systematic Study of Memory Poisoning Attacks in LLM Agents</t>
+          <t>SecInfer: Preventing Prompt Injection via Inference-time Scaling</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -3042,7 +3054,7 @@
       <c r="H9" s="5" t="n"/>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>469d4b8f7660de4bf1651a92bbc1ced997e631ec</t>
+          <t>5b3f710d1923323a0113f6db056aa712a04b0f13</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3064,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>From Untrusted Input to Trusted Memory: A Systematic Study of Memory Poisoning Attacks in LLM Agents</t>
+          <t>SecInfer: Preventing Prompt Injection via Inference-time Scaling</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -3067,7 +3079,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>reasoning</t>
         </is>
       </c>
       <c r="F10" s="5" t="n"/>
@@ -3075,7 +3087,7 @@
       <c r="H10" s="5" t="n"/>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>469d4b8f7660de4bf1651a92bbc1ced997e631ec</t>
+          <t>5b3f710d1923323a0113f6db056aa712a04b0f13</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3097,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>From Untrusted Input to Trusted Memory: A Systematic Study of Memory Poisoning Attacks in LLM Agents</t>
+          <t>SecInfer: Preventing Prompt Injection via Inference-time Scaling</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -3100,7 +3112,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>cross-session-dormant</t>
+          <t>one-shot</t>
         </is>
       </c>
       <c r="F11" s="5" t="n"/>
@@ -3108,7 +3120,7 @@
       <c r="H11" s="5" t="n"/>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>469d4b8f7660de4bf1651a92bbc1ced997e631ec</t>
+          <t>5b3f710d1923323a0113f6db056aa712a04b0f13</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3130,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>From Untrusted Input to Trusted Memory: A Systematic Study of Memory Poisoning Attacks in LLM Agents</t>
+          <t>SecInfer: Preventing Prompt Injection via Inference-time Scaling</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -3141,7 +3153,7 @@
       <c r="H12" s="5" t="n"/>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>469d4b8f7660de4bf1651a92bbc1ced997e631ec</t>
+          <t>5b3f710d1923323a0113f6db056aa712a04b0f13</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3163,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>From Untrusted Input to Trusted Memory: A Systematic Study of Memory Poisoning Attacks in LLM Agents</t>
+          <t>SecInfer: Preventing Prompt Injection via Inference-time Scaling</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -3166,7 +3178,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>No explicit release URL for MPBench itself (the paper's benchmark/dataset) is given in the extracted text. The paper cites the two open-source agent systems it evaluates against, OpenClaw (https://github.com/openclaw/openclaw) and HERMES Agent (https://github.com/NousResearch/hermes-agent), but these are prior third-party artifacts, not releases from this paper.</t>
+          <t>The paper does not state a public code/dataset release link in the sections reviewed (main text, experimental setup, and conclusion); it relies on existing open-source implementations of attacks and baselines (cited via appendices) and standard public datasets (AG News, MMLU, GPQA, NarrativeQA, SQuAD_v2, SimpleQA, InjecAgent, AgentDojo) rather than releasing a novel dataset or artifact of its own.</t>
         </is>
       </c>
       <c r="F13" s="5" t="n"/>
@@ -3174,7 +3186,7 @@
       <c r="H13" s="5" t="n"/>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>469d4b8f7660de4bf1651a92bbc1ced997e631ec</t>
+          <t>5b3f710d1923323a0113f6db056aa712a04b0f13</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3196,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>From Untrusted Input to Trusted Memory: A Systematic Study of Memory Poisoning Attacks in LLM Agents</t>
+          <t>SecInfer: Preventing Prompt Injection via Inference-time Scaling</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -3199,7 +3211,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Both evaluated agent systems, OpenClaw and HERMES, are run with GPT-OSS-120B as the backend LLM using default system prompts and default memory configurations for each. Four prompt-injection defenses are additionally evaluated as candidate mitigations: PIGuard, DataFilter, CommandSans, and PromptArmor, each tested both off-the-shelf and after retraining/adaptation specifically for memory poisoning (model details for each defense's underlying classifier are in Appendix C). An LLM judge (validated against manual human annotation on a sample) is used to score ASR and RSR outcomes.</t>
+          <t>Two open-weight backend LLMs (LLaMA3.1-8B-Instruct and Qwen3-8B) and two closed-source backend LLMs (GPT-4o and GPT-4.1), with Qwen3-8B used as the default judge LLM in SecInfer's aggregation step (Table 7 separately studies the impact of using a different judge LLM). Optimization-based attacks (GCG, NeuralExec) requiring white-box access are only applicable to the open-weight LLMs, not the closed-source ones.</t>
         </is>
       </c>
       <c r="F14" s="5" t="n"/>
@@ -3207,7 +3219,7 @@
       <c r="H14" s="5" t="n"/>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>469d4b8f7660de4bf1651a92bbc1ced997e631ec</t>
+          <t>5b3f710d1923323a0113f6db056aa712a04b0f13</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3229,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>From Untrusted Input to Trusted Memory: A Systematic Study of Memory Poisoning Attacks in LLM Agents</t>
+          <t>SecInfer: Preventing Prompt Injection via Inference-time Scaling</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -3232,7 +3244,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>The paper's own novel benchmark, MPBench, evaluates memory poisoning attacks on two real agent systems (OpenClaw, HERMES). MPBench's test-case dataset spans the paper's six attack classes across seven domain types (Table 7). It is delivered as a labeled adversarial context block alongside the user query in a controlled emulation of real tool-call/retrieval pipelines. No prior standard benchmark for memory poisoning existed at the granularity used here; the paper notes existing agent-memory and agent-security benchmarks (e.g., AgentDojo) do not cover this specific attack surface.</t>
+          <t>Six target-task datasets split into closed-domain (AG News, MMLU, GPQA) and open-domain (NarrativeQA, SQuAD_v2, SimpleQA) categories; eight injected-task datasets from Open-Prompt-Injection (MRPC, RTE, HSOL, SMS-SPAM, SST2, Jfleg, Gigaword) plus a 'COMPROMISE' injected task from Zaremba et al.; seven prompt injection attacks (five heuristic: Naive Attack, Context Ignoring, Escape Character, Fake Completion, Combined Attack; two optimization-based: GCG-based Attack, NeuralExec) plus six adaptive attacks crafted specifically against SecInfer; and two LLM-agent benchmarks, InjecAgent (Base and Enhanced Attack variants with Direct Harm and Data Stealing subcategories) and AgentDojo, used to validate effectiveness in agentic settings beyond single-turn QA/classification.</t>
         </is>
       </c>
       <c r="F15" s="5" t="n"/>
@@ -3240,7 +3252,7 @@
       <c r="H15" s="5" t="n"/>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>469d4b8f7660de4bf1651a92bbc1ced997e631ec</t>
+          <t>5b3f710d1923323a0113f6db056aa712a04b0f13</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3262,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>From Untrusted Input to Trusted Memory: A Systematic Study of Memory Poisoning Attacks in LLM Agents</t>
+          <t>SecInfer: Preventing Prompt Injection via Inference-time Scaling</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -3265,7 +3277,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Memory poisoning attacks are persistent and broadly effective, with average Attack Success Rate (ASR) of 50.46% and Retrieval Success Rate (RSR) of 41.05% across both agents. HERMES is substantially more vulnerable than OpenClaw across all six attack classes and both metrics: average ASR is 66.67% on HERMES vs. 34.25% on OpenClaw, and average RSR is 64.70% vs. 17.40%, attributed to HERMES's more aggressive/automatic memory write-and-retrieval design (e.g., a frozen memory snapshot loaded at session start, requiring no explicit retrieval step) versus OpenClaw's more conservative, tool-invocation-gated retrieval. Individual attack classes range widely: Conditional Command Insertion reaches 67.89% ASR on OpenClaw and 92.76% RSR on HERMES; Policy-Conformant Fact Injection (a weak-signal attack) achieves only 8.33% ASR on OpenClaw but still 64.50% RSR on HERMES, showing that once a weak-signal payload is written, it persists and is retrieved at high rates regardless of low initial write success. Existing prompt-injection defenses provide only partial coverage: strong-signal attacks (containing explicit injection patterns) are detected substantially better than weak-signal attacks across all four evaluated defenses (e.g., PromptArmor achieves 84.44% detection on strong-signal but only 42.50% on weak-signal attacks, a ~42-point gap); even after retraining/adaptation specifically for memory poisoning, detectors like PIGuard only narrow this strong-weak gap to 1.67 points while capping absolute detection around 46-48%, and PromptArmor's adaptation shows no benefit at all, indicating the weakness is structural rather than a model- or training-data limitation.</t>
+          <t>SecInfer reduces attack success rate (ASR) to nearly zero across LLMs, attacks, and datasets while preserving utility (U) on par with the undefended baseline in the absence of attacks (Table 1), in contrast to a high undefended ASR (often 0.5-0.9 across attacks). Under Combined Attack and GCG attack (Table 2), most existing prevention-based defenses (Delimiters, Sandwich, Instructional, Paraphrasing, Retokenization, PromptArmor) fail with high residual ASR, while DataSentinel+PromptLocate (DS+PL) and MetaSecAlign perform better but still show gaps: DS+PL retains non-negligible ASR on some tasks under GCG (e.g., AG News) and loses utility due to over-flagging clean samples as contaminated, and MetaSecAlign is robust to Combined Attack but defeated by GCG (high ASR, low UA); SecInfer remains effective (ASR near 0) against both attack types and can be combined with MetaSecAlign's fine-tuned backend to further boost UA. Against prior inference-time scaling baselines under Combined Attack (Table 3: ICL-2/4, CoT, iterative refinement, best-of-N, self-consistency), SecInfer achieves ASR of 0.00 across all six target tasks while every baseline retains substantial residual ASR (0.10-0.45), at comparable inference cost (0.612s per sample for SecInfer vs. 0.622s for self-consistency, 0.719s for best-of-N; Table 4). On agentic benchmarks, SecInfer reduces InjecAgent ASR from 0.37/0.40 (Direct Harm/Data Stealing, Base Attack) to 0.00/0.02, and from 0.61/0.68 to 0.01/0.02 under Enhanced Attack (Table 5); on AgentDojo, ASR drops from 0.21 to 0.02 while utility under attack (UA) improves from 0.34 to 0.36 (Table 6). A memorization control test finds over 94% of judge-LLM outputs have string-similarity below 0.6 to ground-truth answers, supporting that SecInfer's effectiveness stems from genuine response evaluation rather than dataset memorization by the judge LLM.</t>
         </is>
       </c>
       <c r="F16" s="5" t="n"/>
@@ -3273,7 +3285,7 @@
       <c r="H16" s="5" t="n"/>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>469d4b8f7660de4bf1651a92bbc1ced997e631ec</t>
+          <t>5b3f710d1923323a0113f6db056aa712a04b0f13</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3295,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>From Untrusted Input to Trusted Memory: A Systematic Study of Memory Poisoning Attacks in LLM Agents</t>
+          <t>SecInfer: Preventing Prompt Injection via Inference-time Scaling</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -3298,7 +3310,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>The paper does not compare against a prior memory-poisoning attack baseline (since it is establishing this as a new systematic area) but instead structures its evaluation around attack-class comparisons (six novel attack classes: Explicit Command Insertion, Conditional Command Insertion, Salience-Driven Compaction, Policy-Conformant Fact Injection, False Precedent Insertion, Skill-Procedure Insertion) across two real agent systems, and compares four off-the-shelf prompt-injection defenses (PIGuard, DataFilter, CommandSans, PromptArmor) against their own retrained/adapted-for-memory-poisoning versions to test whether targeted adaptation closes the coverage gap.</t>
+          <t>Prevention-based defenses: Delimiters, Sandwich prevention, Instructional prevention, Paraphrasing, Retokenization, DataSentinel+PromptLocate (DS+PL), PromptArmor, and MetaSecAlign (StruQ and SecAlign excluded as MetaSecAlign is shown to dominate both). Inference-time scaling baselines: in-context learning with 2 or 4 examples (ICL-2/4), chain-of-thought prompting (CoT), iterative refinement (IR), best-of-N (BoN), and self-consistency (SC).</t>
         </is>
       </c>
       <c r="F17" s="5" t="n"/>
@@ -3306,7 +3318,7 @@
       <c r="H17" s="5" t="n"/>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>469d4b8f7660de4bf1651a92bbc1ced997e631ec</t>
+          <t>5b3f710d1923323a0113f6db056aa712a04b0f13</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3328,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>From Untrusted Input to Trusted Memory: A Systematic Study of Memory Poisoning Attacks in LLM Agents</t>
+          <t>SecInfer: Preventing Prompt Injection via Inference-time Scaling</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -3331,7 +3343,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>The threat model is explicitly black-box: an external adversary with no privileged access, no knowledge of the target model, and no direct access to the persistent memory store, who can only introduce adversarial content through normal agent operation (web pages, documents, emails, tool outputs, or other inputs the agent encounters during ordinary use). The adversary's goal is to induce the agent to write malicious content into its persistent long-term memory (factual, experience, or procedural memory) via one of four identified write channels (explicit instruction-executed write, system-prompt-driven write, compaction-driven write, experience-to-procedure write), so that the poisoned entry is later retrieved and treated as trusted knowledge across future, unrelated sessions -- requiring only a single successful write rather than payload presence in every active context, unlike standard prompt injection or jailbreaking.</t>
+          <t>The paper defines an explicit, strong threat model (Section 3.1). Attacker's goal: contaminate the LLM's input data so the model produces a response semantically aligned with an attacker-chosen injected task instead of the intended target task (e.g., redirecting users to a malicious URL, producing a damaging product summary, or manipulating an LLM agent's tool selection). Attacker's background knowledge: full white-box knowledge of the LLM system, including the target instruction, target data, and the backend LLM's parameters, plus complete knowledge of the SecInfer defense itself (its sampling and aggregation algorithms and the judge LLM's parameters), enabling adaptive attacks specifically crafted against SecInfer. Attacker's capabilities: can contaminate the target data with an injected prompt (realistic when target data comes from untrusted sources like the internet or agent tool responses), but cannot alter the system prompt, target instruction, or backend LLM itself, since these are controlled by developers. The defender's three goals are preserving utility under no attack, preserving utility under attack (except when the attack fully destroys the target data, which no defense can be expected to overcome), and reducing attack success.</t>
         </is>
       </c>
       <c r="F18" s="5" t="n"/>
@@ -3339,7 +3351,7 @@
       <c r="H18" s="5" t="n"/>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>469d4b8f7660de4bf1651a92bbc1ced997e631ec</t>
+          <t>5b3f710d1923323a0113f6db056aa712a04b0f13</t>
         </is>
       </c>
     </row>
@@ -3349,7 +3361,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>From Untrusted Input to Trusted Memory: A Systematic Study of Memory Poisoning Attacks in LLM Agents</t>
+          <t>SecInfer: Preventing Prompt Injection via Inference-time Scaling</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -3364,7 +3376,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>The paper has an explicit 'Limitations.' paragraph (Section 4.5, immediately preceding Section 5 Discussions). It states the evaluation uses a single backbone model, GPT-OSS-120B, for both agents, and different models may exhibit different ASR/RSR behavior. It also notes that for domains such as email, Slack, and web browsing, the benchmark delivers the adversarial payload as a labeled context block alongside the user query rather than through an actual tool call, meaning it does not model the agent's real tool-call and retrieval pipeline through which the payload would arrive in true deployment -- described as a 'controlled emulation of real deployment' following methodology used in prior agent security benchmarks (citing Zhan et al., 2024), with both limitations flagged as important directions for future work.</t>
+          <t>The paper has an explicit 'Discussion and Limitations' section (Section 6). Its primary acknowledged limitation is that SecInfer is substantially less effective when the injected task and target task are of the same type (e.g., both sentiment analysis): in this setting the attack degenerates into a traditional adversarial-example problem, since the contaminated data directly biases the target-task output without an explicit task-redirecting instruction, so SecInfer's target-task-guided aggregation cannot distinguish the attacker-desired response from a legitimate one (ASR remains high, e.g., 0.90 before and 0.79 after applying SecInfer in the sentiment-analysis example given). The Conclusion additionally frames two forward-looking limitations as future work: the number of candidate responses (and thus computational overhead) required by SecInfer has not been minimized via more advanced sampling/aggregation techniques, and the paper's own adaptive-attack evaluation, while described as comprehensive, is explicitly flagged as something that should be extended with even stronger adaptive prompt injection attacks in future work to more thoroughly evaluate SecInfer's security.</t>
         </is>
       </c>
       <c r="F19" s="5" t="n"/>
@@ -3372,7 +3384,7 @@
       <c r="H19" s="5" t="n"/>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>469d4b8f7660de4bf1651a92bbc1ced997e631ec</t>
+          <t>5b3f710d1923323a0113f6db056aa712a04b0f13</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3394,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>From Untrusted Input to Trusted Memory: A Systematic Study of Memory Poisoning Attacks in LLM Agents</t>
+          <t>SecInfer: Preventing Prompt Injection via Inference-time Scaling</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -3397,7 +3409,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>This paper presents a systematic study of memory poisoning attacks in LLM-based agents with persistent long-term memory, distinguishing this threat from standard prompt injection because a single successful adversarial write can exert lasting influence across future, unrelated sessions rather than requiring the payload to be present in every active context. The paper formalizes agent memory as a tuple M=(S,W,R) (persistent store, write function mapping context to memory updates, retrieval function mapping queries to stored entries) and long-term memory into three types: factual (declarative preferences/policies), experience (past action-outcome records), and procedural (reusable instruction sequences governing execution, treated as higher-impact since it directly drives future behavior). It identifies four memory write channels distinguished by trigger and write authority: explicit instruction-executed write (C1, a direct write where the agent stores exactly what an instruction specifies), system-prompt-driven write (C2, an inferred write where the model judges incoming content against a standing memory-write policy), compaction-driven write (C3, consolidation of interaction history into memory at context-limit or session-end events), and experience-to-procedure write (C4, synthesis of a reusable procedure from past experience). These channels are exploitable due to nine structural vulnerabilities the paper identifies across three system layers: model capability (e.g., V-M1 Instruction-Data Boundary Blindness, where LLMs process all input as a flattened token sequence unable to structurally separate instructions from data; V-M2 Source Attribution Failure in multi-source contexts), prompt design (e.g., V-P2 Compaction Without Source Filtering, where summarization prompts lack source-provenance requirements), and system architecture (e.g., V-S1 No Write-Path Validation, V-S2 Shared Multi-Source Context). Based on these vulnerabilities, the paper develops a taxonomy of six memory poisoning attack classes, each mapped to the specific write channel and vulnerabilities it exploits and labeled by 'signal strength' (whether the payload contains an explicit, detectable injection pattern, i.e. 'strong-signal', such as Explicit/Conditional Command Insertion, or is semantically indistinguishable from legitimate content, i.e. 'weak-signal', such as Policy-Conformant Fact Injection and False Precedent Insertion). The paper builds MPBench, an empirical benchmark evaluating these six attack classes via two metrics -- Attack Success Rate (whether the poisoned entry is successfully written and detected via LLM-judge comparison against the intended adversarial directive) and Retrieval Success Rate (whether a subsequent, unrelated user query causes the poisoned entry to be retrieved and reflected in agent output) -- against two real, deployed agent systems (OpenClaw, HERMES), and separately evaluates whether four existing prompt-injection defenses generalize to cover memory poisoning, finding they do not because weak-signal payloads carry no syntactic anomaly detectable at the input boundary and can only be caught by defenses operating at the memory write path itself (e.g., source isolation, write-path provenance tracking, compaction filters, and post-write monitoring evaluated against the agent's authorized behavior rather than known attack-pattern catalogs).</t>
+          <t>SecInfer is a prevention-based defense against prompt injection that reframes the problem as one to be solved via inference-time scaling -- allocating additional computation during LLM inference -- rather than via prompt pre-processing, fine-tuning, or security-policy enforcement, the three dominant existing defense categories the paper argues have limited effectiveness against strong (especially optimization-based) attacks. The method has two steps. Step I, system-prompt-guided sampling, generates N candidate responses to the (possibly contaminated) prompt, but rather than relying solely on standard stochastic decoding's intrinsic randomness (which the authors show is defeatable under strong attacks, since an attacker can manipulate the underlying output distribution so that most or all sampled responses complete the injected task), it randomly draws each response's chain-of-thought system prompt from a diverse, hand-crafted pool designed to induce different reasoning paths, increasing the odds that at least some candidates correctly complete the target task even under attack. Step II, target-task-guided aggregation, then selects the final response using the target task's own semantics rather than generic aggregation (majority voting or reward-model best-of-N, both shown to be defeatable when a majority of candidates are contaminated): for closed-domain tasks (predefined label sets), it filters candidates to the valid output domain and takes the majority within that filtered set; for open-domain tasks, it embeds candidates, clusters them non-parametrically, extracts each cluster's centroid-nearest representative, and uses a separate judge LLM (which may differ from the backend LLM) to pick the representative that best matches the target instruction. The design explicitly targets the two failure modes of prior inference-time scaling methods like self-consistency under adversarial conditions: contaminated distributions defeating simple randomness-based sampling, and contaminated majorities defeating majority-vote or reward-based aggregation. The one class of injection SecInfer explicitly cannot handle is when the injected task shares the same output type/domain as the target task, since then the attack behaves like a conventional adversarial example rather than an explicit task hijack, and target-task-guided filtering provides no discriminating signal.</t>
         </is>
       </c>
       <c r="F20" s="5" t="n"/>
@@ -3405,7 +3417,7 @@
       <c r="H20" s="5" t="n"/>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>469d4b8f7660de4bf1651a92bbc1ced997e631ec</t>
+          <t>5b3f710d1923323a0113f6db056aa712a04b0f13</t>
         </is>
       </c>
     </row>
@@ -3415,7 +3427,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Repair the Amplifier, Not the Symptom: Stable World-Model Correction for Agent Rollouts</t>
+          <t>A Framework for Formalizing LLM Agent Security</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -3438,7 +3450,7 @@
       <c r="H21" s="5" t="n"/>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>965c0cae557aed318e6305af2749aabb9b6a7051</t>
+          <t>arxiv:2603.19469</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3460,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Repair the Amplifier, Not the Symptom: Stable World-Model Correction for Agent Rollouts</t>
+          <t>A Framework for Formalizing LLM Agent Security</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -3463,7 +3475,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>ML/AI</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="F22" s="5" t="n"/>
@@ -3471,7 +3483,7 @@
       <c r="H22" s="5" t="n"/>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>965c0cae557aed318e6305af2749aabb9b6a7051</t>
+          <t>arxiv:2603.19469</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3493,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Repair the Amplifier, Not the Symptom: Stable World-Model Correction for Agent Rollouts</t>
+          <t>A Framework for Formalizing LLM Agent Security</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -3504,7 +3516,7 @@
       <c r="H23" s="5" t="n"/>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>965c0cae557aed318e6305af2749aabb9b6a7051</t>
+          <t>arxiv:2603.19469</t>
         </is>
       </c>
     </row>
@@ -3514,7 +3526,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Repair the Amplifier, Not the Symptom: Stable World-Model Correction for Agent Rollouts</t>
+          <t>A Framework for Formalizing LLM Agent Security</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -3529,7 +3541,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>defense</t>
+          <t>neither</t>
         </is>
       </c>
       <c r="F24" s="5" t="n"/>
@@ -3537,7 +3549,7 @@
       <c r="H24" s="5" t="n"/>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>965c0cae557aed318e6305af2749aabb9b6a7051</t>
+          <t>arxiv:2603.19469</t>
         </is>
       </c>
     </row>
@@ -3547,7 +3559,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Repair the Amplifier, Not the Symptom: Stable World-Model Correction for Agent Rollouts</t>
+          <t>A Framework for Formalizing LLM Agent Security</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -3562,7 +3574,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>direct-input</t>
+          <t>none</t>
         </is>
       </c>
       <c r="F25" s="5" t="n"/>
@@ -3570,7 +3582,7 @@
       <c r="H25" s="5" t="n"/>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>965c0cae557aed318e6305af2749aabb9b6a7051</t>
+          <t>arxiv:2603.19469</t>
         </is>
       </c>
     </row>
@@ -3580,7 +3592,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Repair the Amplifier, Not the Symptom: Stable World-Model Correction for Agent Rollouts</t>
+          <t>A Framework for Formalizing LLM Agent Security</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -3595,7 +3607,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>goal-hijack</t>
         </is>
       </c>
       <c r="F26" s="5" t="n"/>
@@ -3603,7 +3615,7 @@
       <c r="H26" s="5" t="n"/>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>965c0cae557aed318e6305af2749aabb9b6a7051</t>
+          <t>arxiv:2603.19469</t>
         </is>
       </c>
     </row>
@@ -3613,7 +3625,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Repair the Amplifier, Not the Symptom: Stable World-Model Correction for Agent Rollouts</t>
+          <t>A Framework for Formalizing LLM Agent Security</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -3628,7 +3640,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F27" s="5" t="n"/>
@@ -3636,7 +3648,7 @@
       <c r="H27" s="5" t="n"/>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>965c0cae557aed318e6305af2749aabb9b6a7051</t>
+          <t>arxiv:2603.19469</t>
         </is>
       </c>
     </row>
@@ -3646,7 +3658,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Repair the Amplifier, Not the Symptom: Stable World-Model Correction for Agent Rollouts</t>
+          <t>A Framework for Formalizing LLM Agent Security</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -3661,7 +3673,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F28" s="5" t="n"/>
@@ -3669,7 +3681,7 @@
       <c r="H28" s="5" t="n"/>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>965c0cae557aed318e6305af2749aabb9b6a7051</t>
+          <t>arxiv:2603.19469</t>
         </is>
       </c>
     </row>
@@ -3679,7 +3691,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Repair the Amplifier, Not the Symptom: Stable World-Model Correction for Agent Rollouts</t>
+          <t>A Framework for Formalizing LLM Agent Security</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -3702,7 +3714,7 @@
       <c r="H29" s="5" t="n"/>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>965c0cae557aed318e6305af2749aabb9b6a7051</t>
+          <t>arxiv:2603.19469</t>
         </is>
       </c>
     </row>
@@ -3712,7 +3724,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Repair the Amplifier, Not the Symptom: Stable World-Model Correction for Agent Rollouts</t>
+          <t>A Framework for Formalizing LLM Agent Security</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -3727,7 +3739,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>session-persistent</t>
+          <t>one-shot</t>
         </is>
       </c>
       <c r="F30" s="5" t="n"/>
@@ -3735,7 +3747,7 @@
       <c r="H30" s="5" t="n"/>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>965c0cae557aed318e6305af2749aabb9b6a7051</t>
+          <t>arxiv:2603.19469</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3757,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Repair the Amplifier, Not the Symptom: Stable World-Model Correction for Agent Rollouts</t>
+          <t>A Framework for Formalizing LLM Agent Security</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -3768,7 +3780,7 @@
       <c r="H31" s="5" t="n"/>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>965c0cae557aed318e6305af2749aabb9b6a7051</t>
+          <t>arxiv:2603.19469</t>
         </is>
       </c>
     </row>
@@ -3778,7 +3790,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Repair the Amplifier, Not the Symptom: Stable World-Model Correction for Agent Rollouts</t>
+          <t>A Framework for Formalizing LLM Agent Security</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -3793,7 +3805,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Code released at https://github.com/Hik289/world-model-corrector.git as stated in the abstract ('Our code is available at: https://github.com/Hik289/world-model-corrector.git').</t>
+          <t>No code/artifact release. The paper explicitly states in its Ethical Considerations section: 'This work is a systematization and analysis of existing literature. We conducted no experiments, collected no data, and developed no software artifacts.' All sources cited are publicly accessible academic literature, industry documentation, and security advisories.</t>
         </is>
       </c>
       <c r="F32" s="5" t="n"/>
@@ -3801,7 +3813,7 @@
       <c r="H32" s="5" t="n"/>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>965c0cae557aed318e6305af2749aabb9b6a7051</t>
+          <t>arxiv:2603.19469</t>
         </is>
       </c>
     </row>
@@ -3811,7 +3823,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Repair the Amplifier, Not the Symptom: Stable World-Model Correction for Agent Rollouts</t>
+          <t>A Framework for Formalizing LLM Agent Security</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3826,7 +3838,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>GPT-4o-mini (primary/main evaluation model for LLM root-cause repair), with a cross-model study additionally using GPT-4o and Gemini-2.5-Flash to test whether the context-selection advantage transfers across model families. All models are used only as the downstream repair/root-cause-identification module operating on the corrector-selected subgraph, not as the corrector itself (which is a spectral graph algorithm).</t>
+          <t>None. This is a purely theoretical/formal systematization paper with no original empirical evaluation of any LLM or agent system. The running illustrative example (a cooking-assistant agent) is a synthetic conceptual example, not an evaluated system.</t>
         </is>
       </c>
       <c r="F33" s="5" t="n"/>
@@ -3834,7 +3846,7 @@
       <c r="H33" s="5" t="n"/>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>965c0cae557aed318e6305af2749aabb9b6a7051</t>
+          <t>arxiv:2603.19469</t>
         </is>
       </c>
     </row>
@@ -3844,7 +3856,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Repair the Amplifier, Not the Symptom: Stable World-Model Correction for Agent Rollouts</t>
+          <t>A Framework for Formalizing LLM Agent Security</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3859,7 +3871,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>A synthetic 'Agent Calling-Tree Testbed': 50 synthetic heterogeneous typed calling-tree graphs (~26 nodes each, planner/executor/validator/checker/aggregator/reporter/logger/error_handler/final_answer node types) with programmatically injected cascade error dynamics (e_child = 1.1*e_parent + noise); benchmark-inspired topology simulations matching structural statistics of SWE-bench, WebArena, AgentBench-OS, and SWE-agent-style workflows (n=50, Section 7.6); and the real Who&amp;When multi-agent failure-attribution benchmark (Zhang et al. 2025, n=30 algorithm-generated traces) used as an applicability-boundary/generalization test where per-node error signals are unavailable.</t>
+          <t>No original dataset or benchmark; the paper is a systematic literature analysis covering 87 papers on LLM agent attacks and defenses, used to validate that documented attack classes map onto violations of the paper's proposed four security properties.</t>
         </is>
       </c>
       <c r="F34" s="5" t="n"/>
@@ -3867,7 +3879,7 @@
       <c r="H34" s="5" t="n"/>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>965c0cae557aed318e6305af2749aabb9b6a7051</t>
+          <t>arxiv:2603.19469</t>
         </is>
       </c>
     </row>
@@ -3877,7 +3889,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Repair the Amplifier, Not the Symptom: Stable World-Model Correction for Agent Rollouts</t>
+          <t>A Framework for Formalizing LLM Agent Security</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3892,7 +3904,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On the main calling-tree testbed (Table 1), WM-SAR repairs only 8.3 nodes on average yet achieves rho(B)-reduction of 1.95 with near-flat MSE through horizon H=32 (MSE@32=6.3), matching the stability of LocalRepair-3Hop (25.3 nodes, rho-red 1.97, MSE@32=3.3) while using ~3x fewer nodes; pointwise/window/TopK methods leave MSE@32 in the 92-185 range. On the full 200-instance baseline comparison (Table 7), WM-SAR matches Oracle-Region and LLMRepair-Full-Plan on Recovery (0.625) while using 1,389 tokens per successful recovery vs 10,333 for LLMRepair-Full-Plan (7.4x fewer tokens). In the 3-LLM cross-model root-cause study (Table 5), WM-SAR achieves the highest exact-recovery (Rec-Exact) on all three models: 0.500 (GPT-4o-mini), 0.433 (GPT-4o), 0.759 (Gemini-2.5-Flash), vs LocalRepair-2Hop's 0.267/0.300/0.379, statistically significant for Gemini (McNemar p=0.007). On the real Who&amp;When benchmark WM-SAR underperforms LocalRepair-2Hop (0.20 vs 0.60 Rec-Exact), an explicitly reported applicability boundary since GEAF requires per-node error magnitudes that this blackbox-attribution dataset does not expose.</t>
+          <t>The paper's central contribution is a formal framework for 'contextual security' in LLM agents, built on a formalized agent execution model (execution context C_t as a tuple capturing trust, authorized objective, trajectory history, and permitted information flows; a source permission graph G=(S,R) generalizing traditional access control to agent sources). Four security properties are defined, each corresponding to an authorization-relevant component of C_t: task alignment (the agent pursues objectives authorized by the user's prompt), action alignment (individual actions serve the stated task objectives), source authorization (instructions originate from authenticated sources), and data isolation (information flows respect privilege/permission boundaries). To make these properties verifiable at runtime, the paper introduces oracle functions analogous to ideal functionalities in cryptographic protocol analysis: an instruction attribution function I (identifies which inputs contain the instructions an agent actually followed to produce a given action), a source attribution function L (tracks provenance of agent inputs), and objective evaluation functions H_p, H_Tr, H_a (quantify task objectives at different levels). Using this apparatus, the paper reformalizes existing attacks with newly precise, context-aware definitions: indirect prompt injection is redefined as occurring when an agent follows instructions from an unauthorized-source input (violating source authorization) AND the resulting action does not align with the intended task objective (violating action alignment) -- a stricter and more precise definition than prior work (e.g. Liu et al.) that classified any data input containing a prompt as injection regardless of context, which the authors show causes false positives when such prompts originate from authorized sources and align with the task. Direct prompt injection is instead redefined as occurring when an authorized user's own input contains a prompt conflicting with a higher-privilege objective (e.g. the system prompt), violating task alignment alone. Jailbreak, task drift, and memory poisoning attacks are similarly reformalized as violations of one or more of the four properties. The framework is also used to systematize existing defenses as mechanisms that either strengthen the oracle function approximations or directly enforce checks on the four properties, revealing two systematic classes of defense failure: context-agnostic (pattern-based) defenses cannot distinguish context-dependent authorization (causing unavoidable utility-security trade-offs, e.g. blocking all 'delete file' commands prevents both legitimate cleanup and malicious data destruction using identical surface text), and single-property defenses remain vulnerable to attacks that simultaneously violate multiple properties.</t>
         </is>
       </c>
       <c r="F35" s="5" t="n"/>
@@ -3900,7 +3912,7 @@
       <c r="H35" s="5" t="n"/>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>965c0cae557aed318e6305af2749aabb9b6a7051</t>
+          <t>arxiv:2603.19469</t>
         </is>
       </c>
     </row>
@@ -3910,7 +3922,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Repair the Amplifier, Not the Symptom: Stable World-Model Correction for Agent Rollouts</t>
+          <t>A Framework for Formalizing LLM Agent Security</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3925,7 +3937,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Pointwise: Greedy-Point(K=1), TopK-Point(K=3/5), LastError-Point, FirstFailedCall-Point. Window-based: Window-2/4/8-Point, TraceScan-w1/w2/w4-Point/LLM. Neighbourhood/cascade: LocalRepair-2Hop/3Hop, CascadeRepair, k-hop-k2. Global-influence: PageRank-Subgraph. Uncertainty-Subgraph (uncertainty triage). Full-graph: Full-Graph-LLM, LLMRepair-Full-Plan, TraceScan-Full-Point/LLM, Top-B-Nodes/Edges. Oracle-Region (ground-truth corrupted region, attribution upper bound).</t>
+          <t>Not applicable in the empirical sense; the paper instead systematically re-analyzes and critiques prior attack/defense definitions as its comparative baseline -- explicitly showing its context-aware indirect/direct prompt injection definitions are more precise than the definition used in prior work (Liu et al. and the several LLM agent prompt-injection benchmarks that subsequently adopted it), and showing that context-agnostic pattern-matching defenses and single-property-focused defenses each have systematic, provable blind spots under the new framework.</t>
         </is>
       </c>
       <c r="F36" s="5" t="n"/>
@@ -3933,7 +3945,7 @@
       <c r="H36" s="5" t="n"/>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>965c0cae557aed318e6305af2749aabb9b6a7051</t>
+          <t>arxiv:2603.19469</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3955,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Repair the Amplifier, Not the Symptom: Stable World-Model Correction for Agent Rollouts</t>
+          <t>A Framework for Formalizing LLM Agent Security</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3958,7 +3970,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>N/A - non-adversarial. This is a systems-reliability/agent-debugging paper, not a security paper; the incidental failure mode of interest is that long-horizon LLM agents maintaining executable world-model planning graphs (tool calls, validators, memory updates, recovery branches) can fail via error amplification, where repairing the most visible/highest-error node ('the symptom') leaves the underlying causal amplification path intact and allows the failure to recreate itself in subsequent rollouts, while replaying/serializing the full graph is too expensive and unreliable for long-context LLMs to use effectively.</t>
+          <t>Highly formalized general threat model (Section 3) underlying the whole framework. Agents interact with external systems via tool use (reading files, executing code, querying databases, sending messages) and receive inputs from multiple sources of varying trust: authenticated users, external content (emails, web pages, documents), system processes, and tool outputs; the agent maintains persistent memory across interactions. Two categories of security violation are named: confidentiality violations (leaking sensitive system information to external parties) and integrity violations (executing commands on behalf of unauthorized sources, pursuing objectives outside the agent's authorized scope, or performing action sequences inconsistent with legitimate workflows -- e.g. an attacker causing an agent to delete production data under the guise of debugging, or redirect funds to unauthorized accounts) plus persistent compromise via memory poisoning that affects future interactions and enables cascading cross-session attacks. Attacker background knowledge may include memory contents M_t (particularly system prompts in open-source deployments), inferred current task objectives from observed trajectory/environment state, and available tools; the framework explicitly makes no assumption about attacker access to the underlying LLM f itself, since attacks operate purely through input manipulation regardless of model accessibility, and attackers typically cannot access other users' private memory data or the system's exact internal security policies. Attacker capabilities center on manipulating different classes of agent inputs: crafting malicious user prompts p to perform jailbreak and direct prompt injection attacks (attempting to override intended objectives or bypass safety measures), and (implied, continuing beyond the excerpt) manipulating external/tool-sourced content for indirect prompt injection and memory poisoning.</t>
         </is>
       </c>
       <c r="F37" s="5" t="n"/>
@@ -3966,7 +3978,7 @@
       <c r="H37" s="5" t="n"/>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>965c0cae557aed318e6305af2749aabb9b6a7051</t>
+          <t>arxiv:2603.19469</t>
         </is>
       </c>
     </row>
@@ -3976,7 +3988,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Repair the Amplifier, Not the Symptom: Stable World-Model Correction for Agent Rollouts</t>
+          <t>A Framework for Formalizing LLM Agent Security</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3991,7 +4003,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>The paper has an explicit 'Limitations' section: the evaluation is primarily synthetic and diagnostic (50 synthetic ~26-node calling-tree graphs with programmatically generated cascade dynamics, not collected from real deployed systems); the benchmark-topology simulations match structural statistics of SWE-bench/WebArena/AgentBench-OS but do not use actual failed rollout logs; the Who&amp;When real-attribution test is only a small (n=30) boundary check, not full validation on real human-attributed rollout traces; the graph world-model error operators (LX, MX, LA, MA) are estimated from graph statistics rather than a trained parametric GWM (e.g. Error-Aware GWM); state correction is implemented only by zeroing node errors, not edge-structure correction, target-cone rollback, re-rollout from a repair boundary, or validator-boundary insertion (these require per-edge probabilities, live re-simulation, or a runtime validator API absent from the failure-graph-only setting); and the repair objective rho(B_{Gf\R}) is only one valid criterion, losing its advantage in blackbox attribution settings where only final outputs (not per-node errors) are visible.</t>
+          <t>Explicit 'Discussion and Limitations' section (Section 8) with several named sub-limitations. Operational definition of instructions: the framework's instruction-attribution function I defines an input as an instruction only operationally (if it caused an action), which cannot be evaluated without solving causal attribution, treats instruction-ness as binary when influence is actually continuous, and cannot rely on purely linguistic definitions since whether text functions as an instruction is itself context-dependent; the authors note LLM agents may require explicit architectural mechanisms to distinguish instructional from informational inputs. Scope and applicability: the framework applies only to synchronous agents that await observations before proceeding (agents with different execution models may require modified property definitions), focuses on operational security of already-deployed agents rather than training-time attacks, addresses confidentiality/integrity violations rather than availability (denial-of-service and resource exhaustion are explicitly treated as a distinct failure class largely addressed by standard system-level mitigations), and assumes standard security infrastructure (authentication, access control) is already present, with environments lacking these limiting the framework's utility. Oracle approximation quality: the oracle functions define what is theoretically required for contextual authorization but must themselves be approximated in practice, and advancing agent security requires moving beyond content filtering toward better approximating authorization context, an open challenge left largely unaddressed. Compositional safety and framework completeness: the framework identifies compositional violations but does not fully formalize compositional safety (which would require modeling environment state dynamics and enumerating which state changes are safe individually but unsafe in combination); the authors explicitly do not claim the four properties are formally complete or axiomatically derived -- they are shown to be necessary (violations map to known documented security breaches across the 87-paper analysis) but not proven sufficient, and future research may identify attacks requiring additional properties beyond the four proposed.</t>
         </is>
       </c>
       <c r="F38" s="5" t="n"/>
@@ -3999,7 +4011,7 @@
       <c r="H38" s="5" t="n"/>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>965c0cae557aed318e6305af2749aabb9b6a7051</t>
+          <t>arxiv:2603.19469</t>
         </is>
       </c>
     </row>
@@ -4009,7 +4021,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Repair the Amplifier, Not the Symptom: Stable World-Model Correction for Agent Rollouts</t>
+          <t>A Framework for Formalizing LLM Agent Security</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -4024,7 +4036,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>The paper formulates 'world-model correction' for long-horizon LLM agents that maintain planning graphs (typed nodes for planner/executor/validator/etc., typed causal-dependency edges) as the problem of selecting a compact, connected subgraph of a failed rollout's planning graph whose targeted repair stabilizes future rollouts, rather than re-planning or replaying the entire graph. It first formalizes rollout-error propagation theoretically: under a fixed-edge Lipschitz assumption and a coupled node-edge error-propagation operator B (combining node-state Lipschitz constant LX, edge-state constant MA, and cross-coupling terms LA, MX), the spectral radius rho(B) governs whether errors decay or amplify across rollout steps, and a derived planning-regret bound shows the future policy gap is controlled by this residual spectral radius. Building on this theory, the paper proposes WM-SAR (World-Model Subgraph Amplification Repair): it computes a per-node Graph Error Amplification Field (GEAF) score combining observed error e(v) with local structural amplification rho(Av), estimates a node-edge coupling factor kappa_v, ranks seed candidates by e(v)*GEAF*(1+kappa_v), then greedily grows a connected repair region by maximal marginal reduction in the residual spectral radius (Delta-rho-relief) subject to a repair budget, prunes redundant nodes, and only then serializes the final compact region (not the whole graph) to an LLM for root-cause repair. This is benchmarked against a family of engineering correctors (pointwise scans, sliding windows, k-hop neighborhood expansion, cascade repair, full-graph LLM repair) that optimize visible error rather than the residual amplification operator.</t>
+          <t>This paper argues that LLM agent security is inherently contextual -- the same action can be either legitimate behavior or a security violation depending on who issued the underlying instruction, what objective is being pursued, and whether the action serves that objective -- and that existing attack definitions (most notably the widely adopted definition of prompt injection as any data input containing embedded instructions) fail to capture this context-dependence, forcing an unavoidable utility-security trade-off where uniformly applied defenses either produce excessive false positives or leave genuine vulnerabilities. To resolve this, the authors formalize a general LLM agent execution model (user prompt, action-observation trajectory, environment state, persistent memory, and a source-attributed input space governed by a source permission graph generalizing classical access control) and define four contextual security properties directly corresponding to the authorization-relevant components of this model: task alignment (pursued objectives are authorized), action alignment (individual actions serve those objectives), source authorization (executed instructions originate from authenticated sources), and data isolation (information flows respect privilege boundaries). To make these properties checkable at runtime despite being defined over ideally-complete information, the paper introduces 'oracle functions' -- explicitly analogous to ideal functionalities in cryptographic protocol analysis -- comprising an instruction attribution function (identifying which inputs caused a given action), a source attribution function (tracking input provenance), and objective evaluation functions (quantifying task-objective satisfaction at the prompt, trajectory, and action levels), which together specify what information any real defense mechanism must approximate to achieve genuine contextual authorization. Using this apparatus, the paper reformalizes major existing LLM agent attack classes -- indirect prompt injection, direct prompt injection, jailbreak, task drift, and memory poisoning -- as precise combinations of one or more property violations rather than surface-pattern-based classifications, notably yielding a stricter and more accurate definition of indirect prompt injection (unauthorized source AND misaligned action) than prior benchmark-adopted definitions, and similarly reformalizes existing defenses as mechanisms that either strengthen the oracle function approximations or directly enforce property checks, using this lens to reveal two systematic classes of defense failure (context-agnostic pattern matching, and single-property-only coverage) that scattered prior work had not clearly articulated. The paper is explicitly a systematization/theory contribution -- no experiments were run, no data collected, and no software built -- validated by an analysis of 87 papers showing documented attack classes consistently map onto violations of the proposed four properties, and closes by identifying concrete future research directions including practical oracle-function implementation, formalizing multi-agent delegation mechanisms, and developing benchmarks that evaluate these properties across extended agent interactions.</t>
         </is>
       </c>
       <c r="F39" s="5" t="n"/>
@@ -4032,7 +4044,7 @@
       <c r="H39" s="5" t="n"/>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>965c0cae557aed318e6305af2749aabb9b6a7051</t>
+          <t>arxiv:2603.19469</t>
         </is>
       </c>
     </row>
@@ -4042,7 +4054,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Enhancing Retrieval-Augmented Large Vision Language Models via Knowledge Conflict Mitigation</t>
+          <t>Tensor Trust: Interpretable Prompt Injection Attacks from an Online Game</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -4065,7 +4077,7 @@
       <c r="H40" s="5" t="n"/>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>452b4750bfc661f1a78a953f56ebdf2d34369a19</t>
+          <t>e25b4bdfc3f5a8293ea6cd687a0203e446594188</t>
         </is>
       </c>
     </row>
@@ -4075,7 +4087,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Enhancing Retrieval-Augmented Large Vision Language Models via Knowledge Conflict Mitigation</t>
+          <t>Tensor Trust: Interpretable Prompt Injection Attacks from an Online Game</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -4090,7 +4102,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>ML/AI</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="F41" s="5" t="n"/>
@@ -4098,7 +4110,7 @@
       <c r="H41" s="5" t="n"/>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>452b4750bfc661f1a78a953f56ebdf2d34369a19</t>
+          <t>e25b4bdfc3f5a8293ea6cd687a0203e446594188</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4120,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Enhancing Retrieval-Augmented Large Vision Language Models via Knowledge Conflict Mitigation</t>
+          <t>Tensor Trust: Interpretable Prompt Injection Attacks from an Online Game</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -4131,7 +4143,7 @@
       <c r="H42" s="5" t="n"/>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>452b4750bfc661f1a78a953f56ebdf2d34369a19</t>
+          <t>e25b4bdfc3f5a8293ea6cd687a0203e446594188</t>
         </is>
       </c>
     </row>
@@ -4141,7 +4153,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Enhancing Retrieval-Augmented Large Vision Language Models via Knowledge Conflict Mitigation</t>
+          <t>Tensor Trust: Interpretable Prompt Injection Attacks from an Online Game</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -4156,7 +4168,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>defense</t>
+          <t>attack</t>
         </is>
       </c>
       <c r="F43" s="5" t="n"/>
@@ -4164,7 +4176,7 @@
       <c r="H43" s="5" t="n"/>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>452b4750bfc661f1a78a953f56ebdf2d34369a19</t>
+          <t>e25b4bdfc3f5a8293ea6cd687a0203e446594188</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4186,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Enhancing Retrieval-Augmented Large Vision Language Models via Knowledge Conflict Mitigation</t>
+          <t>Tensor Trust: Interpretable Prompt Injection Attacks from an Online Game</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -4189,7 +4201,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>cross-modal</t>
+          <t>direct-input</t>
         </is>
       </c>
       <c r="F44" s="5" t="n"/>
@@ -4197,7 +4209,7 @@
       <c r="H44" s="5" t="n"/>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>452b4750bfc661f1a78a953f56ebdf2d34369a19</t>
+          <t>e25b4bdfc3f5a8293ea6cd687a0203e446594188</t>
         </is>
       </c>
     </row>
@@ -4207,7 +4219,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Enhancing Retrieval-Augmented Large Vision Language Models via Knowledge Conflict Mitigation</t>
+          <t>Tensor Trust: Interpretable Prompt Injection Attacks from an Online Game</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -4222,7 +4234,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>silent-corruption</t>
+          <t>goal-hijack</t>
         </is>
       </c>
       <c r="F45" s="5" t="n"/>
@@ -4230,7 +4242,7 @@
       <c r="H45" s="5" t="n"/>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>452b4750bfc661f1a78a953f56ebdf2d34369a19</t>
+          <t>e25b4bdfc3f5a8293ea6cd687a0203e446594188</t>
         </is>
       </c>
     </row>
@@ -4240,7 +4252,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Enhancing Retrieval-Augmented Large Vision Language Models via Knowledge Conflict Mitigation</t>
+          <t>Tensor Trust: Interpretable Prompt Injection Attacks from an Online Game</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -4255,7 +4267,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F46" s="5" t="n"/>
@@ -4263,7 +4275,7 @@
       <c r="H46" s="5" t="n"/>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>452b4750bfc661f1a78a953f56ebdf2d34369a19</t>
+          <t>e25b4bdfc3f5a8293ea6cd687a0203e446594188</t>
         </is>
       </c>
     </row>
@@ -4273,7 +4285,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Enhancing Retrieval-Augmented Large Vision Language Models via Knowledge Conflict Mitigation</t>
+          <t>Tensor Trust: Interpretable Prompt Injection Attacks from an Online Game</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4296,7 +4308,7 @@
       <c r="H47" s="5" t="n"/>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>452b4750bfc661f1a78a953f56ebdf2d34369a19</t>
+          <t>e25b4bdfc3f5a8293ea6cd687a0203e446594188</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4318,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Enhancing Retrieval-Augmented Large Vision Language Models via Knowledge Conflict Mitigation</t>
+          <t>Tensor Trust: Interpretable Prompt Injection Attacks from an Online Game</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4321,7 +4333,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>reasoning</t>
+          <t>none</t>
         </is>
       </c>
       <c r="F48" s="5" t="n"/>
@@ -4329,7 +4341,7 @@
       <c r="H48" s="5" t="n"/>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>452b4750bfc661f1a78a953f56ebdf2d34369a19</t>
+          <t>e25b4bdfc3f5a8293ea6cd687a0203e446594188</t>
         </is>
       </c>
     </row>
@@ -4339,7 +4351,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Enhancing Retrieval-Augmented Large Vision Language Models via Knowledge Conflict Mitigation</t>
+          <t>Tensor Trust: Interpretable Prompt Injection Attacks from an Online Game</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4362,7 +4374,7 @@
       <c r="H49" s="5" t="n"/>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>452b4750bfc661f1a78a953f56ebdf2d34369a19</t>
+          <t>e25b4bdfc3f5a8293ea6cd687a0203e446594188</t>
         </is>
       </c>
     </row>
@@ -4372,7 +4384,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Enhancing Retrieval-Augmented Large Vision Language Models via Knowledge Conflict Mitigation</t>
+          <t>Tensor Trust: Interpretable Prompt Injection Attacks from an Online Game</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4395,7 +4407,7 @@
       <c r="H50" s="5" t="n"/>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>452b4750bfc661f1a78a953f56ebdf2d34369a19</t>
+          <t>e25b4bdfc3f5a8293ea6cd687a0203e446594188</t>
         </is>
       </c>
     </row>
@@ -4405,7 +4417,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Enhancing Retrieval-Augmented Large Vision Language Models via Knowledge Conflict Mitigation</t>
+          <t>Tensor Trust: Interpretable Prompt Injection Attacks from an Online Game</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4418,13 +4430,17 @@
           <t>secondary</t>
         </is>
       </c>
-      <c r="E51" s="2" t="n"/>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Y - full dataset and web-game source code at tensortrust.ai/paper, with the extraction-detection dataset at github.com/HumanCompatibleAI/tensor-trust-data</t>
+        </is>
+      </c>
       <c r="F51" s="5" t="n"/>
       <c r="G51" s="5" t="n"/>
       <c r="H51" s="5" t="n"/>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>452b4750bfc661f1a78a953f56ebdf2d34369a19</t>
+          <t>e25b4bdfc3f5a8293ea6cd687a0203e446594188</t>
         </is>
       </c>
     </row>
@@ -4434,7 +4450,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Enhancing Retrieval-Augmented Large Vision Language Models via Knowledge Conflict Mitigation</t>
+          <t>Tensor Trust: Interpretable Prompt Injection Attacks from an Online Game</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4449,7 +4465,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Six representative Large Vision Language Models, including LLaVA-1.5 (7B) and InstructBLIP-family models. Retrieval uses the CLIP-ViT-L/14-336 vision encoder, with Wikipedia dumps and associated images as the knowledge base. Multinomial sampling is the default decoding strategy, with six alternatives (Top-P, Top-K, greedy, temperature sampling and others) tested for robustness.</t>
+          <t>Eight benchmark models: GPT-3.5 Turbo (gpt-3.5-turbo-0613), GPT-4, Claude-instant-1.2, Claude-2.0, PaLM 2, and LLaMA 2 Chat at 7B, 13B and 70B. Attack transfer was additionally tested against the deployed applications ChatGPT, Claude, Bard, Bing Chat and Notion AI.</t>
         </is>
       </c>
       <c r="F52" s="5" t="n"/>
@@ -4457,7 +4473,7 @@
       <c r="H52" s="5" t="n"/>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>452b4750bfc661f1a78a953f56ebdf2d34369a19</t>
+          <t>e25b4bdfc3f5a8293ea6cd687a0203e446594188</t>
         </is>
       </c>
     </row>
@@ -4467,7 +4483,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Enhancing Retrieval-Augmented Large Vision Language Models via Knowledge Conflict Mitigation</t>
+          <t>Tensor Trust: Interpretable Prompt Injection Attacks from an Online Game</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4482,7 +4498,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Seven knowledge-intensive datasets across three categories: free-form generative (Human, Validation), multi-choice discriminative (InfoSeek, ViQuAE), and commonsense knowledge (OK-VQA, AOK-VQA, Encyclopedic VQA). Knowledge base is Wikipedia dumps with associated images. Metrics are accuracy plus Memorization Ratio and Context Ratio quantifying reliance on parametric versus contextual knowledge; discriminative results are averaged over three runs.</t>
+          <t>Releases 126,808 human-written prompt injection attacks (69,906 distinct attacker inputs) and roughly 46,000 prompt-based defenses collected from the Tensor Trust web game -- the largest human-generated adversarial dataset for instruction-following LLMs at the time. Derives two robustness benchmarks by adversarial filtering and manual validation: prompt hijacking (775 samples) and prompt extraction (569 samples), scored by Hijacking/Extraction Robustness Rate and Defense Validity, plus a 230-sample class-balanced dataset for detecting prompt extraction.</t>
         </is>
       </c>
       <c r="F53" s="5" t="n"/>
@@ -4490,7 +4506,7 @@
       <c r="H53" s="5" t="n"/>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>452b4750bfc661f1a78a953f56ebdf2d34369a19</t>
+          <t>e25b4bdfc3f5a8293ea6cd687a0203e446594188</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4516,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Enhancing Retrieval-Augmented Large Vision Language Models via Knowledge Conflict Mitigation</t>
+          <t>Tensor Trust: Interpretable Prompt Injection Attacks from an Online Game</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4515,7 +4531,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>KCM outperforms state-of-the-art methods consistently and by clear margins across both generative and discriminative benchmarks, without extra training or external tools. The evaluation is broad by the standards of this corpus: six representative LVLMs (including LLaVA-1.5 7B and InstructBLIP-class models) across seven datasets spanning three task types - free-form generative (Human, Validation), multi-choice discriminative (InfoSeek, ViQuAE), and commonsense (OK-VQA, AOK-VQA, Encyclopedic VQA) - with discriminative results averaged over three runs. Robustness of the finding is tested against decoding strategy, which matters because the method manipulates logits: beyond the default multinomial sampling, the authors verify effectiveness on InfoSeek with LLaVA-1.5 under six further decoding strategies including Top-P (p=0.5), Top-K (k=50), greedy, and temperature sampling, so the gain is not an artifact of one sampling regime. Comparisons include the parametric-only condition and the contrastive decoding family (CD, CAD, AdaCAD) as baselines, and a control condition using perfect contextual knowledge (GT Context) establishes the ceiling. The Memorization Ratio and Context Ratio metrics show the improvement comes from shifting reliance toward contextual knowledge, confirming the intended mechanism rather than merely reporting higher accuracy.</t>
+          <t>Even the most capable LLMs fall to basic human-written attacks on a task as simple as controlling when the model says 'access granted': all eight benchmarked models show low hijacking and extraction robustness, with Claude-instant-1.2 outperforming GPT-3.5 Turbo and Bard, GPT-4 best on defense validity and extraction robustness, and LLaMA 2 Chat (especially 70B) much weaker on extraction than hijacking because its verbose 'helpful' refusals leak the defense prompt. An ablation over OpenAI message roles shows role separation gives little protection. Some attacks transfer verbatim to ChatGPT, Claude, Bard, Bing Chat and Notion AI, though only 1 of 3 tested strategies transferred reliably across ten phrasings.</t>
         </is>
       </c>
       <c r="F54" s="5" t="n"/>
@@ -4523,7 +4539,7 @@
       <c r="H54" s="5" t="n"/>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>452b4750bfc661f1a78a953f56ebdf2d34369a19</t>
+          <t>e25b4bdfc3f5a8293ea6cd687a0203e446594188</t>
         </is>
       </c>
     </row>
@@ -4533,7 +4549,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Enhancing Retrieval-Augmented Large Vision Language Models via Knowledge Conflict Mitigation</t>
+          <t>Tensor Trust: Interpretable Prompt Injection Attacks from an Online Game</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4548,7 +4564,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Regular decoding, a parametric-knowledge-only condition, and three contrastive-decoding methods - CD, CAD and AdaCAD - evaluated per model on InfoSeek and ViQuAE among others. A ground-truth-context (GT Context) condition provides the perfect-retrieval upper bound. Six LVLMs are used as the model axis, and six additional decoding strategies serve as a robustness check on the comparison.</t>
+          <t>Cross-model comparison of eight LLMs on both benchmarks against reference models (GPT-3.5 Turbo, Claude Instant 1.2, PaLM 2) used for filtering, plus a message-role ablation and a dummy irrelevant-text 'attack' as a control in the transfer study; GPT-3.5 Turbo versus GPT-4 as zero-shot extraction detectors.</t>
         </is>
       </c>
       <c r="F55" s="5" t="n"/>
@@ -4556,7 +4572,7 @@
       <c r="H55" s="5" t="n"/>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>452b4750bfc661f1a78a953f56ebdf2d34369a19</t>
+          <t>e25b4bdfc3f5a8293ea6cd687a0203e446594188</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4582,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Enhancing Retrieval-Augmented Large Vision Language Models via Knowledge Conflict Mitigation</t>
+          <t>Tensor Trust: Interpretable Prompt Injection Attacks from an Online Game</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4579,13 +4595,17 @@
           <t>freetext</t>
         </is>
       </c>
-      <c r="E56" s="2" t="n"/>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>A malicious user (or third party whose text reaches the prompt) submits input to an LLM application to subvert the system designer's intent, without knowing the defense prompt or the secret access code. Two goals are distinguished: prompt hijacking, overriding the defense so the model emits the attacker's target string, and prompt extraction, making the model reveal enough of the defense prompt or access code to break in or clone the app. The attacker has only black-box prompt access.</t>
+        </is>
+      </c>
       <c r="F56" s="5" t="n"/>
       <c r="G56" s="5" t="n"/>
       <c r="H56" s="5" t="n"/>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>452b4750bfc661f1a78a953f56ebdf2d34369a19</t>
+          <t>e25b4bdfc3f5a8293ea6cd687a0203e446594188</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4615,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Enhancing Retrieval-Augmented Large Vision Language Models via Knowledge Conflict Mitigation</t>
+          <t>Tensor Trust: Interpretable Prompt Injection Attacks from an Online Game</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4610,7 +4630,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>The paper is a strong empirical contribution but its scope conditions bound the claim. KCM requires white-box access to modify attention distributions, prune neurons, and inject logits, so it is inapplicable to closed API models - a significant deployment constraint not shared by prompt-level defenses. Neuron pruning targets neurons encoding coarse-grained parametric knowledge; suppressing parametric knowledge is beneficial exactly when retrieved context is correct, but the paper's framing assumes context should generally win, and the case where retrieval is wrong and parametric memory is right is the mirror risk that the Memorization/Context Ratio metrics illuminate but do not resolve. Evaluation is entirely on incidental knowledge conflict arising from ordinary retrieval misalignment; no adversarial or deliberately poisoned context is tested, so the method's behaviour under an attacker who controls the retrieved item - the PoisonedRAG-style threat model - is unestablished, which is precisely the cross-threat-model gap this SoK documents. Retrieval uses a fixed CLIP-ViT-L/14-336 encoder appending only the top-1 retrieved item, so sensitivity to retrieval depth and quality is not explored.</t>
+          <t>The authors note their benchmark task (a string-comparison game) is far simpler than real applications, so they view it as a lower bound on the robustness needed; that many attacks do not transfer robustly across settings and need manual tweaking to produce serious breaks; and that building a truly robust prompt-extraction classifier remains an open problem left to future work (GPT-3.5 Turbo barely beats random guessing at it).</t>
         </is>
       </c>
       <c r="F57" s="5" t="n"/>
@@ -4618,7 +4638,7 @@
       <c r="H57" s="5" t="n"/>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>452b4750bfc661f1a78a953f56ebdf2d34369a19</t>
+          <t>e25b4bdfc3f5a8293ea6cd687a0203e446594188</t>
         </is>
       </c>
     </row>
@@ -4628,7 +4648,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Enhancing Retrieval-Augmented Large Vision Language Models via Knowledge Conflict Mitigation</t>
+          <t>Tensor Trust: Interpretable Prompt Injection Attacks from an Online Game</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4643,7 +4663,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Proposes KCM, a training-free, plug-and-play framework that mitigates knowledge conflicts in Multimodal Retrieval-Augmented Generation for Large Vision Language Models. The problem it targets is a Track B incidental mechanism rather than an attack: MRAG retrieves external contextual knowledge to compensate for an LVLM's coarse-grained parametric knowledge, but the retrieved content is frequently misaligned with what the model already believes, and the resulting conflict produces unreliable responses - the paper's running example being a model answering 'Japan' from parametric memory when the retrieved context indicates Holland. KCM intervenes on the model's internals at inference time from three complementary angles. First, it adaptively adjusts attention distributions across attention heads so the model attends to contextual knowledge with less distraction. Second, it identifies and prunes 'knowledge-centric' neurons that encode coarse-grained parametric knowledge, suppressing the internal signal that competes with retrieved context. Third, it amplifies information flow from the input context by injecting supplementary context logits, reinforcing the context's contribution to the output distribution. Notably all three operate on the architecture at inference without retraining or external tooling, making it a reasoning-stage defense in this corpus's terms and directly comparable to the contrastive-decoding family (CD, CAD, AdaCAD) that RQ6's CK-PLUG case study also belongs to. The paper measures not just accuracy but the balance of knowledge sources, reporting Memorization Ratio and Context Ratio to quantify reliance on parametric versus contextual knowledge - a diagnostic pairing that makes the mechanism of improvement visible rather than inferred.</t>
+          <t>Presents Tensor Trust, an online game whose players write defense prompts that should make an LLM output 'access granted' only for a secret code, and attack prompts that try to break in, yielding the largest public corpus of human-generated prompt injection attacks and prompt-based defenses. Turns that corpus into two adversarially filtered robustness benchmarks, for prompt hijacking and prompt extraction, and evaluates eight LLMs with Hijacking/Extraction Robustness Rate and Defense Validity metrics. Applies LDA topic modeling to 3,912 successful attacks to distill 16 interpretable, compositional attack strategies (role-play, fake completions, repeated characters, glitch tokens such as artisanlib, and so on) and shows several transfer to deployed chatbots and writing assistants. Matters because it supplies the human-attack distribution and the hijacking/extraction benchmarks that several defenses in this corpus (including the Instruction Hierarchy) evaluate against, and because its message-role ablation is early evidence that role separation alone does not stop injection.</t>
         </is>
       </c>
       <c r="F58" s="5" t="n"/>
@@ -4651,7 +4671,7 @@
       <c r="H58" s="5" t="n"/>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>452b4750bfc661f1a78a953f56ebdf2d34369a19</t>
+          <t>e25b4bdfc3f5a8293ea6cd687a0203e446594188</t>
         </is>
       </c>
     </row>
@@ -4661,7 +4681,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Uncovering Security Threats and Architecting Defenses in Autonomous Agents: A Case Study of OpenClaw</t>
+          <t>Manipulating LLM Web Agents with Indirect Prompt Injection Attack via HTML Accessibility Tree</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4684,7 +4704,7 @@
       <c r="H59" s="5" t="n"/>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>ec338413be097a8f6de120397411e86952c475ca</t>
+          <t>2b73f8dbb2af737fe707df3b2dcb21a9cea62db5</t>
         </is>
       </c>
     </row>
@@ -4694,7 +4714,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Uncovering Security Threats and Architecting Defenses in Autonomous Agents: A Case Study of OpenClaw</t>
+          <t>Manipulating LLM Web Agents with Indirect Prompt Injection Attack via HTML Accessibility Tree</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4717,7 +4737,7 @@
       <c r="H60" s="5" t="n"/>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>ec338413be097a8f6de120397411e86952c475ca</t>
+          <t>2b73f8dbb2af737fe707df3b2dcb21a9cea62db5</t>
         </is>
       </c>
     </row>
@@ -4727,7 +4747,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Uncovering Security Threats and Architecting Defenses in Autonomous Agents: A Case Study of OpenClaw</t>
+          <t>Manipulating LLM Web Agents with Indirect Prompt Injection Attack via HTML Accessibility Tree</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4750,7 +4770,7 @@
       <c r="H61" s="5" t="n"/>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>ec338413be097a8f6de120397411e86952c475ca</t>
+          <t>2b73f8dbb2af737fe707df3b2dcb21a9cea62db5</t>
         </is>
       </c>
     </row>
@@ -4760,7 +4780,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Uncovering Security Threats and Architecting Defenses in Autonomous Agents: A Case Study of OpenClaw</t>
+          <t>Manipulating LLM Web Agents with Indirect Prompt Injection Attack via HTML Accessibility Tree</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4775,7 +4795,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>defense</t>
+          <t>attack</t>
         </is>
       </c>
       <c r="F62" s="5" t="n"/>
@@ -4783,7 +4803,7 @@
       <c r="H62" s="5" t="n"/>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>ec338413be097a8f6de120397411e86952c475ca</t>
+          <t>2b73f8dbb2af737fe707df3b2dcb21a9cea62db5</t>
         </is>
       </c>
     </row>
@@ -4793,7 +4813,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Uncovering Security Threats and Architecting Defenses in Autonomous Agents: A Case Study of OpenClaw</t>
+          <t>Manipulating LLM Web Agents with Indirect Prompt Injection Attack via HTML Accessibility Tree</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -4816,7 +4836,7 @@
       <c r="H63" s="5" t="n"/>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>ec338413be097a8f6de120397411e86952c475ca</t>
+          <t>2b73f8dbb2af737fe707df3b2dcb21a9cea62db5</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4846,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Uncovering Security Threats and Architecting Defenses in Autonomous Agents: A Case Study of OpenClaw</t>
+          <t>Manipulating LLM Web Agents with Indirect Prompt Injection Attack via HTML Accessibility Tree</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -4849,7 +4869,7 @@
       <c r="H64" s="5" t="n"/>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>ec338413be097a8f6de120397411e86952c475ca</t>
+          <t>2b73f8dbb2af737fe707df3b2dcb21a9cea62db5</t>
         </is>
       </c>
     </row>
@@ -4859,7 +4879,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Uncovering Security Threats and Architecting Defenses in Autonomous Agents: A Case Study of OpenClaw</t>
+          <t>Manipulating LLM Web Agents with Indirect Prompt Injection Attack via HTML Accessibility Tree</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -4874,7 +4894,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F65" s="5" t="n"/>
@@ -4882,7 +4902,7 @@
       <c r="H65" s="5" t="n"/>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>ec338413be097a8f6de120397411e86952c475ca</t>
+          <t>2b73f8dbb2af737fe707df3b2dcb21a9cea62db5</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4912,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Uncovering Security Threats and Architecting Defenses in Autonomous Agents: A Case Study of OpenClaw</t>
+          <t>Manipulating LLM Web Agents with Indirect Prompt Injection Attack via HTML Accessibility Tree</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -4915,7 +4935,7 @@
       <c r="H66" s="5" t="n"/>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>ec338413be097a8f6de120397411e86952c475ca</t>
+          <t>2b73f8dbb2af737fe707df3b2dcb21a9cea62db5</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4945,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Uncovering Security Threats and Architecting Defenses in Autonomous Agents: A Case Study of OpenClaw</t>
+          <t>Manipulating LLM Web Agents with Indirect Prompt Injection Attack via HTML Accessibility Tree</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -4940,7 +4960,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>execution</t>
+          <t>none</t>
         </is>
       </c>
       <c r="F67" s="5" t="n"/>
@@ -4948,7 +4968,7 @@
       <c r="H67" s="5" t="n"/>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>ec338413be097a8f6de120397411e86952c475ca</t>
+          <t>2b73f8dbb2af737fe707df3b2dcb21a9cea62db5</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4978,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Uncovering Security Threats and Architecting Defenses in Autonomous Agents: A Case Study of OpenClaw</t>
+          <t>Manipulating LLM Web Agents with Indirect Prompt Injection Attack via HTML Accessibility Tree</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -4981,7 +5001,7 @@
       <c r="H68" s="5" t="n"/>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>ec338413be097a8f6de120397411e86952c475ca</t>
+          <t>2b73f8dbb2af737fe707df3b2dcb21a9cea62db5</t>
         </is>
       </c>
     </row>
@@ -4991,7 +5011,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Uncovering Security Threats and Architecting Defenses in Autonomous Agents: A Case Study of OpenClaw</t>
+          <t>Manipulating LLM Web Agents with Indirect Prompt Injection Attack via HTML Accessibility Tree</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5014,7 +5034,7 @@
       <c r="H69" s="5" t="n"/>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>ec338413be097a8f6de120397411e86952c475ca</t>
+          <t>2b73f8dbb2af737fe707df3b2dcb21a9cea62db5</t>
         </is>
       </c>
     </row>
@@ -5024,7 +5044,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Uncovering Security Threats and Architecting Defenses in Autonomous Agents: A Case Study of OpenClaw</t>
+          <t>Manipulating LLM Web Agents with Indirect Prompt Injection Attack via HTML Accessibility Tree</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5039,7 +5059,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Code and dataset for Project ClawGuard (the paper's ongoing defense engineering initiative implementing the proposed FASA architecture) are publicly available at https://github.com/NY1024/ClawGuard, described as an early-stage/prototype release including primary security modules.</t>
+          <t>The system software (a Python library for generating IPI attacks) is released under the MIT License at https://github.com/sej2020/manipulating-web-agents, and an accompanying publicly available interactive demo website (http://lethaiq.github.io/attack-web-llm-agent) presents cached attack results on five real-world websites without requiring live model inference or full browser emulation. The Universal Website Targeted Instruction (login credential exfiltration) scenario is deliberately withheld from the public demo for ethical reasons.</t>
         </is>
       </c>
       <c r="F70" s="5" t="n"/>
@@ -5047,7 +5067,7 @@
       <c r="H70" s="5" t="n"/>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>ec338413be097a8f6de120397411e86952c475ca</t>
+          <t>2b73f8dbb2af737fe707df3b2dcb21a9cea62db5</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5077,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Uncovering Security Threats and Architecting Defenses in Autonomous Agents: A Case Study of OpenClaw</t>
+          <t>Manipulating LLM Web Agents with Indirect Prompt Injection Attack via HTML Accessibility Tree</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5072,7 +5092,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>No specific LLMs are benchmarked; this is a security case-study/systematization report on the OpenClaw agent framework (an open-source, self-hosted autonomous AI assistant, colloquially 'Lobster', built around a 'Pi Agent Runtime' reasoning engine) rather than a controlled empirical evaluation of particular LLM backbones. The vulnerabilities documented are framework/architecture-level and largely backbone-agnostic.</t>
+          <t>Meta's Llama-3.1-8B-Instruct as the primary target model for the Browser Gym web navigation agent. Transferability of TWUI-optimized triggers was additionally tested (unsuccessfully, without joint multi-model optimization) against Llama-2-7b-chat-hf and Mistral-7B-Instruct-v0.3.</t>
         </is>
       </c>
       <c r="F71" s="5" t="n"/>
@@ -5080,7 +5100,7 @@
       <c r="H71" s="5" t="n"/>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>ec338413be097a8f6de120397411e86952c475ca</t>
+          <t>2b73f8dbb2af737fe707df3b2dcb21a9cea62db5</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5110,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Uncovering Security Threats and Architecting Defenses in Autonomous Agents: A Case Study of OpenClaw</t>
+          <t>Manipulating LLM Web Agents with Indirect Prompt Injection Attack via HTML Accessibility Tree</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5105,7 +5125,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>No formal benchmark dataset is used. The paper instead synthesizes real-world, publicly documented incidents and vulnerability reports as its evidence base: a highlighted case of catastrophic autonomous failure (an OpenClaw agent deleting a user's entire email inbox due to context-window compression evicting a safety constraint), CVE-2026-25253 ('ClawJacked', a gateway authentication bypass leading to RCE), documented supply-chain/skill-marketplace poisoning incidents (malware embedded in ClawHub skills stealing SSH keys), and third-party security research (e.g., Snyk Labs' sandbox-bypass and credential-leak research) covering 280+ leaky skills exposing API keys and PII.</t>
+          <t>No pre-existing benchmark dataset is used; the authors construct their own evaluation sets from five real-world websites (chess.com, games.penjee.com binary-numbers-game, citybrewtours.com, norway.no/en/missions/un, translate.google.com) for Targeted-Website-Targeted-Instruction (TWTI) and Targeted-Website-Universal-Instruction (TWUI) scenarios, with 200 varied navigation-instruction prompts per website for TWUI attack-success testing. For the Universal-Website-Targeted-Instruction (UWTI) credential-exfiltration scenario, they construct copies of eight real-world login pages (forums/social media sites) for trigger training and eleven held-out login pages for evaluation.</t>
         </is>
       </c>
       <c r="F72" s="5" t="n"/>
@@ -5113,7 +5133,7 @@
       <c r="H72" s="5" t="n"/>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>ec338413be097a8f6de120397411e86952c475ca</t>
+          <t>2b73f8dbb2af737fe707df3b2dcb21a9cea62db5</t>
         </is>
       </c>
     </row>
@@ -5123,7 +5143,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Uncovering Security Threats and Architecting Defenses in Autonomous Agents: A Case Study of OpenClaw</t>
+          <t>Manipulating LLM Web Agents with Indirect Prompt Injection Attack via HTML Accessibility Tree</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5138,7 +5158,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>The paper's primary 'result' is a Tri-layered Risk Taxonomy (AI &amp; Cognitive Security, Software &amp; Execution Security, Information &amp; System Security) empirically grounded in real, documented OpenClaw vulnerabilities (Table 1), rather than a quantitative experimental finding. Concretely mapped vulnerabilities include: (1) AI/Cognitive layer -- 'Instruction Amnesia' (context-window compression silently evicted a user's safety constraint 'Do not delete any emails,' leading the agent to autonomously delete the user's entire inbox), indirect prompt injection via hidden HTML text during web-browsing tasks causing unintended local-file exfiltration, and 'Memory Pollution/Soft Backdoors' where malicious preferences injected via multi-turn conversation get permanently written into the agent's RAG vector database and silently trigger during unrelated future tasks; (2) Software/Execution layer -- complete absence of sandboxing/containerization (agents run with full host-user OS privileges), 'Sequential Tool Attack Chains' (STAC) where an attacker chains several individually-benign tools -- e.g., reading ~/.ssh/id_rsa, compressing it, and posting it via an HTTP tool -- to bypass single-endpoint security filters, and unaudited third-party 'Skills' marketplace (ClawHub) poisoning, where attackers uploaded malicious plugins turning user devices into botnets, with no static auditing or signature verification prior to deployment; (3) Information/System layer -- CVE-2026-25253 ('ClawJacked'), a real, publicly disclosed vulnerability where the WebSocket gateway's default exemption of the loopback address (127.0.0.1) from strict authentication allowed a malicious link, when clicked, to force the victim's browser to connect to an attacker-controlled gateway and transmit authentication tokens, enabling arbitrary remote code execution; and insecure state storage, where sensitive intermediate reasoning traces (including psychological user profiling and raw API keys) are stored in unencrypted local Markdown files or SQLite databases, with third-party research (Snyk Labs) documenting 280+ leaky skills exposing API keys and PII in practice.</t>
+          <t>In the TWUI setting (universal trigger per website, tested across 200 held-out navigation goals per site), attack success rate (ASR, response passes the syntactic filter and invokes the targeted computer-use function) was very high across all five sample websites, with the lowest ASR observed at 0.83 (city/citybrewtours.com); some sites (e.g., chess.com) showed notably higher ASR than the stricter ASRV metric (exact verbatim target sequence match), attributed mainly to benign quote-style discrepancies that Browser Gym still parsed successfully. In the UWTI credential-exfiltration setting, a single universal trigger induced information leakage (username and/or password) on seven of eight training-set login pages, and on three of eleven held-out test-set login pages, for a test-set ASR of 0.55. Standard GCG hyperparameters required roughly several hours per optimization run; using a smaller search width (128) kept average runtime under three hours, and including the target output string directly in the initial trigger sequence reduced optimization time to under an hour (sometimes under ten minutes), while trigger length and Carlini-Wagner loss versus cross-entropy loss showed no measurable effect on convergence speed. Failure analysis identified two dominant failure clusters: instructions with only one obvious correct action (high prior probability on the correct-action tokens overwhelmed the trigger), and cases where the model defaulted to chain-of-thought reasoning preambles ('To achieve the goal of...') instead of the target action, both linked to high baseline token priors that the optimized trigger could not fully override. Attempted trigger transfer to Llama-2-7b-chat-hf and Mistral-7B-Instruct-v0.3 (without joint multi-model optimization) was unsuccessful, indicating triggers optimized via single-model GCG are largely model-specific.</t>
         </is>
       </c>
       <c r="F73" s="5" t="n"/>
@@ -5146,7 +5166,7 @@
       <c r="H73" s="5" t="n"/>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>ec338413be097a8f6de120397411e86952c475ca</t>
+          <t>2b73f8dbb2af737fe707df3b2dcb21a9cea62db5</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5176,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Uncovering Security Threats and Architecting Defenses in Autonomous Agents: A Case Study of OpenClaw</t>
+          <t>Manipulating LLM Web Agents with Indirect Prompt Injection Attack via HTML Accessibility Tree</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5171,7 +5191,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>N/A -- this is a case-study/systematization and defense-blueprint paper rather than a comparative empirical evaluation; no attack or defense baselines are quantitatively benchmarked against each other. The paper does implicitly contrast its proposed zero-trust, full-lifecycle FASA defense philosophy against 'traditional' security measures (static Web Application Firewalls, basic input/content filtering, conventional LLM-centric text-filtering guardrails), arguing these are structurally inadequate for autonomous, tool-calling agents.</t>
+          <t>No defense mechanisms or competing attack methods are empirically benchmarked against; the paper's own three attack scenario variants (TWTI: per-website-per-instruction trigger; TWUI: universal trigger across many instructions for one website; UWTI: universal trigger across multiple websites/login pages for credential theft) serve as internally compared conditions, and GCG hyperparameter variants (search width, top-k token replacement candidates, Carlini-Wagner vs. cross-entropy loss, inclusion of target string in initial trigger) are compared against each other for optimization time-to-completion rather than against alternative attack algorithms.</t>
         </is>
       </c>
       <c r="F74" s="5" t="n"/>
@@ -5179,7 +5199,7 @@
       <c r="H74" s="5" t="n"/>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>ec338413be097a8f6de120397411e86952c475ca</t>
+          <t>2b73f8dbb2af737fe707df3b2dcb21a9cea62db5</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5209,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Uncovering Security Threats and Architecting Defenses in Autonomous Agents: A Case Study of OpenClaw</t>
+          <t>Manipulating LLM Web Agents with Indirect Prompt Injection Attack via HTML Accessibility Tree</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5204,7 +5224,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Formal, real-world-grounded threat characterization organized around OpenClaw's 'Security Paradox of Autonomy': the framework connects to real, public-facing messaging surfaces and continuously ingests untrusted internet content, while simultaneously holding OS-level execution privileges (shell command execution, file read/write, browser automation, and access to 20+ communication channels and native OS APIs including camera, screen recording, and location services on macOS/iOS/Android). The core threat model observes that because instructions and data are conflated within LLM context (unlike traditional software where code/data separation mitigates injection, e.g., SQL injection defenses), an attacker who can place adversarial text anywhere the agent will read it (a scraped webpage, a document, a multi-turn conversation, a marketplace-distributed 'Skill') can escalate what would traditionally be a content-generation risk into system-level compromise: arbitrary remote code execution, lateral network movement, credential/data exfiltration, or persistent 'soft backdoors' written into long-term memory. The threat model explicitly spans single-shot injection (one malicious instruction triggering one harmful action), toolchain composition attacks (multiple individually-benign tool calls chained into a malicious workflow, evading single-endpoint security filters), supply-chain attacks (malicious third-party plugins/skills distributed via an unaudited marketplace), and authentication-bypass attacks (network-level gateway exploitation, as in the documented ClawJacked CVE) -- treating the entire agent execution lifecycle, not just model output, as the attack surface.</t>
+          <t>The attacker's goal is to hijack an LLM-based web navigation agent's actions by embedding an adversarial trigger sequence into webpage HTML that the agent's accessibility-tree parser feeds into its prompt, without the end user noticing (stealth achieved via URL-hiding, transparent font, or CSS-based element hiding). The attacker's capability requirement is control over some portion of the HTML the navigation agent will consume -- e.g., a website owner, a third-party ad broker whose ad content is embedded on many sites, or an adversary exploiting user-generated content areas (comment sections, forum entries, profiles); the attacker does not need white-box access to the agent's LLM weights beyond what is needed to run GCG optimization against a copy of the (open-source) target model, and triggers are optimized offline via the Greedy Coordinate Gradient algorithm to be universal across many user instructions (TWUI) or across many websites for a fixed instruction type such as login-page credential theft (UWTI). Concrete attack goals demonstrated include forcing malicious ad clicks, redirecting to phishing/malware links, exfiltrating login credentials to an external party, and other unintended computer-use actions (clicks, tab closures, following social media accounts) contrary to the user's actual instruction; the threat model explicitly notes limitations that reduce attacker feasibility, including LLM-specificity of triggers and dependence on syntactic validity of the target action within the specific web agent framework.</t>
         </is>
       </c>
       <c r="F75" s="5" t="n"/>
@@ -5212,7 +5232,7 @@
       <c r="H75" s="5" t="n"/>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>ec338413be097a8f6de120397411e86952c475ca</t>
+          <t>2b73f8dbb2af737fe707df3b2dcb21a9cea62db5</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5242,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Uncovering Security Threats and Architecting Defenses in Autonomous Agents: A Case Study of OpenClaw</t>
+          <t>Manipulating LLM Web Agents with Indirect Prompt Injection Attack via HTML Accessibility Tree</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5237,7 +5257,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>The paper has no dedicated 'Limitations' section; it closes with a 'Conclusion' summarizing the tri-layered taxonomy and the proposed FASA defense blueprint without explicitly enumerating study weaknesses. The paper does implicitly acknowledge two significant caveats in its own narrative: first, that FASA is described throughout as a 'theoretical defense blueprint' rather than a validated, deployed system, and its concrete implementation (Project ClawGuard) is explicitly stated to be an 'ongoing engineering initiative' with only 'early prototypes' including 'primary security modules as a starting point' -- i.e., the proposed defenses are not yet empirically evaluated for effectiveness against the documented attacks; second, the evidence base for the vulnerability taxonomy consists of real-world, publicly reported incidents and third-party security research (news articles, CVE records, Snyk Labs reports) rather than the authors' own controlled, reproducible experiments, meaning severity/prevalence claims rely on external reporting rather than independently measured attack-success rates.</t>
+          <t>The paper has an explicit 'Limitations' section listing three practical constraints on the attack technique: (1) the attacker must have access to some part of the HTML consumed by the navigation agent; (2) triggers are trained for a particular LLM (or set of LLMs), so agents powered by other/untested LLMs are much less susceptible to a given trigger, as confirmed by the unsuccessful transfer attempts to Llama-2 and Mistral; and (3) triggers are optimized for a specific target output sequence, so they can only exploit a web navigation framework if that target sequence is syntactically valid within the framework's action space -- meaning a closed-source framework that rotates its action-space scheme and does not disclose its underlying LLM would be substantially more resistant to this attack. The paper notes this resistance is currently undermined in practice by the open-source ecosystem's broad adoption and low discretion around LLM-integrated application internals. The Conclusion additionally acknowledges that attack success 'depends on content control and model-specific tuning,' an implicit scope caveat beyond the formal Limitations section.</t>
         </is>
       </c>
       <c r="F76" s="5" t="n"/>
@@ -5245,7 +5265,7 @@
       <c r="H76" s="5" t="n"/>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>ec338413be097a8f6de120397411e86952c475ca</t>
+          <t>2b73f8dbb2af737fe707df3b2dcb21a9cea62db5</t>
         </is>
       </c>
     </row>
@@ -5255,7 +5275,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Uncovering Security Threats and Architecting Defenses in Autonomous Agents: A Case Study of OpenClaw</t>
+          <t>Manipulating LLM Web Agents with Indirect Prompt Injection Attack via HTML Accessibility Tree</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -5270,7 +5290,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>This paper is a security case-study and defense-architecture proposal centered on OpenClaw, a highly popular (200,000+ GitHub stars by February 2026), open-source, self-hosted autonomous AI agent framework that decouples LLM cognitive decision-making (via its 'Pi Agent Runtime') from tool execution across a decoupled, local-first architecture (a WebSocket-based 'Gateway' control plane, omni-channel messaging integration across 20+ platforms, cross-platform native OS nodes with device-level API access, and a browser-automation/skills-plugin ecosystem via ClawHub). The authors argue that granting an LLM direct operating-system-level permissions fundamentally reconstructs the security perimeter of AI systems: whereas conventional LLMs face content-centric risks (hallucination, toxic text), tool-calling agents like OpenClaw inherit these same underlying vulnerabilities (principally the conflation of instructions and data within LLM context, since instructions cannot be cleanly separated from data the way SQL injection defenses separate code from data) but amplify them into system-level compromise -- a single successful prompt injection can trigger unauthorized remote code execution, arbitrary file deletion, or data exfiltration rather than merely a bad chat response. Grounded in a series of real, publicly documented OpenClaw incidents and disclosed vulnerabilities (context-compression-induced catastrophic data loss, indirect prompt injection via hidden webpage text, memory-pollution 'soft backdoors' persisted in a RAG vector database, unsandboxed full-host-privilege execution, sequential multi-tool attack chains, unaudited third-party plugin/supply-chain poisoning on the ClawHub marketplace, and a real disclosed CVE for a gateway-authentication-bypass RCE), the paper proposes a Tri-layered Risk Taxonomy for autonomous agents spanning AI &amp; Cognitive Security, Software &amp; Execution Security, and Information &amp; System Security, mapping each empirically observed OpenClaw vulnerability to its corresponding theoretical risk category (Table 1). Building on this taxonomy, the paper proposes the Full-Lifecycle Agent Security Architecture (FASA), a theoretical zero-trust defense blueprint spanning four sequential layers covering the entire agent execution lifecycle: Perception and Isolation (input sanitization stripping executable content from untrusted external data before it enters the LLM's reasoning context), Cognitive Guardrails (behavioral intent analysis decomposing complex execution plans into atomic actions to detect collectively-malicious tool sequences, plus agent-to-agent protocol inspection in multi-agent settings), Execution and Response (a cross-layer 'reasoning-action correlation' mechanism that flags mismatches between the LLM's inferred semantic intent and its actual system-level behavior, backed by kernel-level OS telemetry and automated containment such as process termination), and Governance and Evolution (continuous threat-intelligence integration and adaptive adversarial red-teaming to keep detection/mitigation strategies current against emerging attack patterns). The paper concludes by introducing Project ClawGuard, the authors' ongoing open-source engineering effort to implement the FASA paradigm as a concrete security platform for the OpenClaw ecosystem, explicitly framed as early-stage and still in development.</t>
+          <t>The paper demonstrates a concrete, practical Indirect Prompt Injection (IPI) attack against LLM-based web navigation agents by embedding optimized adversarial trigger sequences directly into webpage HTML, exploiting the fact that agent frameworks like Browser Gym parse the page's accessibility tree (HTML rendered for readability) into the LLM's prompt alongside the user's task instruction and available action space. Building on the Greedy Coordinate Gradient (GCG) algorithm originally used to induce objectionable outputs from safety-aligned LLMs, the authors adapt trigger optimization to the IPI setting by allowing flexible trigger placement within the HTML portion of the prompt (rather than only as a suffix, since an HTML-only attacker cannot control the full prompt) and by extending the objective to universal optimization across multiple prompt contexts, i.e., minimizing negative log-probability of a fixed target action-response across n different (xpre, xpost) context pairs drawn from different user instructions or different websites, using a NanoGCG-based implementation modified for this multi-context universal-trigger setting. Using Meta's Llama-3.1-8B-Instruct as the target LLM within a Browser Gym web-navigation agent, the authors demonstrate three escalating attack scenarios on real websites: Targeted-Website-Targeted-Instruction (a single trigger for one website/instruction pair, e.g., forcing chess.com's agent to report a fabricated cheating violation, forcing clicks on ad banners or hidden blog links, or forcing a Twitter-follow action), Targeted-Website-Universal-Instruction (one trigger per website that reliably induces the target action regardless of the user's specific navigation goal, tested against 200 varied instructions per site), and Universal-Website-Targeted-Instruction (a single trigger effective across multiple different websites for a fixed high-value goal, specifically credential exfiltration from login pages via a simulated malicious browser-extension modal). Optimization typically completes within several hours under standard GCG hyperparameters, with search-width reduction and target-string-seeded initialization identified empirically as the most effective speedup techniques (reducing completion time to under an hour in many cases), while trigger length and Carlini-Wagner loss showed no measurable speed benefit. The work provides concrete evidence that current LLM-based web agents lack robust defenses against HTML-embedded prompt injection and argues for stronger safeguards such as input sanitization and prompt hardening as agent deployment scales, while responsibly withholding the most sensitive credential-theft demonstration from the public-facing demo.</t>
         </is>
       </c>
       <c r="F77" s="5" t="n"/>
@@ -5278,7 +5298,7 @@
       <c r="H77" s="5" t="n"/>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>ec338413be097a8f6de120397411e86952c475ca</t>
+          <t>2b73f8dbb2af737fe707df3b2dcb21a9cea62db5</t>
         </is>
       </c>
     </row>
@@ -5288,7 +5308,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Agent Skills in the Wild: An Empirical Study of Security Vulnerabilities at Scale</t>
+          <t>Context Cartography: Toward Structured Governance of Contextual Space in Large Language Model Systems</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -5311,7 +5331,7 @@
       <c r="H78" s="5" t="n"/>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>017083cfa88785e0a5dbddf6b5027caa281bc881</t>
+          <t>arxiv:2603.20578</t>
         </is>
       </c>
     </row>
@@ -5321,7 +5341,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Agent Skills in the Wild: An Empirical Study of Security Vulnerabilities at Scale</t>
+          <t>Context Cartography: Toward Structured Governance of Contextual Space in Large Language Model Systems</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -5336,7 +5356,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>ML/AI</t>
         </is>
       </c>
       <c r="F79" s="5" t="n"/>
@@ -5344,7 +5364,7 @@
       <c r="H79" s="5" t="n"/>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>017083cfa88785e0a5dbddf6b5027caa281bc881</t>
+          <t>arxiv:2603.20578</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5374,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Agent Skills in the Wild: An Empirical Study of Security Vulnerabilities at Scale</t>
+          <t>Context Cartography: Toward Structured Governance of Contextual Space in Large Language Model Systems</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -5377,7 +5397,7 @@
       <c r="H80" s="5" t="n"/>
       <c r="I80" s="5" t="inlineStr">
         <is>
-          <t>017083cfa88785e0a5dbddf6b5027caa281bc881</t>
+          <t>arxiv:2603.20578</t>
         </is>
       </c>
     </row>
@@ -5387,7 +5407,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Agent Skills in the Wild: An Empirical Study of Security Vulnerabilities at Scale</t>
+          <t>Context Cartography: Toward Structured Governance of Contextual Space in Large Language Model Systems</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -5402,7 +5422,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>defense</t>
+          <t>neither</t>
         </is>
       </c>
       <c r="F81" s="5" t="n"/>
@@ -5410,7 +5430,7 @@
       <c r="H81" s="5" t="n"/>
       <c r="I81" s="5" t="inlineStr">
         <is>
-          <t>017083cfa88785e0a5dbddf6b5027caa281bc881</t>
+          <t>arxiv:2603.20578</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5440,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Agent Skills in the Wild: An Empirical Study of Security Vulnerabilities at Scale</t>
+          <t>Context Cartography: Toward Structured Governance of Contextual Space in Large Language Model Systems</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -5435,7 +5455,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>skill</t>
+          <t>direct-input</t>
         </is>
       </c>
       <c r="F82" s="5" t="n"/>
@@ -5443,7 +5463,7 @@
       <c r="H82" s="5" t="n"/>
       <c r="I82" s="5" t="inlineStr">
         <is>
-          <t>017083cfa88785e0a5dbddf6b5027caa281bc881</t>
+          <t>arxiv:2603.20578</t>
         </is>
       </c>
     </row>
@@ -5453,7 +5473,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Agent Skills in the Wild: An Empirical Study of Security Vulnerabilities at Scale</t>
+          <t>Context Cartography: Toward Structured Governance of Contextual Space in Large Language Model Systems</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -5468,7 +5488,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>goal-hijack</t>
+          <t>reasoning-corruption</t>
         </is>
       </c>
       <c r="F83" s="5" t="n"/>
@@ -5476,7 +5496,7 @@
       <c r="H83" s="5" t="n"/>
       <c r="I83" s="5" t="inlineStr">
         <is>
-          <t>017083cfa88785e0a5dbddf6b5027caa281bc881</t>
+          <t>arxiv:2603.20578</t>
         </is>
       </c>
     </row>
@@ -5486,7 +5506,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Agent Skills in the Wild: An Empirical Study of Security Vulnerabilities at Scale</t>
+          <t>Context Cartography: Toward Structured Governance of Contextual Space in Large Language Model Systems</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -5509,7 +5529,7 @@
       <c r="H84" s="5" t="n"/>
       <c r="I84" s="5" t="inlineStr">
         <is>
-          <t>017083cfa88785e0a5dbddf6b5027caa281bc881</t>
+          <t>arxiv:2603.20578</t>
         </is>
       </c>
     </row>
@@ -5519,7 +5539,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Agent Skills in the Wild: An Empirical Study of Security Vulnerabilities at Scale</t>
+          <t>Context Cartography: Toward Structured Governance of Contextual Space in Large Language Model Systems</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -5534,7 +5554,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F85" s="5" t="n"/>
@@ -5542,7 +5562,7 @@
       <c r="H85" s="5" t="n"/>
       <c r="I85" s="5" t="inlineStr">
         <is>
-          <t>017083cfa88785e0a5dbddf6b5027caa281bc881</t>
+          <t>arxiv:2603.20578</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5572,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Agent Skills in the Wild: An Empirical Study of Security Vulnerabilities at Scale</t>
+          <t>Context Cartography: Toward Structured Governance of Contextual Space in Large Language Model Systems</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -5567,7 +5587,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>reasoning</t>
         </is>
       </c>
       <c r="F86" s="5" t="n"/>
@@ -5575,7 +5595,7 @@
       <c r="H86" s="5" t="n"/>
       <c r="I86" s="5" t="inlineStr">
         <is>
-          <t>017083cfa88785e0a5dbddf6b5027caa281bc881</t>
+          <t>arxiv:2603.20578</t>
         </is>
       </c>
     </row>
@@ -5585,7 +5605,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Agent Skills in the Wild: An Empirical Study of Security Vulnerabilities at Scale</t>
+          <t>Context Cartography: Toward Structured Governance of Contextual Space in Large Language Model Systems</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -5600,7 +5620,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>one-shot</t>
+          <t>session-persistent</t>
         </is>
       </c>
       <c r="F87" s="5" t="n"/>
@@ -5608,7 +5628,7 @@
       <c r="H87" s="5" t="n"/>
       <c r="I87" s="5" t="inlineStr">
         <is>
-          <t>017083cfa88785e0a5dbddf6b5027caa281bc881</t>
+          <t>arxiv:2603.20578</t>
         </is>
       </c>
     </row>
@@ -5618,7 +5638,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Agent Skills in the Wild: An Empirical Study of Security Vulnerabilities at Scale</t>
+          <t>Context Cartography: Toward Structured Governance of Contextual Space in Large Language Model Systems</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -5641,7 +5661,7 @@
       <c r="H88" s="5" t="n"/>
       <c r="I88" s="5" t="inlineStr">
         <is>
-          <t>017083cfa88785e0a5dbddf6b5027caa281bc881</t>
+          <t>arxiv:2603.20578</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5671,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Agent Skills in the Wild: An Empirical Study of Security Vulnerabilities at Scale</t>
+          <t>Context Cartography: Toward Structured Governance of Contextual Space in Large Language Model Systems</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -5666,7 +5686,7 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Y — the authors release an annotated dataset of 31,132 labeled agent skills, their collection pipeline, and their SkillScan detection toolkit, hosted at an anonymized repository (https://anonymous.4open.science/r/skillscan/ per the reference list). Precautions are applied to the release: potentially harmful code snippets are redacted/anonymized, repository URLs for clearly malicious skills are withheld, only detection signatures (not complete exploit code) are provided, and in-paper examples are synthesized to illustrate patterns without working exploits.</t>
+          <t>No code, dataset, or software artifact is released by the authors; this is a theoretical/conceptual framework paper. It proposes (but does not yet implement or release) a diagnostic 'CCD' (Context Cartography Diagnostic) benchmark for future community implementation and evaluation. It cites third-party open-source systems analyzed as case studies (e.g., OpenViking at https://github.com/volcengine/OpenViking) but does not release any artifact of its own.</t>
         </is>
       </c>
       <c r="F89" s="5" t="n"/>
@@ -5674,7 +5694,7 @@
       <c r="H89" s="5" t="n"/>
       <c r="I89" s="5" t="inlineStr">
         <is>
-          <t>017083cfa88785e0a5dbddf6b5027caa281bc881</t>
+          <t>arxiv:2603.20578</t>
         </is>
       </c>
     </row>
@@ -5684,7 +5704,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Agent Skills in the Wild: An Empirical Study of Security Vulnerabilities at Scale</t>
+          <t>Context Cartography: Toward Structured Governance of Contextual Space in Large Language Model Systems</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5699,7 +5719,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Claude 3.5 Sonnet (temperature 0, structured JSON output) is used as the LLM component of SkillScan's hybrid classification stage to semantically classify candidate-flagged skills; the paper is not evaluating general-purpose LLMs as agents but using one LLM as part of its own detection pipeline. LLM-Guard (v0.3.14, an open-source scanner library, not itself an LLM) provides 10 chained specialized scanners (PromptInjection, Secrets, Gibberish, InvisibleText, Sentiment, Toxicity, BanSubstrings, BanTopics, Code, Regex) as a second detection layer.</t>
+          <t>N/A - this is a theoretical framework paper, not a paper that trains or benchmarks LLMs directly. It analyzes four existing production/research agent memory systems as case studies rather than evaluating specific base LLMs: Claude Code (Anthropic), Letta/MemGPT, MemOS, and OpenViking (Volcengine). Where systems self-report empirical results (e.g., MemOS's 159% gain in temporal reasoning and 60.95% token reduction on the LoCoMo benchmark), these are cited as secondary evidence rather than reproduced by the authors.</t>
         </is>
       </c>
       <c r="F90" s="5" t="n"/>
@@ -5707,7 +5727,7 @@
       <c r="H90" s="5" t="n"/>
       <c r="I90" s="5" t="inlineStr">
         <is>
-          <t>017083cfa88785e0a5dbddf6b5027caa281bc881</t>
+          <t>arxiv:2603.20578</t>
         </is>
       </c>
     </row>
@@ -5717,7 +5737,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Agent Skills in the Wild: An Empirical Study of Security Vulnerabilities at Scale</t>
+          <t>Context Cartography: Toward Structured Governance of Contextual Space in Large Language Model Systems</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -5732,7 +5752,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>The paper's own newly constructed dataset: 42,447 agent skills crawled from two marketplaces (skills.rest: 27,365 skills/35,124 scripts; skillsmp.com: 15,082 skills/19,856 scripts) in December 2025, filtered/deduplicated down to 31,132 unique skills with 3,574 associated scripts, spanning 8 functional categories (Development Tools 31.8%, External Integrations 19.2%, System Admin, Data Analysis, Security/Red-team, Documentation, Communication, Other). A categorized sample of 1,218 skills was manually/automatically labeled for category-level analysis (89.2% agreement with manual labels, kappa=0.86). Ground truth for detection validation: 200 stratified, manually annotated skills (63 vulnerable), with taxonomy development on a separate 500-skill sample and rule calibration on a separate 300-skill sample (strict temporal/non-overlapping separation across all three samples).</t>
+          <t>No benchmark evaluation is conducted by the authors; the paper instead proposes a not-yet-implemented diagnostic benchmark ('CCD') with task categories designed to isolate individual cartographic operators and zone transitions, explicitly contrasted with general-purpose long-context benchmarks. The paper's empirical grounding consists of a structured cross-system analysis (Table 5) scoring four existing systems (Claude Code, Letta, MemOS, OpenViking) against seven cartographic operators using five binary criteria (Present, Explicit, Configurable, Automated, Documented) per operator-system pair, plus citation of self-reported third-party results (e.g., MemOS's reported performance on the LoCoMo benchmark).</t>
         </is>
       </c>
       <c r="F91" s="5" t="n"/>
@@ -5740,7 +5760,7 @@
       <c r="H91" s="5" t="n"/>
       <c r="I91" s="5" t="inlineStr">
         <is>
-          <t>017083cfa88785e0a5dbddf6b5027caa281bc881</t>
+          <t>arxiv:2603.20578</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5770,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Agent Skills in the Wild: An Empirical Study of Security Vulnerabilities at Scale</t>
+          <t>Context Cartography: Toward Structured Governance of Contextual Space in Large Language Model Systems</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -5765,7 +5785,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>26.1% of the 31,132 analyzed skills (8,126 skills) contain at least one flagged vulnerability across 14 patterns in 4 categories; adjusted for classifier imperfection via Rogan-Gladen correction, the estimated true prevalence is 23-30% (point estimate 26.5%/26.1%). By severity: 5.2% exhibit high-severity patterns (likely malicious intent), 8.1% medium-severity, 12.8% only low-severity (likely negligent practices). By category, data exfiltration (13.3%) and privilege escalation (11.8%) are most prevalent; prompt injection is rarest (0.7%). SkillScan achieves 86.7% precision and 82.5% recall (F1 84.6%) against the 200-skill manually annotated ground truth (static patterns alone: 71.4% precision/91.2% recall; hybrid LLM classification raises precision to 86.7% at a recall cost of 82.5%). Skills bundling executable scripts are 2.12x more likely to be vulnerable than instruction-only skills (40.6% vs. 24.2% vulnerability rate, OR=2.12, p&lt;0.001); larger skills (&gt;500 lines) are 2.14x more likely to be vulnerable (OR=2.14, 95% CI 1.62-2.83, p&lt;0.01); skills with 5+ external dependencies show 47.9% vulnerability rates vs. 36.8% for fewer dependencies. Security/Red-team skills show the highest raw vulnerability rate (67.4%), but manual review of 60 flagged skills found only 31.7% showed actual vulnerability indicators (rest were legitimate security tooling), yielding an adjusted rate of 21.4% for that category. A pilot dynamic-validation test on 25 high-confidence flagged skills confirmed 72% exhibited exploitable behavior. Active maintenance recency (commit within 90 days) showed no significant association with vulnerability presence (p=0.47, OR=0.91), a notable negative finding.</t>
+          <t>The paper's central empirical contribution is a cross-system operator-coverage analysis (Table 5) scoring four production/research memory systems against seven formally defined cartographic operators on a 0-5 implementation-depth scale (Present/Explicit/Configurable/Automated/Documented). Layering (compartmentalizing distinct memory stores) is the most universally and deeply implemented operator across all four systems (mean 5.00/5, full implementation in every system), while Displacement (relocating information between zones) is the least implemented (mean 1.25/5). Projection (re-rendering stored memory at different resolutions/summarization levels) is strongly implemented in Letta, MemOS, and OpenViking (scores of 5) but comparatively weak in Claude Code (score 2), while conversely Claude Code strongly implements Reconnaissance/exploration governance (score 5) where the other three systems score only 1, revealing that systems bifurcate along a projection-governance versus exploration-governance axis (Letta bridges both). System-level mean coverage across all seven operators is fairly similar across the four systems (ranging 2.71-3.29 out of 5), suggesting no single system has yet achieved comprehensive cartographic governance. The authors interpret this pattern of partial, non-overlapping operator coverage across independently developed systems as evidence that these seven operators are converging independently across the industry as architecturally necessary compensations for transformer limitations (linear prefix memory, append-only state, entropy accumulation) rather than arbitrary design choices, even though no single system implements the full operator set explicitly and configurably.</t>
         </is>
       </c>
       <c r="F92" s="5" t="n"/>
@@ -5773,7 +5793,7 @@
       <c r="H92" s="5" t="n"/>
       <c r="I92" s="5" t="inlineStr">
         <is>
-          <t>017083cfa88785e0a5dbddf6b5027caa281bc881</t>
+          <t>arxiv:2603.20578</t>
         </is>
       </c>
     </row>
@@ -5783,7 +5803,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Agent Skills in the Wild: An Empirical Study of Security Vulnerabilities at Scale</t>
+          <t>Context Cartography: Toward Structured Governance of Contextual Space in Large Language Model Systems</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -5798,7 +5818,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>SkillScan's own pipeline stages are compared against each other as ablation-style baselines: static pattern matching alone (71.4% precision/91.2% recall) vs. the full hybrid static+LLM-Guard+LLM-classification pipeline (86.7%/82.5%). The paper also notes that general-purpose static analysis tools (Semgrep, Bandit) achieve 'near-zero recall' on instruction-level threats in a preliminary comparison, motivating the custom skill-security-scan tool built for this study. Detection-stage overlap analysis (static scanner vs. LLM-Guard: only 1.0% overlap) is used to justify the union-based candidate-selection design rather than as a competing baseline.</t>
+          <t>N/A - this is a theoretical framework paper with no experimental baselines in the conventional sense; the paper's comparative structure is the four case-study systems (Claude Code, Letta, MemOS, OpenViking) scored against each other and against the paper's proposed seven-operator taxonomy, rather than a machine-learning baseline comparison.</t>
         </is>
       </c>
       <c r="F93" s="5" t="n"/>
@@ -5806,7 +5826,7 @@
       <c r="H93" s="5" t="n"/>
       <c r="I93" s="5" t="inlineStr">
         <is>
-          <t>017083cfa88785e0a5dbddf6b5027caa281bc881</t>
+          <t>arxiv:2603.20578</t>
         </is>
       </c>
     </row>
@@ -5816,7 +5836,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Agent Skills in the Wild: An Empirical Study of Security Vulnerabilities at Scale</t>
+          <t>Context Cartography: Toward Structured Governance of Contextual Space in Large Language Model Systems</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -5831,7 +5851,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>This is a security/measurement paper with an explicit threat model (Section 2.2, illustrated in Figure 2). The authors identify three adversary categories: (1) Malicious Authors who intentionally publish skills designed to exfiltrate data, establish persistence, or manipulate agent behavior, potentially via natural-language instructions that bypass code-level detection; (2) Supply Chain Attackers who compromise previously benign skills through account takeover, dependency confusion, or repository hijacking; and (3) Negligent Developers who unintentionally introduce vulnerabilities through insecure coding, excessive permission requests, or unsafe instruction patterns. All three exploit a common 'consent gap': once a user approves a skill, it gains persistent permissions (file read/write, code download, network access) without further per-action prompts, and users cannot meaningfully audit bundled code and natural-language instructions before granting trust. The paper scopes itself to vulnerabilities introduced by skill content (instructions and bundled code) under an assumed-trusted runtime, explicitly excluding attacks on the underlying LLM itself, side channels, and physical access.</t>
+          <t>N/A - non-adversarial (this is a conceptual/architectural framework paper about context management and memory governance in LLM agent systems, not a security paper). The incidental phenomena of interest are structural, non-adversarial degradation effects in transformer context handling: the 'lost in the middle' effect (performance degradation when critical information occupies intermediate context positions), long-distance relational knowledge degradation as token distance increases, and effective context utilization falling short of stated model capacity -- framed as inherent structural gradients, salience asymmetries, and entropy accumulation in transformer attention rather than as attacker-induced failures.</t>
         </is>
       </c>
       <c r="F94" s="5" t="n"/>
@@ -5839,7 +5859,7 @@
       <c r="H94" s="5" t="n"/>
       <c r="I94" s="5" t="inlineStr">
         <is>
-          <t>017083cfa88785e0a5dbddf6b5027caa281bc881</t>
+          <t>arxiv:2603.20578</t>
         </is>
       </c>
     </row>
@@ -5849,7 +5869,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Agent Skills in the Wild: An Empirical Study of Security Vulnerabilities at Scale</t>
+          <t>Context Cartography: Toward Structured Governance of Contextual Space in Large Language Model Systems</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -5864,7 +5884,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>The paper has an explicit 'Limitations' subsection within the Discussion section. Key limitations stated: (1) the 26.1% headline prevalence figure conflates intentional malice, negligent practices, and ambiguous patterns, so it should be interpreted as 'patterns warranting review' rather than 'confirmed malicious skills'; (2) the detection framework's 86.7% precision/82.5% recall implies false positives (from legitimate security tools accessing sensitive resources by design) and false negatives (from obfuscation techniques like dynamic URL construction, natural-language obfuscation, and delayed/conditional execution) documented via explicit error analysis (n=11 false negatives, n=8 false positives); (3) only a pilot dynamic-validation test was run on 25 high-confidence skills (72% confirmed exploitable) — full runtime/dynamic analysis across the entire dataset remains future work; (4) the hybrid LLM classifier exhibits non-determinism (5.5% run-to-run variance, 9.0% prompt-variant variance), so the authors recommend production deployments prioritize static patterns for reproducibility; (5) the December 2025 snapshot represents an early-stage, unvetted ecosystem and may not generalize to enterprise deployments or the ecosystem's future steady state; (6) survivorship/exclusion bias — 17.3% of initially crawled skills had been deleted (404 errors) before analysis and were disproportionately likely to include malicious content already removed by platforms or users, meaning the reported prevalence may undercount the true attack surface at collection time. The paper explicitly flags these as motivating future work: dynamic analysis to confirm exploitability, longitudinal studies tracking ecosystem evolution, and user studies on trust assessment. Additional scope limitations (multi-tenant interactions, skill chaining, dual-use tools) are noted as discussed in Appendix B (not captured in this extraction).</t>
+          <t>Explicit Section 7 'Limitations' identifying six points: (1) the framework is primarily interpretive rather than a full mathematical theory -- cartographic operators are derived from cartographic generalization theory with only a partial distinction between structural isomorphisms and functional analogies; (2) the four-system case study analysis (Section 4) is post-hoc, since the operators were partly informed by observing these systems, making the 'independent convergence' finding interpretive rather than predictive; (3) additional cartographic operators (e.g., symbolization, rotation) may have unidentified context analogues beyond the seven derived, and the zone-general scope of some operators may need finer distinctions as evidence accumulates; (4) the research agenda derives testable predictions but does not empirically validate them -- the proposed CCD diagnostic benchmark requires future community implementation and evaluation; (5) the zonal model is defined only for a single agent, and while a multi-agent extension identifies failure modes and architectural responses, it does not formally extend the core zone definitions or operator signatures to federated/multi-agent settings; (6) extending cartographic theory from geographic (continuous, low-dimensional) to contextual (sequential, high-dimensional) space introduces representational differences whose full transferability -- and whether the proposed invariant triad (semantic, structural, salience) fully characterizes contextual distortion -- requires further investigation.</t>
         </is>
       </c>
       <c r="F95" s="5" t="n"/>
@@ -5872,7 +5892,7 @@
       <c r="H95" s="5" t="n"/>
       <c r="I95" s="5" t="inlineStr">
         <is>
-          <t>017083cfa88785e0a5dbddf6b5027caa281bc881</t>
+          <t>arxiv:2603.20578</t>
         </is>
       </c>
     </row>
@@ -5882,7 +5902,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Agent Skills in the Wild: An Empirical Study of Security Vulnerabilities at Scale</t>
+          <t>Context Cartography: Toward Structured Governance of Contextual Space in Large Language Model Systems</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -5897,7 +5917,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>This paper presents the first large-scale empirical security analysis of 'agent skills' — modular packages (a SKILL.md instruction/metadata file plus optional bundled scripts) that let AI agent frameworks like Claude Code, Codex CLI, and Gemini CLI dynamically extend their capabilities via progressive disclosure. The authors built an automated crawling pipeline that collected 42,447 skills from two major community marketplaces (skills.rest and skillsmp.com), which after deduplication and quality filtering yielded 31,132 unique skills with 3,574 bundled scripts. To detect vulnerabilities at this scale, they developed SkillScan, a multi-stage hybrid detection framework: (1) a custom static security scanner (built because general tools like Semgrep/Bandit lack patterns for agent-specific threats) that applies regex/keyword matching over both SKILL.md instructions and bundled code to flag dangerous patterns; (2) LLM-Guard, an off-the-shelf library of 10 chained input scanners catching prompt injection, secrets, obfuscation, and other semantic red flags; and (3) a hybrid LLM classification stage using Claude 3.5 Sonnet with structured JSON output to adjudicate candidate findings from stages 1-2 with a confidence score, using an asymmetric, security-conservative aggregation rule that requires higher confidence to overturn a static finding than to confirm one. Through iterative open coding on temporally-separated development/calibration/validation samples (500/300/200 skills respectively, with strict non-overlap to avoid circularity), the authors derive a grounded taxonomy of 14 vulnerability patterns across four categories — prompt injection (4 patterns), data exfiltration (4 patterns), privilege escalation (3 patterns), and supply chain risks (3 patterns) — each assigned a deterministic severity tier (high/medium/low) based on attack potential. Applying SkillScan across the full 31,132-skill dataset, they find 26.1% of skills flagged as vulnerable (with statistical corrections for classifier imperfection yielding a 23-30% true-prevalence range), identify script-bundling and skill size as strong statistically-significant predictors of vulnerability via odds-ratio analysis, and present three real-world case studies (a cloud-backup skill with credential exfiltration, a code-review skill with hidden prompt-injection instructions, and a dependency manager with multi-vector supply-chain risks) illustrating how these patterns manifest and gain user adoption before detection. The paper frames the agent skills ecosystem as recapitulating the early, under-vetted browser-extension landscape and argues for platform-level mandatory security review, capability-based permission manifests, and runtime sandboxing before this attack surface is further exploited; findings were responsibly disclosed to platform maintainers prior to publication, with over a hundred flagged skills subsequently removed.</t>
+          <t>This paper introduces Context Cartography, a formal conceptual framework for the deliberate governance of contextual space in large language model systems, arguing against the prevailing assumption that expanding context windows alone improves reasoning, given documented empirical phenomena like the 'lost in the middle' effect and long-distance relational degradation. The framework extends cartographic generalization theory (traditionally used for geographic map-making) to LLM context management, treating context not as a passive transcript to be extended but as structured 'terrain' with boundaries, gradients, and transitions requiring deliberate governance. Its core contribution is a tripartite zonal model of contextual space -- analogous to 'fog of war' in strategy games -- partitioning information into black fog (unobserved), gray fog (stored memory), and the visible field (active reasoning surface), with explicit state transitions and failure modes between zones. Building on this, the authors formalize seven cartographic operators derived from a systematic coverage analysis of all non-trivial zone transformations: reconnaissance, selection, simplification, aggregation, projection, displacement, and layering, each characterized as an architecturally necessary compensation for transformer limitations including linear prefix memory, append-only state accumulation, and entropy growth under expanding context. The framework is grounded empirically (in an interpretive, non-experimental sense) through a structured comparative analysis of four contemporary agent memory systems -- Claude Code, Letta (MemGPT), MemOS, and OpenViking -- scoring each system's implementation depth of each operator along five binary criteria (present, explicit, configurable, automated, documented), finding that these independently-developed industry systems exhibit convergent but only partially overlapping coverage of the same seven operators, interpreted as evidence that this operator taxonomy captures architecturally necessary rather than arbitrary design patterns. The paper further discusses multi-agent extensions of the zonal model and concludes by proposing a not-yet-implemented diagnostic benchmark (CCD) and a set of operator-specific ablation hypotheses as a research agenda for future empirical validation of the framework's testable predictions.</t>
         </is>
       </c>
       <c r="F96" s="5" t="n"/>
@@ -5905,7 +5925,7 @@
       <c r="H96" s="5" t="n"/>
       <c r="I96" s="5" t="inlineStr">
         <is>
-          <t>017083cfa88785e0a5dbddf6b5027caa281bc881</t>
+          <t>arxiv:2603.20578</t>
         </is>
       </c>
     </row>
@@ -5915,7 +5935,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Overcoming the Retrieval Barrier: Indirect Prompt Injection in the Wild for LLM Systems</t>
+          <t>Bridging AI and Software Security: A Comparative Vulnerability Assessment of LLM Agent Deployment Paradigms</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -5938,7 +5958,7 @@
       <c r="H97" s="5" t="n"/>
       <c r="I97" s="5" t="inlineStr">
         <is>
-          <t>81eb760ebbe224ae52cd7aea8f7f2865e4134908</t>
+          <t>3037549015be6f15d4f1ec59b34554b9238ac0c3</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5968,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Overcoming the Retrieval Barrier: Indirect Prompt Injection in the Wild for LLM Systems</t>
+          <t>Bridging AI and Software Security: A Comparative Vulnerability Assessment of LLM Agent Deployment Paradigms</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -5971,7 +5991,7 @@
       <c r="H98" s="5" t="n"/>
       <c r="I98" s="5" t="inlineStr">
         <is>
-          <t>81eb760ebbe224ae52cd7aea8f7f2865e4134908</t>
+          <t>3037549015be6f15d4f1ec59b34554b9238ac0c3</t>
         </is>
       </c>
     </row>
@@ -5981,7 +6001,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Overcoming the Retrieval Barrier: Indirect Prompt Injection in the Wild for LLM Systems</t>
+          <t>Bridging AI and Software Security: A Comparative Vulnerability Assessment of LLM Agent Deployment Paradigms</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -6004,7 +6024,7 @@
       <c r="H99" s="5" t="n"/>
       <c r="I99" s="5" t="inlineStr">
         <is>
-          <t>81eb760ebbe224ae52cd7aea8f7f2865e4134908</t>
+          <t>3037549015be6f15d4f1ec59b34554b9238ac0c3</t>
         </is>
       </c>
     </row>
@@ -6014,7 +6034,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Overcoming the Retrieval Barrier: Indirect Prompt Injection in the Wild for LLM Systems</t>
+          <t>Bridging AI and Software Security: A Comparative Vulnerability Assessment of LLM Agent Deployment Paradigms</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -6029,7 +6049,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>attack</t>
+          <t>neither</t>
         </is>
       </c>
       <c r="F100" s="5" t="n"/>
@@ -6037,7 +6057,7 @@
       <c r="H100" s="5" t="n"/>
       <c r="I100" s="5" t="inlineStr">
         <is>
-          <t>81eb760ebbe224ae52cd7aea8f7f2865e4134908</t>
+          <t>3037549015be6f15d4f1ec59b34554b9238ac0c3</t>
         </is>
       </c>
     </row>
@@ -6047,7 +6067,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Overcoming the Retrieval Barrier: Indirect Prompt Injection in the Wild for LLM Systems</t>
+          <t>Bridging AI and Software Security: A Comparative Vulnerability Assessment of LLM Agent Deployment Paradigms</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -6062,7 +6082,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>RAG</t>
+          <t>tool-output</t>
         </is>
       </c>
       <c r="F101" s="5" t="n"/>
@@ -6070,7 +6090,7 @@
       <c r="H101" s="5" t="n"/>
       <c r="I101" s="5" t="inlineStr">
         <is>
-          <t>81eb760ebbe224ae52cd7aea8f7f2865e4134908</t>
+          <t>3037549015be6f15d4f1ec59b34554b9238ac0c3</t>
         </is>
       </c>
     </row>
@@ -6080,7 +6100,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Overcoming the Retrieval Barrier: Indirect Prompt Injection in the Wild for LLM Systems</t>
+          <t>Bridging AI and Software Security: A Comparative Vulnerability Assessment of LLM Agent Deployment Paradigms</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -6103,7 +6123,7 @@
       <c r="H102" s="5" t="n"/>
       <c r="I102" s="5" t="inlineStr">
         <is>
-          <t>81eb760ebbe224ae52cd7aea8f7f2865e4134908</t>
+          <t>3037549015be6f15d4f1ec59b34554b9238ac0c3</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6133,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Overcoming the Retrieval Barrier: Indirect Prompt Injection in the Wild for LLM Systems</t>
+          <t>Bridging AI and Software Security: A Comparative Vulnerability Assessment of LLM Agent Deployment Paradigms</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -6136,7 +6156,7 @@
       <c r="H103" s="5" t="n"/>
       <c r="I103" s="5" t="inlineStr">
         <is>
-          <t>81eb760ebbe224ae52cd7aea8f7f2865e4134908</t>
+          <t>3037549015be6f15d4f1ec59b34554b9238ac0c3</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6166,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Overcoming the Retrieval Barrier: Indirect Prompt Injection in the Wild for LLM Systems</t>
+          <t>Bridging AI and Software Security: A Comparative Vulnerability Assessment of LLM Agent Deployment Paradigms</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -6169,7 +6189,7 @@
       <c r="H104" s="5" t="n"/>
       <c r="I104" s="5" t="inlineStr">
         <is>
-          <t>81eb760ebbe224ae52cd7aea8f7f2865e4134908</t>
+          <t>3037549015be6f15d4f1ec59b34554b9238ac0c3</t>
         </is>
       </c>
     </row>
@@ -6179,7 +6199,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Overcoming the Retrieval Barrier: Indirect Prompt Injection in the Wild for LLM Systems</t>
+          <t>Bridging AI and Software Security: A Comparative Vulnerability Assessment of LLM Agent Deployment Paradigms</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -6202,7 +6222,7 @@
       <c r="H105" s="5" t="n"/>
       <c r="I105" s="5" t="inlineStr">
         <is>
-          <t>81eb760ebbe224ae52cd7aea8f7f2865e4134908</t>
+          <t>3037549015be6f15d4f1ec59b34554b9238ac0c3</t>
         </is>
       </c>
     </row>
@@ -6212,7 +6232,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Overcoming the Retrieval Barrier: Indirect Prompt Injection in the Wild for LLM Systems</t>
+          <t>Bridging AI and Software Security: A Comparative Vulnerability Assessment of LLM Agent Deployment Paradigms</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -6235,7 +6255,7 @@
       <c r="H106" s="5" t="n"/>
       <c r="I106" s="5" t="inlineStr">
         <is>
-          <t>81eb760ebbe224ae52cd7aea8f7f2865e4134908</t>
+          <t>3037549015be6f15d4f1ec59b34554b9238ac0c3</t>
         </is>
       </c>
     </row>
@@ -6245,7 +6265,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Overcoming the Retrieval Barrier: Indirect Prompt Injection in the Wild for LLM Systems</t>
+          <t>Bridging AI and Software Security: A Comparative Vulnerability Assessment of LLM Agent Deployment Paradigms</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -6268,7 +6288,7 @@
       <c r="H107" s="5" t="n"/>
       <c r="I107" s="5" t="inlineStr">
         <is>
-          <t>81eb760ebbe224ae52cd7aea8f7f2865e4134908</t>
+          <t>3037549015be6f15d4f1ec59b34554b9238ac0c3</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6298,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Overcoming the Retrieval Barrier: Indirect Prompt Injection in the Wild for LLM Systems</t>
+          <t>Bridging AI and Software Security: A Comparative Vulnerability Assessment of LLM Agent Deployment Paradigms</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -6293,7 +6313,7 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>No public code/data release URL is stated in the extracted text (unlike many other IPI papers in this corpus). The paper does provide a detailed algorithmic description (Algorithm 1: CEM Attack for Prefix Search) and full attack prompts/attack fragments in an appendix (referenced as Appendix A.3), intended for scientific reproducibility, but explicitly frames this disclosure as limited to avoid functioning as a how-to guide.</t>
+          <t>Code and experimental materials are publicly available at https://github.com/theconsciouslab-ai/llm-agent-security, including the unified threat classification framework, attack simulation implementations, and the extensible testing framework for evaluating LLM agents across both Function Calling and MCP paradigms.</t>
         </is>
       </c>
       <c r="F108" s="5" t="n"/>
@@ -6301,7 +6321,7 @@
       <c r="H108" s="5" t="n"/>
       <c r="I108" s="5" t="inlineStr">
         <is>
-          <t>81eb760ebbe224ae52cd7aea8f7f2865e4134908</t>
+          <t>3037549015be6f15d4f1ec59b34554b9238ac0c3</t>
         </is>
       </c>
     </row>
@@ -6311,7 +6331,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Overcoming the Retrieval Barrier: Indirect Prompt Injection in the Wild for LLM Systems</t>
+          <t>Bridging AI and Software Security: A Comparative Vulnerability Assessment of LLM Agent Deployment Paradigms</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -6326,7 +6346,7 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>For end-to-end agentic/RAG attack evaluation: GPT-4o and GPT-4o-mini as base LLMs in single- and multi-agent workflows. For retrieval-attack evaluation: 8 embedding models spanning open-source (including contriever-msmarco, ~768-dimensional models) and proprietary/closed-source services (OpenAI text-embedding-3-small, Voyage voyage-3.5-lite, voyage-3-large, and others referenced as 'embedding-v4'-class models). For knowledge-poisoning comparison experiments: LLaMa-2-7B, following Zou et al.'s (2023-style) experimental setup with the contriever embedding model. Instruction-tuned vs. base and model-scale comparisons (e.g., Vicuna-7B vs. 13B, multiple Qwen-series scales) are also evaluated for downstream susceptibility once retrieval succeeds.</t>
+          <t>Seven language models deployed across two major cloud providers (Azure and AWS) and two tool-calling architectural paradigms (Function Calling and MCP), including O1, O3-mini, Claude 3-5, Claude 3-7, Claude Haiku, GPT-4.1, and at least one additional model (the paper explicitly names O1, O3-mini, Claude 3-7 as reasoning models, and Claude 3-5, GPT-4.1, Claude Haiku as specific data points in results).</t>
         </is>
       </c>
       <c r="F109" s="5" t="n"/>
@@ -6334,7 +6354,7 @@
       <c r="H109" s="5" t="n"/>
       <c r="I109" s="5" t="inlineStr">
         <is>
-          <t>81eb760ebbe224ae52cd7aea8f7f2865e4134908</t>
+          <t>3037549015be6f15d4f1ec59b34554b9238ac0c3</t>
         </is>
       </c>
     </row>
@@ -6344,7 +6364,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Overcoming the Retrieval Barrier: Indirect Prompt Injection in the Wild for LLM Systems</t>
+          <t>Bridging AI and Software Security: A Comparative Vulnerability Assessment of LLM Agent Deployment Paradigms</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -6359,7 +6379,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>11 BEIR benchmark information-retrieval corpora spanning diverse domains (MSMARCO, TREC-COVID, NFCorpus, NQ, HotpotQA, FiQA-2018, ArguAna, DBPedia, SCIDOCS, FEVER, SciFact) used to evaluate retrieval-attack effectiveness across natural user queries. For end-to-end agentic evaluation, the authors construct realistic multi-agent workflows over email/tool-use scenarios (targeted-answer manipulation, phishing-worm propagation via email self-replication, tool misuse/mass-contact spamming, and code execution/SSH-key exfiltration), following an injection template adapted from prior multi-agent-security work (referred to as [89]) but extended to include the retrieval step. Knowledge-poisoning comparison experiments follow Zou et al.'s exact benchmark setup on NQ, MS-MARCO, and HotpotQA with LLaMa-2-7B.</t>
+          <t>No pre-existing benchmark dataset is used; the authors construct their own unified threat classification framework (Table 1) covering nine primary attack vectors spanning both AI-specific threats (prompt injection, indirect prompt injection) and traditional software vulnerabilities (JSON injection, tool injection, denial-of-service), informed by frameworks such as ATFAA. They generate 3,250 total attack scenarios across three complexity tiers -- simple (single-vector), composed (multi-technique using function compositions), and chained (multi-stage, traversing system nodes sequentially) -- tested against both Function Calling and MCP deployment paradigms across the seven models and two cloud providers.</t>
         </is>
       </c>
       <c r="F110" s="5" t="n"/>
@@ -6367,7 +6387,7 @@
       <c r="H110" s="5" t="n"/>
       <c r="I110" s="5" t="inlineStr">
         <is>
-          <t>81eb760ebbe224ae52cd7aea8f7f2865e4134908</t>
+          <t>3037549015be6f15d4f1ec59b34554b9238ac0c3</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6397,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Overcoming the Retrieval Barrier: Indirect Prompt Injection in the Wild for LLM Systems</t>
+          <t>Bridging AI and Software Security: A Comparative Vulnerability Assessment of LLM Agent Deployment Paradigms</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -6392,7 +6412,7 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Unoptimized (naive) malicious text is essentially never retrieved under natural queries across all 11 BEIR corpora regardless of corpus size or query length, establishing retrieval as the true bottleneck for IPI. The paper's CEM-based prefix-optimization attack, using as few as 10 trigger tokens, achieves near-100% retrieval: at trigger length n=10, average Recall@5 across the 11 datasets reaches 95.6% (versus 29.5% at n=3), with several datasets (NFCorpus, NQ, HotpotQA, DBPedia, SCIDOCS, FEVER, SciFact) reaching 100% Recall@5, and the attack costs as little as $0.21 per target query on OpenAI/Voyage embeddings. In end-to-end agentic evaluation with GPT-4o, a single poisoned email using the Fusion variant of the attack achieved 80% attack success rate (ASR) for SSH-key exfiltration via code execution in a multi-agent workflow, roughly 40x higher than the equivalent single-agent setting (2% ASR) despite GPT-4o's greater conservatism when directly exposed to overtly malicious content; worm propagation ASR reached 84% (email phishing link) and 18% (full self-replication chain) for GPT-4o under the Fusion attack, and tool-misuse (contact harvesting plus phishing) reached 98% ASR. Comparisons against the 'ideal' baseline (attack fragment assumed already in context, mirroring prior idealized IPI evaluations) showed idealized evaluation can substantially underestimate real risk (e.g., code execution ASR of only 2-4% under the ideal baseline versus 26-80% under the full end-to-end attack with realistic retrieval), while in the multi-agent worm-propagation-under-ideal-context case it could also overestimate risk relative to realistic conditions in other settings, underscoring that both retrieval and downstream execution stages must be jointly evaluated. Three intuitive black-box defenses (query paraphrasing, perplexity filtering, token masking) each provided only modest protection against the non-adaptive attack and collapsed entirely against simple adaptive countermeasures (e.g., jointly optimizing over multiple paraphrases restored or exceeded baseline attack performance; repeating the malicious text reduced its perplexity below that of clean documents, defeating perplexity filters).</t>
+          <t>Overall, Function Calling showed a higher aggregate attack success rate (73.5% ASR) than MCP (62.59% ASR), but the vulnerability profile inverts by threat type: Function Calling exhibits substantially higher system-centric ASR (87.98%, later cited as 92.27% for Azure specifically) due to tightly-coupled LLM orchestration/tool-registry/execution layers and heavy reliance on JSON schemas, whereas MCP exhibits higher LLM-centric ASR (68.28%) due to its context-rich, standardized prompt-passing and persistent session management expanding attack surface for reasoning-targeted threats; MCP's client-server separation correspondingly gives it a lower system-centric ASR (57%). Provider comparison within Function Calling shows Azure (no system role access) is more resistant to LLM-centric attacks (55.42% vs. AWS's 63%) but more vulnerable to system-centric attacks (92.27% vs. AWS's 84.76%), with both providers converging to a similar overall ASR (~74%). A counterintuitive model-level finding: models with stronger reasoning capabilities (O1, O3-mini, Claude 3-7) show better initial threat detection (averaging 17.8% Refusal Rate vs. non-reasoning models) yet the most capable/sophisticated models exhibit the highest overall attack success once defenses are breached -- Claude 3-5 (75% ASR) and GPT-4.1 (72% ASR) represent peak vulnerability, while the more narrowly-optimized Claude Haiku achieves a more balanced profile (65.56% ASR, 18.37% RR); even within the same Anthropic Responsible Scaling Policy tier (ASL-2), Claude 3-5 and Claude Haiku show a 9.44-percentage-point ASR gap, demonstrating static safety classifications alone cannot predict model-specific vulnerability. Attack complexity dramatically amplifies effectiveness: simple attacks achieved only ~50% ASR on most vectors (with DoS attacks at 0% ASR due to cloud-provider safeguard interception), but composed attacks showed diverging architectural effects -- Function Calling ASR rose from 56% to 70% under composition (tight coupling accelerates multi-stage propagation), while MCP ASR actually decreased from 60% to 51.32% under composition (client-server separation impedes multi-stage propagation) -- though composed attacks did succeed in circumventing DoS-specific cloud safeguards by embedding DoS techniques within prompt-injection vectors. Chained (multi-stage) attacks achieved the highest and most consistent success rates across both paradigms, reaching 91-96% ASR (up to 88-96% via contextual-poisoning pathways in MCP), dramatically exceeding any single-vector baseline and demonstrating that single-vector security assessments substantially underestimate real-world risk.</t>
         </is>
       </c>
       <c r="F111" s="5" t="n"/>
@@ -6400,7 +6420,7 @@
       <c r="H111" s="5" t="n"/>
       <c r="I111" s="5" t="inlineStr">
         <is>
-          <t>81eb760ebbe224ae52cd7aea8f7f2865e4134908</t>
+          <t>3037549015be6f15d4f1ec59b34554b9238ac0c3</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6430,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Overcoming the Retrieval Barrier: Indirect Prompt Injection in the Wild for LLM Systems</t>
+          <t>Bridging AI and Software Security: A Comparative Vulnerability Assessment of LLM Agent Deployment Paradigms</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -6425,7 +6445,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>An 'ideal' baseline (following prior work) that assumes the attack fragment is already retrieved/in-context, mirroring standard idealized IPI evaluation setups. Query+ (from Zou et al., prepending the user query itself to the attack fragment), described as the strongest prior black-box heuristic reported in the literature. The paper's own Ours (CEM) variant (a learned 10-token trigger prefix from the proposed Cross-Entropy-Method-based black-box optimization) and Ours (Fusion) variant (concatenating the CEM-generated trigger, the user query, and the attack fragment). For knowledge-poisoning comparison, the paper additionally benchmarks against a Disinformation baseline and the white-box-adjacent Baseline attack from Zou et al. on LLaMa-2-7B with the contriever embedding model, across varying trigger fragment lengths (1-5 tokens) of the proposed method.</t>
+          <t>No prior defense systems are directly benchmarked as external baselines; the study's comparative structure is internal -- Function Calling vs. MCP architectural paradigms, Azure vs. AWS cloud-provider implementations of Function Calling, seven different LLM backbones (reasoning vs. non-reasoning models), and three attack-complexity tiers (simple vs. composed vs. chained) -- used to isolate how architecture, provider, model capability, and attack sophistication each independently and interactively affect vulnerability.</t>
         </is>
       </c>
       <c r="F112" s="5" t="n"/>
@@ -6433,7 +6453,7 @@
       <c r="H112" s="5" t="n"/>
       <c r="I112" s="5" t="inlineStr">
         <is>
-          <t>81eb760ebbe224ae52cd7aea8f7f2865e4134908</t>
+          <t>3037549015be6f15d4f1ec59b34554b9238ac0c3</t>
         </is>
       </c>
     </row>
@@ -6443,7 +6463,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Overcoming the Retrieval Barrier: Indirect Prompt Injection in the Wild for LLM Systems</t>
+          <t>Bridging AI and Software Security: A Comparative Vulnerability Assessment of LLM Agent Deployment Paradigms</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -6458,7 +6478,7 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>The adversary seeks to coerce a retrieval-augmented LLM system into executing an arbitrary attacker-chosen attack fragment (e.g., misinformation, phishing links, malicious Python commands like exfiltrating SSH keys) by ensuring it is retrieved into the model's context for a target natural user query, without assuming the malicious text is already 'in context' as prior idealized evaluations do. The threat model is strictly black-box: the adversary has no access to the parameters of the embedding model or retriever/LLM, can only query the embedding model via standard APIs (reflecting realistic deployments using proprietary services like OpenAI's text-embedding-3-small), has no visibility into the external corpus contents beyond the ability to inject their own single item (simulating a stealth attack practical for adversaries who can write to unverified-party-writable sources such as public web pages or email systems), and does not control the retriever's ranking mechanism. The attacker's construction is formalized as decomposing the injected text into a trigger fragment (an optimized short token prefix whose sole purpose is guaranteeing retrieval under natural, non-adversarial queries) and an attack fragment (the actual malicious payload, whose content/design is treated as out of scope and delegated to the separate direct-prompt-injection literature). Demonstrated end-to-end attack objectives span RAG-style answer manipulation, phishing-worm propagation via self-replicating email instructions, tool misuse (mass-messaging via harvested contacts), and code execution leading to credential exfiltration, evaluated in both single-agent and multi-agent pipelines, with multi-agent orchestration shown to substantially amplify attack success because downstream agents implicitly trust content passed from upstream 'teammate' agents.</t>
+          <t>The paper develops a structured, three-stage threat modeling and attack-simulation framework (Section 3.2, Figure 3) rather than a single fixed adversary definition, explicitly designed to enable comparative analysis across the two deployment paradigms. Stage 1 (Attack Surfaces Identification) systematically maps four vulnerable components: System Prompt, User Prompt, Tool Parameters, and Tool Output. Stage 2 (Attack Vector Classification) categorizes exploitation techniques into four types: Prompt Injection, Indirect Prompt Injection, JSON Injection, and Tool Injection, unified into a nine-primary-attack-vector taxonomy (Table 1) spanning both AI-specific threats (T1, T2, T5, T8 -- LLM-centric, e.g. reasoning-process manipulation) and traditional software vulnerabilities (T3, T4 -- system-centric, e.g. tool registry/execution compromise), explicitly framed against the CIA (Confidentiality, Integrity, Availability) triad adapted for LLM agents' probabilistic outputs and autonomous decision-making. Stage 3 (Attack Progression) models how attacks evolve in complexity from simple (single-vector exploits targeting individual surfaces) to composed (multi-technique exploits using function compositions) to chained (multi-stage exploits traversing system nodes sequentially), with formal ASR composition equations (e.g., ASR of a chain as the product of conditional per-step success probabilities). Two complementary evaluation metrics are defined: Attack Success Rate (ASR, probability of successful exploitation) and Refusal Rate (RR, the agent's explicit rejection of malicious requests), validated via LLM-as-judge scoring.</t>
         </is>
       </c>
       <c r="F113" s="5" t="n"/>
@@ -6466,7 +6486,7 @@
       <c r="H113" s="5" t="n"/>
       <c r="I113" s="5" t="inlineStr">
         <is>
-          <t>81eb760ebbe224ae52cd7aea8f7f2865e4134908</t>
+          <t>3037549015be6f15d4f1ec59b34554b9238ac0c3</t>
         </is>
       </c>
     </row>
@@ -6476,7 +6496,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Overcoming the Retrieval Barrier: Indirect Prompt Injection in the Wild for LLM Systems</t>
+          <t>Bridging AI and Software Security: A Comparative Vulnerability Assessment of LLM Agent Deployment Paradigms</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -6491,7 +6511,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>The paper has an explicit 'Limitations' section (Section 8) with three subsections: (1) Scope of this work -- the evaluation is strictly limited to embedding-based retrieval systems, and the defense evaluation (Section 6) is restricted to the retrieval stage; the attack's effectiveness against hybrid retrieval pipelines (combining dense and sparse/keyword search) and reranking mechanisms, which could potentially mitigate the attack, was not evaluated, an explicitly acknowledged gap; (2) Transferability -- the attack does not ensure transferability when the reference embedding model used for optimization and the target embedding model differ in architecture (referencing performance disparities in an appendix figure), which the authors flag as an interesting but challenging direction for future work; (3) Novelty -- the authors explicitly disclaim originality of the underlying Cross-Entropy Method optimization algorithm, crediting it to prior art and clarifying their contribution is specifically its adaptation to the indirect-prompt-injection retrieval problem. A separate Ethical Considerations section (following USENIX ethics guidelines) further scopes the work as controlled-benchmark research not representative of attacks against deployed production systems, and states the authors deliberately withheld novel payloads or step-by-step attack procedures beyond what is necessary for reproducibility to avoid the work functioning as a how-to guide.</t>
+          <t>The paper has a dedicated 'Study Limitations' subsection (Section 7.3, before the Conclusion) enumerating five specific constraints. Model/provider coverage: the evaluation spans seven LLM models across two major cloud providers, a substantial but non-exhaustive market sample; excluding emerging models/providers may limit generalizability, especially as rapid LLM evolution means model-specific vulnerability patterns may shift as architectures and safety mechanisms change. Architectural scope: the focus on Function Calling and MCP paradigms may not capture security implications of emerging decentralized agent-communication architectures (e.g., Google's A2A Protocol, IBM's ACP, Microsoft's multi-agent orchestration, Amazon's MARCO framework), which introduce peer-to-peer interactions, dynamic discovery, and autonomous collaboration patterns fundamentally different from the hierarchical/client-server models studied, potentially creating novel attack surfaces (inter-agent trust relationships, decentralized state management) the current analysis cannot address. Threat-taxonomy scope: the unified framework covers nine primary attack vectors derived from current literature and observed patterns, but the dynamic threat landscape means novel attack categories may emerge beyond this framework, motivating future systematic evaluation of emerging vectors. Temporal validity: findings represent a snapshot of security postures at time of testing; the security landscape evolves rapidly with new defensive mechanisms, model updates, and architectural improvements, and given the reactive nature of security improvements following vulnerability disclosure, current defensive capabilities may differ from what was measured. Deployment scope: analysis focused on cloud-based deployments via established APIs, which may not capture edge deployments, hybrid architectures, or custom implementation patterns, so organizations using alternative deployment strategies may see different vulnerability profiles than reported.</t>
         </is>
       </c>
       <c r="F114" s="5" t="n"/>
@@ -6499,7 +6519,7 @@
       <c r="H114" s="5" t="n"/>
       <c r="I114" s="5" t="inlineStr">
         <is>
-          <t>81eb760ebbe224ae52cd7aea8f7f2865e4134908</t>
+          <t>3037549015be6f15d4f1ec59b34554b9238ac0c3</t>
         </is>
       </c>
     </row>
@@ -6509,7 +6529,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Overcoming the Retrieval Barrier: Indirect Prompt Injection in the Wild for LLM Systems</t>
+          <t>Bridging AI and Software Security: A Comparative Vulnerability Assessment of LLM Agent Deployment Paradigms</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -6524,7 +6544,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>This paper identifies and closes a critical gap in prior indirect prompt injection (IPI) research: nearly all previous IPI evaluations assumed the malicious text is already retrieved into an LLM's context (e.g., by designating a 'latest email' as poisoned, using single-item corpora, or requiring specially optimized trigger tokens in the user query itself), which blurs the distinction between direct and indirect injection and leaves the real-world retrieval feasibility of IPI attacks unclear. The authors empirically confirm this gap by showing that unoptimized malicious text is essentially never retrieved under natural queries across 11 diverse BEIR retrieval benchmarks, establishing retrieval as the decisive bottleneck for any IPI attack to succeed. To address this, they formalize IPI attack construction as decomposing an injected item into a trigger fragment x (a short token prefix whose sole purpose is guaranteeing the item's retrieval for a target query) and an attack fragment D_adv (the arbitrary malicious payload executed once the item is in context), reducing the retrieval-guarantee problem to a black-box similarity-maximization problem: finding x such that the cosine similarity between the query embedding and the embedding of x-concatenated-with-D_adv places the item within the top-K retrieved results, under a strict black-box threat model where the adversary only has API-level query access to the embedding model (no white-box gradients, matching real-world deployments using proprietary embedding services). Because this discrete optimization is intractable via naive greedy search (requiring on the order of n|V| scoring calls) and provably NP-hard in the fully unknown-corpus setting, the authors adapt the classic Cross-Entropy Method (CEM), a black-box, sampling-based stochastic optimization algorithm, to iteratively refine a distribution over trigger tokens toward high-similarity prefixes using only black-box embedding API calls -- yielding an attack that is practical (API-only), cost-efficient (as little as $0.21 per target query), and highly effective (near-100% retrieval with as few as 10 tokens) across all 11 benchmark corpora and 8 embedding models spanning open-source and proprietary services. Building on this retrieval-guarantee primitive, the paper conducts the first end-to-end IPI evaluation spanning both RAG-style answer manipulation and realistic single-/multi-agent workflows (phishing-worm email propagation, tool misuse/contact-harvesting, and code-execution-based credential exfiltration), demonstrating that a single poisoned email under a natural user query (e.g., 'summarize emails about the reimbursement process') can coerce GPT-4o into exfiltrating SSH keys in up to 80% of trials in a multi-agent setting -- roughly 40x higher than the equivalent single-agent configuration, because downstream agents in a pipeline implicitly trust content forwarded by upstream teammate agents and never directly observe the injected content or original user query. The paper further evaluates three practical defenses requiring no knowledge of the attacker's optimization (query paraphrasing, perplexity filtering, and token masking), showing each collapses under simple adaptive countermeasures the attacker can readily apply (joint multi-paraphrase optimization, text repetition to reduce perplexity below clean-document levels, and the flexible/benign-looking positioning of trigger tokens), concluding that retrieval-stage security remains a largely unaddressed and critical open vulnerability in deployed retrieval-augmented LLM systems.</t>
+          <t>This paper presents the first comprehensive comparative security evaluation bridging AI-specific and traditional software-security perspectives on LLM agent deployment, motivated by the observation that prior research treats these domains separately: AI-centric studies (e.g., Agent Safety Benchmark, AgentDojo, InjecAgent) evaluate agent vulnerability at the LLM decision-making boundary without tracing how compromises cascade through connected software systems, while software-centric research examines plugin/supply-chain vulnerabilities without connecting them to AI-specific exploitation. The paper compares two representative LLM-agent tool-calling architectural paradigms with contrasting design philosophies: Function Calling (manual, platform-specific, tightly coupling LLM orchestration, tool registry, and execution into API endpoints) and the Model Context Protocol/MCP (a dynamic, standardized client-server protocol with tool execution on dedicated servers). The authors build a unified, three-stage threat modeling and attack-simulation framework -- attack surface identification (system prompt, user prompt, tool parameters, tool output), attack vector classification (prompt injection, indirect prompt injection, JSON injection, tool injection, unified into nine primary attack vectors spanning both AI-specific and traditional software threats), and attack progression modeling (simple, composed, and chained attacks of increasing multi-stage sophistication) -- and use it to generate and execute 3,250 attack scenarios across seven LLM backbones deployed through both paradigms and two cloud providers (Azure, AWS), measuring Attack Success Rate and Refusal Rate via LLM-as-judge evaluation. The central finding is that architectural choice fundamentally and asymmetrically reshapes the threat landscape rather than uniformly improving or degrading security: Function Calling's tight component coupling produces higher system-centric vulnerability (favoring attacks on tool execution/registry) while MCP's richer, standardized, session-persistent protocol produces higher LLM-centric vulnerability (favoring attacks on reasoning/context), and these architectural properties interact non-trivially with attack complexity -- Function Calling's coupling amplifies composed multi-technique attacks while MCP's client-server separation actually impedes them, but both paradigms converge toward near-total compromise (91-96% ASR) once attacks are chained into multi-stage sequences, meaning single-vector security assessments dramatically understate real-world exploitability. A further counterintuitive finding is that more capable/sophisticated reasoning models, despite superior initial threat detection and refusal behavior, exhibit higher overall exploitability once an attack breaches initial defenses, undermining the assumption that model capability alone predicts security posture, and demonstrating that even models under the same formal safety classification tier can have substantially different measured vulnerability.</t>
         </is>
       </c>
       <c r="F115" s="5" t="n"/>
@@ -6532,7 +6552,7 @@
       <c r="H115" s="5" t="n"/>
       <c r="I115" s="5" t="inlineStr">
         <is>
-          <t>81eb760ebbe224ae52cd7aea8f7f2865e4134908</t>
+          <t>3037549015be6f15d4f1ec59b34554b9238ac0c3</t>
         </is>
       </c>
     </row>
@@ -6542,7 +6562,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Manipulating LLM Web Agents with Indirect Prompt Injection Attack via HTML Accessibility Tree</t>
+          <t>LivePI: More Realistic Benchmarking of Agents Against Indirect Prompt Injection</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -6565,7 +6585,7 @@
       <c r="H116" s="5" t="n"/>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>2b73f8dbb2af737fe707df3b2dcb21a9cea62db5</t>
+          <t>4e959fca0e4d91c84b708457efa08b0f729a05ef</t>
         </is>
       </c>
     </row>
@@ -6575,7 +6595,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Manipulating LLM Web Agents with Indirect Prompt Injection Attack via HTML Accessibility Tree</t>
+          <t>LivePI: More Realistic Benchmarking of Agents Against Indirect Prompt Injection</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -6598,7 +6618,7 @@
       <c r="H117" s="5" t="n"/>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>2b73f8dbb2af737fe707df3b2dcb21a9cea62db5</t>
+          <t>4e959fca0e4d91c84b708457efa08b0f729a05ef</t>
         </is>
       </c>
     </row>
@@ -6608,7 +6628,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Manipulating LLM Web Agents with Indirect Prompt Injection Attack via HTML Accessibility Tree</t>
+          <t>LivePI: More Realistic Benchmarking of Agents Against Indirect Prompt Injection</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -6631,7 +6651,7 @@
       <c r="H118" s="5" t="n"/>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>2b73f8dbb2af737fe707df3b2dcb21a9cea62db5</t>
+          <t>4e959fca0e4d91c84b708457efa08b0f729a05ef</t>
         </is>
       </c>
     </row>
@@ -6641,7 +6661,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Manipulating LLM Web Agents with Indirect Prompt Injection Attack via HTML Accessibility Tree</t>
+          <t>LivePI: More Realistic Benchmarking of Agents Against Indirect Prompt Injection</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -6656,7 +6676,7 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>attack</t>
+          <t>neither</t>
         </is>
       </c>
       <c r="F119" s="5" t="n"/>
@@ -6664,7 +6684,7 @@
       <c r="H119" s="5" t="n"/>
       <c r="I119" s="5" t="inlineStr">
         <is>
-          <t>2b73f8dbb2af737fe707df3b2dcb21a9cea62db5</t>
+          <t>4e959fca0e4d91c84b708457efa08b0f729a05ef</t>
         </is>
       </c>
     </row>
@@ -6674,7 +6694,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Manipulating LLM Web Agents with Indirect Prompt Injection Attack via HTML Accessibility Tree</t>
+          <t>LivePI: More Realistic Benchmarking of Agents Against Indirect Prompt Injection</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -6697,7 +6717,7 @@
       <c r="H120" s="5" t="n"/>
       <c r="I120" s="5" t="inlineStr">
         <is>
-          <t>2b73f8dbb2af737fe707df3b2dcb21a9cea62db5</t>
+          <t>4e959fca0e4d91c84b708457efa08b0f729a05ef</t>
         </is>
       </c>
     </row>
@@ -6707,7 +6727,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Manipulating LLM Web Agents with Indirect Prompt Injection Attack via HTML Accessibility Tree</t>
+          <t>LivePI: More Realistic Benchmarking of Agents Against Indirect Prompt Injection</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -6730,7 +6750,7 @@
       <c r="H121" s="5" t="n"/>
       <c r="I121" s="5" t="inlineStr">
         <is>
-          <t>2b73f8dbb2af737fe707df3b2dcb21a9cea62db5</t>
+          <t>4e959fca0e4d91c84b708457efa08b0f729a05ef</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6760,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Manipulating LLM Web Agents with Indirect Prompt Injection Attack via HTML Accessibility Tree</t>
+          <t>LivePI: More Realistic Benchmarking of Agents Against Indirect Prompt Injection</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -6763,7 +6783,7 @@
       <c r="H122" s="5" t="n"/>
       <c r="I122" s="5" t="inlineStr">
         <is>
-          <t>2b73f8dbb2af737fe707df3b2dcb21a9cea62db5</t>
+          <t>4e959fca0e4d91c84b708457efa08b0f729a05ef</t>
         </is>
       </c>
     </row>
@@ -6773,7 +6793,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Manipulating LLM Web Agents with Indirect Prompt Injection Attack via HTML Accessibility Tree</t>
+          <t>LivePI: More Realistic Benchmarking of Agents Against Indirect Prompt Injection</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -6796,7 +6816,7 @@
       <c r="H123" s="5" t="n"/>
       <c r="I123" s="5" t="inlineStr">
         <is>
-          <t>2b73f8dbb2af737fe707df3b2dcb21a9cea62db5</t>
+          <t>4e959fca0e4d91c84b708457efa08b0f729a05ef</t>
         </is>
       </c>
     </row>
@@ -6806,7 +6826,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Manipulating LLM Web Agents with Indirect Prompt Injection Attack via HTML Accessibility Tree</t>
+          <t>LivePI: More Realistic Benchmarking of Agents Against Indirect Prompt Injection</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -6829,7 +6849,7 @@
       <c r="H124" s="5" t="n"/>
       <c r="I124" s="5" t="inlineStr">
         <is>
-          <t>2b73f8dbb2af737fe707df3b2dcb21a9cea62db5</t>
+          <t>4e959fca0e4d91c84b708457efa08b0f729a05ef</t>
         </is>
       </c>
     </row>
@@ -6839,7 +6859,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Manipulating LLM Web Agents with Indirect Prompt Injection Attack via HTML Accessibility Tree</t>
+          <t>LivePI: More Realistic Benchmarking of Agents Against Indirect Prompt Injection</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -6862,7 +6882,7 @@
       <c r="H125" s="5" t="n"/>
       <c r="I125" s="5" t="inlineStr">
         <is>
-          <t>2b73f8dbb2af737fe707df3b2dcb21a9cea62db5</t>
+          <t>4e959fca0e4d91c84b708457efa08b0f729a05ef</t>
         </is>
       </c>
     </row>
@@ -6872,7 +6892,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Manipulating LLM Web Agents with Indirect Prompt Injection Attack via HTML Accessibility Tree</t>
+          <t>LivePI: More Realistic Benchmarking of Agents Against Indirect Prompt Injection</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -6895,7 +6915,7 @@
       <c r="H126" s="5" t="n"/>
       <c r="I126" s="5" t="inlineStr">
         <is>
-          <t>2b73f8dbb2af737fe707df3b2dcb21a9cea62db5</t>
+          <t>4e959fca0e4d91c84b708457efa08b0f729a05ef</t>
         </is>
       </c>
     </row>
@@ -6905,7 +6925,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Manipulating LLM Web Agents with Indirect Prompt Injection Attack via HTML Accessibility Tree</t>
+          <t>LivePI: More Realistic Benchmarking of Agents Against Indirect Prompt Injection</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -6920,7 +6940,7 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>The system software (a Python library for generating IPI attacks) is released under the MIT License at https://github.com/sej2020/manipulating-web-agents, and an accompanying publicly available interactive demo website (http://lethaiq.github.io/attack-web-llm-agent) presents cached attack results on five real-world websites without requiring live model inference or full browser emulation. The Universal Website Targeted Instruction (login credential exfiltration) scenario is deliberately withheld from the public demo for ethical reasons.</t>
+          <t>Project page at https://leizhao7.github.io/livepi/ and code released at https://github.com/leizhao7/livepi, both stated on the title page of the paper.</t>
         </is>
       </c>
       <c r="F127" s="5" t="n"/>
@@ -6928,7 +6948,7 @@
       <c r="H127" s="5" t="n"/>
       <c r="I127" s="5" t="inlineStr">
         <is>
-          <t>2b73f8dbb2af737fe707df3b2dcb21a9cea62db5</t>
+          <t>4e959fca0e4d91c84b708457efa08b0f729a05ef</t>
         </is>
       </c>
     </row>
@@ -6938,7 +6958,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Manipulating LLM Web Agents with Indirect Prompt Injection Attack via HTML Accessibility Tree</t>
+          <t>LivePI: More Realistic Benchmarking of Agents Against Indirect Prompt Injection</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -6953,7 +6973,7 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Meta's Llama-3.1-8B-Instruct as the primary target model for the Browser Gym web navigation agent. Transferability of TWUI-optimized triggers was additionally tested (unsuccessfully, without joint multi-model optimization) against Llama-2-7b-chat-hf and Mistral-7B-Instruct-v0.3.</t>
+          <t>Five LLM backbones powering the OpenClaw agent under test: GPT-5.3-Codex, Claude Opus 4.6, Gemini 3.1 Pro, Kimi K2.5, and GLM-5. Note the defended (Layer 1+Layer 2) evaluation is run only for the GPT-5.3-Codex configuration, an explicitly stated limitation. An LLM judge (supplemented by deterministic checks) is used for outcome grading, with the paper noting one evaluated backbone shares a model family with the judge, a potential source of bias.</t>
         </is>
       </c>
       <c r="F128" s="5" t="n"/>
@@ -6961,7 +6981,7 @@
       <c r="H128" s="5" t="n"/>
       <c r="I128" s="5" t="inlineStr">
         <is>
-          <t>2b73f8dbb2af737fe707df3b2dcb21a9cea62db5</t>
+          <t>4e959fca0e4d91c84b708457efa08b0f729a05ef</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6991,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Manipulating LLM Web Agents with Indirect Prompt Injection Attack via HTML Accessibility Tree</t>
+          <t>LivePI: More Realistic Benchmarking of Agents Against Indirect Prompt Injection</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -6986,7 +7006,7 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>No pre-existing benchmark dataset is used; the authors construct their own evaluation sets from five real-world websites (chess.com, games.penjee.com binary-numbers-game, citybrewtours.com, norway.no/en/missions/un, translate.google.com) for Targeted-Website-Targeted-Instruction (TWTI) and Targeted-Website-Universal-Instruction (TWUI) scenarios, with 200 varied navigation-instruction prompts per website for TWUI attack-success testing. For the Universal-Website-Targeted-Instruction (UWTI) credential-exfiltration scenario, they construct copies of eight real-world login pages (forums/social media sites) for trigger training and eleven held-out login pages for evaluation.</t>
+          <t>LivePI (Live Prompt Injection): a custom benchmark of 169 executable attack instances spanning 7 injection surfaces (group chat, email, local docs, repository links, gist, and others per Table 1), 12 attack-technique/rendering families (Table 2), and 5 malicious goals (protected-information exfiltration, unauthorized security-control changes, unsafe code retrieval/execution, inbox-summary exfiltration, and unauthorized cryptocurrency transfer; Table 3), run against a real OpenClaw agent instance on a virtual machine with live but test-controlled email, chat, web, local-file, repository, and bounded-wallet interfaces (not a purely simulated sandbox). Benign utility is evaluated using PinchBench, an existing 123-task benchmark for OpenClaw agents covering productivity, research, writing, coding, analysis, email, memory, and skill-use workflows.</t>
         </is>
       </c>
       <c r="F129" s="5" t="n"/>
@@ -6994,7 +7014,7 @@
       <c r="H129" s="5" t="n"/>
       <c r="I129" s="5" t="inlineStr">
         <is>
-          <t>2b73f8dbb2af737fe707df3b2dcb21a9cea62db5</t>
+          <t>4e959fca0e4d91c84b708457efa08b0f729a05ef</t>
         </is>
       </c>
     </row>
@@ -7004,7 +7024,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Manipulating LLM Web Agents with Indirect Prompt Injection Attack via HTML Accessibility Tree</t>
+          <t>LivePI: More Realistic Benchmarking of Agents Against Indirect Prompt Injection</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -7019,7 +7039,7 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>In the TWUI setting (universal trigger per website, tested across 200 held-out navigation goals per site), attack success rate (ASR, response passes the syntactic filter and invokes the targeted computer-use function) was very high across all five sample websites, with the lowest ASR observed at 0.83 (city/citybrewtours.com); some sites (e.g., chess.com) showed notably higher ASR than the stricter ASRV metric (exact verbatim target sequence match), attributed mainly to benign quote-style discrepancies that Browser Gym still parsed successfully. In the UWTI credential-exfiltration setting, a single universal trigger induced information leakage (username and/or password) on seven of eight training-set login pages, and on three of eleven held-out test-set login pages, for a test-set ASR of 0.55. Standard GCG hyperparameters required roughly several hours per optimization run; using a smaller search width (128) kept average runtime under three hours, and including the target output string directly in the initial trigger sequence reduced optimization time to under an hour (sometimes under ten minutes), while trigger length and Carlini-Wagner loss versus cross-entropy loss showed no measurable effect on convergence speed. Failure analysis identified two dominant failure clusters: instructions with only one obvious correct action (high prior probability on the correct-action tokens overwhelmed the trigger), and cases where the model defaulted to chain-of-thought reasoning preambles ('To achieve the goal of...') instead of the target action, both linked to high baseline token priors that the optimized trigger could not fully override. Attempted trigger transfer to Llama-2-7b-chat-hf and Mistral-7B-Instruct-v0.3 (without joint multi-model optimization) was unsuccessful, indicating triggers optimized via single-model GCG are largely model-specific.</t>
+          <t>Total attack success rate (ASR) across the five backbones ranges from 10.7% (Claude Opus 4.6, the safest) to 29.6% (Gemini 3.1 Pro), with GLM-5 at 27.8%, GPT-5.3-Codex at 27.2%, and Kimi K2.5 at 16.6% (Table 4). Group-chat injection succeeds uniformly at 100% ASR across all five models regardless of backbone, traced to a runtime implementation detail: group-member messages enter the model context with role 'user' while tool outputs use role 'toolResult,' causing malicious group content to be interpreted as instruction-bearing user intent even when the attacker account has never paired with the bot. Repository-link attacks also show severe failure rates (4/4 fully successful for four of five models, 2/4 for Claude Opus 4.6), though the authors caution this reflects only 4 test cases and should be read as a high-severity risk signal rather than a precise prevalence estimate. Email (2.0%-20.0% ASR) and Gist (0.0% for four models, 20.0% for Gemini 3.1 Pro) are comparatively weaker attack surfaces; Local Docs is strongly model-dependent, ranging from 0.0% (Claude Opus 4.6) to 50.0% (GLM-5). The two-layer defense (prompt-level filtering plus pre-execution tool-call policy authorization), evaluated only in the GPT-5.3-Codex configuration with seven custom policy rules added to built-in presets, reduces ASR on LivePI's attack suite to 0% while on the PinchBench benign-utility suite (899 total tool calls) only 0.89% of calls are sent to human review and 0.11% are blocked (Table 5), indicating the defense substantially improves safety with low friction to normal agent operation under this specific configuration.</t>
         </is>
       </c>
       <c r="F130" s="5" t="n"/>
@@ -7027,7 +7047,7 @@
       <c r="H130" s="5" t="n"/>
       <c r="I130" s="5" t="inlineStr">
         <is>
-          <t>2b73f8dbb2af737fe707df3b2dcb21a9cea62db5</t>
+          <t>4e959fca0e4d91c84b708457efa08b0f729a05ef</t>
         </is>
       </c>
     </row>
@@ -7037,7 +7057,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Manipulating LLM Web Agents with Indirect Prompt Injection Attack via HTML Accessibility Tree</t>
+          <t>LivePI: More Realistic Benchmarking of Agents Against Indirect Prompt Injection</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -7052,7 +7072,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>No defense mechanisms or competing attack methods are empirically benchmarked against; the paper's own three attack scenario variants (TWTI: per-website-per-instruction trigger; TWUI: universal trigger across many instructions for one website; UWTI: universal trigger across multiple websites/login pages for credential theft) serve as internally compared conditions, and GCG hyperparameter variants (search width, top-k token replacement candidates, Carlini-Wagner vs. cross-entropy loss, inclusion of target string in initial trigger) are compared against each other for optimization time-to-completion rather than against alternative attack algorithms.</t>
+          <t>The five LLM backbones (GPT-5.3-Codex, Claude Opus 4.6, Gemini 3.1 Pro, Kimi K2.5, GLM-5) are compared against each other as the primary comparison across all seven injection surfaces. The two-layer defense (prompt-level detector + policy-based tool-call gate) is evaluated against an undefended baseline (same GPT-5.3-Codex agent without the defense plugin) on both the LivePI attack suite (ASR) and the PinchBench benign-utility suite (review/block rate).</t>
         </is>
       </c>
       <c r="F131" s="5" t="n"/>
@@ -7060,7 +7080,7 @@
       <c r="H131" s="5" t="n"/>
       <c r="I131" s="5" t="inlineStr">
         <is>
-          <t>2b73f8dbb2af737fe707df3b2dcb21a9cea62db5</t>
+          <t>4e959fca0e4d91c84b708457efa08b0f729a05ef</t>
         </is>
       </c>
     </row>
@@ -7070,7 +7090,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Manipulating LLM Web Agents with Indirect Prompt Injection Attack via HTML Accessibility Tree</t>
+          <t>LivePI: More Realistic Benchmarking of Agents Against Indirect Prompt Injection</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -7085,7 +7105,7 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>The attacker's goal is to hijack an LLM-based web navigation agent's actions by embedding an adversarial trigger sequence into webpage HTML that the agent's accessibility-tree parser feeds into its prompt, without the end user noticing (stealth achieved via URL-hiding, transparent font, or CSS-based element hiding). The attacker's capability requirement is control over some portion of the HTML the navigation agent will consume -- e.g., a website owner, a third-party ad broker whose ad content is embedded on many sites, or an adversary exploiting user-generated content areas (comment sections, forum entries, profiles); the attacker does not need white-box access to the agent's LLM weights beyond what is needed to run GCG optimization against a copy of the (open-source) target model, and triggers are optimized offline via the Greedy Coordinate Gradient algorithm to be universal across many user instructions (TWUI) or across many websites for a fixed instruction type such as login-page credential theft (UWTI). Concrete attack goals demonstrated include forcing malicious ad clicks, redirecting to phishing/malware links, exfiltrating login credentials to an external party, and other unintended computer-use actions (clicks, tab closures, following social media accounts) contrary to the user's actual instruction; the threat model explicitly notes limitations that reduce attacker feasibility, including LLM-specificity of triggers and dependence on syntactic validity of the target action within the specific web agent framework.</t>
+          <t>Formal indirect-prompt-injection (IPI) threat model for real, tool-using AI agents (focused on OpenClaw). Attacker-controlled instructions are embedded in content that appears to be ordinary data -- email, downloaded files, webpages, repositories, or group-chat messages -- delivered through one of seven live-but-test-controlled input surfaces; once this content enters the agent's observation stream, the model may incorrectly treat it as an instruction rather than untrusted evidence, leading it to take unsafe, high-privilege real-world actions (financial transfer via a bounded crypto wallet, disabling security controls, exfiltrating protected information or inbox summaries, retrieving/executing unsafe code) rather than only text-generation failures. The paper identifies two recurring mechanistic failure modes underlying successful attacks: (1) the agent over-trusts instructions from unverified participants in shared chat channels (traced to a role-labeling implementation flaw where group messages are tagged 'user' rather than distinguished from trusted tool output), and (2) the agent follows injected directives interleaved within otherwise legitimate multi-step task execution. The defense side formalizes a two-layer threat-mitigation architecture: Layer 1 (prompt-level pattern-matching detector flagging suspicious instructions such as 'ignore previous instructions,' hidden-prompt reveal requests, safety-rule bypass, role impersonation, or secret exfiltration) and Layer 2 (a policy gate mapping every proposed tool call, given structured risk evidence including tool name/arguments/normalized semantics/execution-cost estimate/detector results/session taint state, to ALLOW/REVIEW/BLOCK before execution).</t>
         </is>
       </c>
       <c r="F132" s="5" t="n"/>
@@ -7093,7 +7113,7 @@
       <c r="H132" s="5" t="n"/>
       <c r="I132" s="5" t="inlineStr">
         <is>
-          <t>2b73f8dbb2af737fe707df3b2dcb21a9cea62db5</t>
+          <t>4e959fca0e4d91c84b708457efa08b0f729a05ef</t>
         </is>
       </c>
     </row>
@@ -7103,7 +7123,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Manipulating LLM Web Agents with Indirect Prompt Injection Attack via HTML Accessibility Tree</t>
+          <t>LivePI: More Realistic Benchmarking of Agents Against Indirect Prompt Injection</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -7118,7 +7138,7 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>The paper has an explicit 'Limitations' section listing three practical constraints on the attack technique: (1) the attacker must have access to some part of the HTML consumed by the navigation agent; (2) triggers are trained for a particular LLM (or set of LLMs), so agents powered by other/untested LLMs are much less susceptible to a given trigger, as confirmed by the unsuccessful transfer attempts to Llama-2 and Mistral; and (3) triggers are optimized for a specific target output sequence, so they can only exploit a web navigation framework if that target sequence is syntactically valid within the framework's action space -- meaning a closed-source framework that rotates its action-space scheme and does not disclose its underlying LLM would be substantially more resistant to this attack. The paper notes this resistance is currently undermined in practice by the open-source ecosystem's broad adoption and low discretion around LLM-integrated application internals. The Conclusion additionally acknowledges that attack success 'depends on content control and model-specific tuning,' an implicit scope caveat beyond the formal Limitations section.</t>
+          <t>The paper contains an explicit 'Limitations and Discussion' section (Section 6) with five distinct points: (1) the defense policy is deliberately targeted to the attack classes present in LivePI, so results do not constitute a claim of general protection; (2) the defended evaluation is run for the GPT-5.3-Codex configuration only, so additional defended runs across all five backbones would be needed to determine how much of the 0% defended-ASR result is policy-driven versus model-dependent; (3) the repository-link surface has only four executable test cases in the current version of LivePI, so those results should be read as high-severity risk signals rather than precise real-world prevalence estimates; (4) the current presentation reports case-weighted ASR point estimates without confidence intervals, repeated stochastic runs, or decoding-setting sensitivity analysis, all of which would clarify quantitative uncertainty; (5) the benign-utility evaluation uses tasks derived from PinchBench only, so broader workloads and longer-horizon sessions are needed in future work; and (6) outcome grading uses an LLM judge supplemented by deterministic checks, introducing possible judge-model bias and residual grading error, particularly since one evaluated backbone shares a model family with the judge -- future work should add human evaluation, inter-judge agreement analysis, and adversarially audited deterministic checks.</t>
         </is>
       </c>
       <c r="F133" s="5" t="n"/>
@@ -7126,7 +7146,7 @@
       <c r="H133" s="5" t="n"/>
       <c r="I133" s="5" t="inlineStr">
         <is>
-          <t>2b73f8dbb2af737fe707df3b2dcb21a9cea62db5</t>
+          <t>4e959fca0e4d91c84b708457efa08b0f729a05ef</t>
         </is>
       </c>
     </row>
@@ -7136,7 +7156,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Manipulating LLM Web Agents with Indirect Prompt Injection Attack via HTML Accessibility Tree</t>
+          <t>LivePI: More Realistic Benchmarking of Agents Against Indirect Prompt Injection</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -7151,7 +7171,7 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>The paper demonstrates a concrete, practical Indirect Prompt Injection (IPI) attack against LLM-based web navigation agents by embedding optimized adversarial trigger sequences directly into webpage HTML, exploiting the fact that agent frameworks like Browser Gym parse the page's accessibility tree (HTML rendered for readability) into the LLM's prompt alongside the user's task instruction and available action space. Building on the Greedy Coordinate Gradient (GCG) algorithm originally used to induce objectionable outputs from safety-aligned LLMs, the authors adapt trigger optimization to the IPI setting by allowing flexible trigger placement within the HTML portion of the prompt (rather than only as a suffix, since an HTML-only attacker cannot control the full prompt) and by extending the objective to universal optimization across multiple prompt contexts, i.e., minimizing negative log-probability of a fixed target action-response across n different (xpre, xpost) context pairs drawn from different user instructions or different websites, using a NanoGCG-based implementation modified for this multi-context universal-trigger setting. Using Meta's Llama-3.1-8B-Instruct as the target LLM within a Browser Gym web-navigation agent, the authors demonstrate three escalating attack scenarios on real websites: Targeted-Website-Targeted-Instruction (a single trigger for one website/instruction pair, e.g., forcing chess.com's agent to report a fabricated cheating violation, forcing clicks on ad banners or hidden blog links, or forcing a Twitter-follow action), Targeted-Website-Universal-Instruction (one trigger per website that reliably induces the target action regardless of the user's specific navigation goal, tested against 200 varied instructions per site), and Universal-Website-Targeted-Instruction (a single trigger effective across multiple different websites for a fixed high-value goal, specifically credential exfiltration from login pages via a simulated malicious browser-extension modal). Optimization typically completes within several hours under standard GCG hyperparameters, with search-width reduction and target-string-seeded initialization identified empirically as the most effective speedup techniques (reducing completion time to under an hour in many cases), while trigger length and Carlini-Wagner loss showed no measurable speed benefit. The work provides concrete evidence that current LLM-based web agents lack robust defenses against HTML-embedded prompt injection and argues for stronger safeguards such as input sanitization and prompt hardening as agent deployment scales, while responsibly withholding the most sensitive credential-theft demonstration from the public-facing demo.</t>
+          <t>LivePI is a structured benchmark for measuring indirect prompt injection (IPI) risk against real, tool-using AI agents (specifically OpenClaw) in a production-like but test-controlled deployment, addressing a gap the authors identify in prior evaluations that are small, purely simulated, or narrow in channel/goal coverage and therefore miss failures depending on live message provenance, persistent host state, authentication flows, or real tool side effects. The benchmark is organized along three dimensions -- injection surface (7 channels: group chat, email, local docs, repository links, gist, web, and others), attack technique/rendering family (12 families), and malicious goal (5 goals: protected-information exfiltration, unauthorized security-control changes, unsafe code retrieval/execution, inbox-summary exfiltration, cryptocurrency transfer) -- and instantiates 169 executable attack instances across feasible surface-technique-goal combinations, run against a real OpenClaw instance on a virtual machine with live but test-controlled email, chat, web, local-file, repository, and bounded cryptocurrency-wallet interfaces rather than a purely simulated sandbox. After demonstrating that five frontier LLM backbones (GPT-5.3-Codex, Claude Opus 4.6, Gemini 3.1 Pro, Kimi K2.5, GLM-5) all remain substantially vulnerable, with two recurring mechanistic failure modes identified (over-trust of unverified group-chat participants due to a message-role-labeling implementation gap, and susceptibility to injected directives interleaved with legitimate multi-step task execution), the authors design and evaluate a two-layer runtime defense tailored to this setting: a Layer 1 prompt-level detector that pattern-matches suspicious instructions before the agent's base model reads the prompt, and a Layer 2 policy-based gate that maps every proposed tool call to ALLOW/REVIEW/BLOCK using structured risk evidence (tool semantics, execution-cost estimate, detector signals, session taint state) plus environment-specific custom policy rules (e.g., protecting wallet credentials, firewall settings, private documents), evaluated for both security (attack success rate on LivePI) and utility (review/block friction rate on the existing PinchBench benign-workload benchmark) in the GPT-5.3-Codex configuration.</t>
         </is>
       </c>
       <c r="F134" s="5" t="n"/>
@@ -7159,7 +7179,7 @@
       <c r="H134" s="5" t="n"/>
       <c r="I134" s="5" t="inlineStr">
         <is>
-          <t>2b73f8dbb2af737fe707df3b2dcb21a9cea62db5</t>
+          <t>4e959fca0e4d91c84b708457efa08b0f729a05ef</t>
         </is>
       </c>
     </row>
@@ -7169,7 +7189,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Meta SecAlign: A Secure Foundation LLM Against Prompt Injection Attacks</t>
+          <t>Memory as Action: Autonomous Context Curation for Long-Horizon Agentic Tasks</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -7192,7 +7212,7 @@
       <c r="H135" s="5" t="n"/>
       <c r="I135" s="5" t="inlineStr">
         <is>
-          <t>fc3d1be58cc8fe00f15923493a0b59db2c50004c</t>
+          <t>5f0f0c762c094bb6e1deba3222331ee51b98d1fc</t>
         </is>
       </c>
     </row>
@@ -7202,7 +7222,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Meta SecAlign: A Secure Foundation LLM Against Prompt Injection Attacks</t>
+          <t>Memory as Action: Autonomous Context Curation for Long-Horizon Agentic Tasks</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -7217,7 +7237,7 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>ML/AI</t>
         </is>
       </c>
       <c r="F136" s="5" t="n"/>
@@ -7225,7 +7245,7 @@
       <c r="H136" s="5" t="n"/>
       <c r="I136" s="5" t="inlineStr">
         <is>
-          <t>fc3d1be58cc8fe00f15923493a0b59db2c50004c</t>
+          <t>5f0f0c762c094bb6e1deba3222331ee51b98d1fc</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7255,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Meta SecAlign: A Secure Foundation LLM Against Prompt Injection Attacks</t>
+          <t>Memory as Action: Autonomous Context Curation for Long-Horizon Agentic Tasks</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -7258,7 +7278,7 @@
       <c r="H137" s="5" t="n"/>
       <c r="I137" s="5" t="inlineStr">
         <is>
-          <t>fc3d1be58cc8fe00f15923493a0b59db2c50004c</t>
+          <t>5f0f0c762c094bb6e1deba3222331ee51b98d1fc</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7288,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Meta SecAlign: A Secure Foundation LLM Against Prompt Injection Attacks</t>
+          <t>Memory as Action: Autonomous Context Curation for Long-Horizon Agentic Tasks</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -7291,7 +7311,7 @@
       <c r="H138" s="5" t="n"/>
       <c r="I138" s="5" t="inlineStr">
         <is>
-          <t>fc3d1be58cc8fe00f15923493a0b59db2c50004c</t>
+          <t>5f0f0c762c094bb6e1deba3222331ee51b98d1fc</t>
         </is>
       </c>
     </row>
@@ -7301,7 +7321,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Meta SecAlign: A Secure Foundation LLM Against Prompt Injection Attacks</t>
+          <t>Memory as Action: Autonomous Context Curation for Long-Horizon Agentic Tasks</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -7316,7 +7336,7 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>memory</t>
         </is>
       </c>
       <c r="F139" s="5" t="n"/>
@@ -7324,7 +7344,7 @@
       <c r="H139" s="5" t="n"/>
       <c r="I139" s="5" t="inlineStr">
         <is>
-          <t>fc3d1be58cc8fe00f15923493a0b59db2c50004c</t>
+          <t>5f0f0c762c094bb6e1deba3222331ee51b98d1fc</t>
         </is>
       </c>
     </row>
@@ -7334,7 +7354,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Meta SecAlign: A Secure Foundation LLM Against Prompt Injection Attacks</t>
+          <t>Memory as Action: Autonomous Context Curation for Long-Horizon Agentic Tasks</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -7349,7 +7369,7 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>goal-hijack</t>
+          <t>reasoning-corruption</t>
         </is>
       </c>
       <c r="F140" s="5" t="n"/>
@@ -7357,7 +7377,7 @@
       <c r="H140" s="5" t="n"/>
       <c r="I140" s="5" t="inlineStr">
         <is>
-          <t>fc3d1be58cc8fe00f15923493a0b59db2c50004c</t>
+          <t>5f0f0c762c094bb6e1deba3222331ee51b98d1fc</t>
         </is>
       </c>
     </row>
@@ -7367,7 +7387,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Meta SecAlign: A Secure Foundation LLM Against Prompt Injection Attacks</t>
+          <t>Memory as Action: Autonomous Context Curation for Long-Horizon Agentic Tasks</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -7382,7 +7402,7 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F141" s="5" t="n"/>
@@ -7390,7 +7410,7 @@
       <c r="H141" s="5" t="n"/>
       <c r="I141" s="5" t="inlineStr">
         <is>
-          <t>fc3d1be58cc8fe00f15923493a0b59db2c50004c</t>
+          <t>5f0f0c762c094bb6e1deba3222331ee51b98d1fc</t>
         </is>
       </c>
     </row>
@@ -7400,7 +7420,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Meta SecAlign: A Secure Foundation LLM Against Prompt Injection Attacks</t>
+          <t>Memory as Action: Autonomous Context Curation for Long-Horizon Agentic Tasks</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -7415,7 +7435,7 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F142" s="5" t="n"/>
@@ -7423,7 +7443,7 @@
       <c r="H142" s="5" t="n"/>
       <c r="I142" s="5" t="inlineStr">
         <is>
-          <t>fc3d1be58cc8fe00f15923493a0b59db2c50004c</t>
+          <t>5f0f0c762c094bb6e1deba3222331ee51b98d1fc</t>
         </is>
       </c>
     </row>
@@ -7433,7 +7453,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Meta SecAlign: A Secure Foundation LLM Against Prompt Injection Attacks</t>
+          <t>Memory as Action: Autonomous Context Curation for Long-Horizon Agentic Tasks</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -7456,7 +7476,7 @@
       <c r="H143" s="5" t="n"/>
       <c r="I143" s="5" t="inlineStr">
         <is>
-          <t>fc3d1be58cc8fe00f15923493a0b59db2c50004c</t>
+          <t>5f0f0c762c094bb6e1deba3222331ee51b98d1fc</t>
         </is>
       </c>
     </row>
@@ -7466,7 +7486,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Meta SecAlign: A Secure Foundation LLM Against Prompt Injection Attacks</t>
+          <t>Memory as Action: Autonomous Context Curation for Long-Horizon Agentic Tasks</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -7481,7 +7501,7 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>one-shot</t>
+          <t>session-persistent</t>
         </is>
       </c>
       <c r="F144" s="5" t="n"/>
@@ -7489,7 +7509,7 @@
       <c r="H144" s="5" t="n"/>
       <c r="I144" s="5" t="inlineStr">
         <is>
-          <t>fc3d1be58cc8fe00f15923493a0b59db2c50004c</t>
+          <t>5f0f0c762c094bb6e1deba3222331ee51b98d1fc</t>
         </is>
       </c>
     </row>
@@ -7499,7 +7519,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Meta SecAlign: A Secure Foundation LLM Against Prompt Injection Attacks</t>
+          <t>Memory as Action: Autonomous Context Curation for Long-Horizon Agentic Tasks</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -7514,7 +7534,7 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F145" s="5" t="n"/>
@@ -7522,7 +7542,7 @@
       <c r="H145" s="5" t="n"/>
       <c r="I145" s="5" t="inlineStr">
         <is>
-          <t>fc3d1be58cc8fe00f15923493a0b59db2c50004c</t>
+          <t>5f0f0c762c094bb6e1deba3222331ee51b98d1fc</t>
         </is>
       </c>
     </row>
@@ -7532,7 +7552,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Meta SecAlign: A Secure Foundation LLM Against Prompt Injection Attacks</t>
+          <t>Memory as Action: Autonomous Context Curation for Long-Horizon Agentic Tasks</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -7547,7 +7567,7 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>Fully open-sourced code, training recipe, and two model checkpoints: Meta-SecAlign-8B and Meta-SecAlign-70B (fine-tuned from Llama-3.1-8B-Instruct and Llama-3.3-70B-Instruct), released under the Llama 3 community license with public tokenizer.chat_template implementing the new 'input' message role. AgentDojo interaction logs for Llama-3.3-70B-Instruct and Meta-SecAlign-70B are also released for community analysis. Weights had been downloaded 16K times at time of writing.</t>
+          <t>Code and datasets released at https://github.com/ADaM-BJTU/MemAct, including the MemAct SFT/RL training pipeline, the Dynamic Context Policy Optimization (DCPO) implementation, and the multi-objective HotpotQA-based training/evaluation dataset construction.</t>
         </is>
       </c>
       <c r="F146" s="5" t="n"/>
@@ -7555,7 +7575,7 @@
       <c r="H146" s="5" t="n"/>
       <c r="I146" s="5" t="inlineStr">
         <is>
-          <t>fc3d1be58cc8fe00f15923493a0b59db2c50004c</t>
+          <t>5f0f0c762c094bb6e1deba3222331ee51b98d1fc</t>
         </is>
       </c>
     </row>
@@ -7565,7 +7585,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Meta SecAlign: A Secure Foundation LLM Against Prompt Injection Attacks</t>
+          <t>Memory as Action: Autonomous Context Curation for Long-Horizon Agentic Tasks</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -7580,7 +7600,7 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>Llama-3.1-8B-Instruct, Llama-3.1-70B-Instruct, Llama-3.3-70B-Instruct (undefended and SecAlign/SecAlign++ defended), Qwen3-4B-Instruct-2507, and Llama-4-Scout-17B-16E-Instruct (109B MoE, 17B active) to test generality; compared against closed-source GPT-4o-mini, GPT-4o, GPT-5 (high reasoning), Gemini-2-Flash, Gemini-2.5-Flash, and Gemini-3-Pro.</t>
+          <t>Qwen2.5-7B-Instruct and Qwen2.5-14B-Instruct as base models for MemAct (SFT and SFT+RL variants). Compared against Qwen3-235B-A22B-Instruct (full-context upper-bound baseline), Qwen2.5-14B (no-memory-management baseline), Tongyi-DeepResearch (a 30B specialized deep-research RL model), Search-R1 (SFT+RL baseline, effectively MemAct without memory actions), and MEM1 (an RL-based memory-learning baseline), plus non-learned externally-managed baselines Sliding Window, Summarization, and A-MEM.</t>
         </is>
       </c>
       <c r="F147" s="5" t="n"/>
@@ -7588,7 +7608,7 @@
       <c r="H147" s="5" t="n"/>
       <c r="I147" s="5" t="inlineStr">
         <is>
-          <t>fc3d1be58cc8fe00f15923493a0b59db2c50004c</t>
+          <t>5f0f0c762c094bb6e1deba3222331ee51b98d1fc</t>
         </is>
       </c>
     </row>
@@ -7598,7 +7618,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Meta SecAlign: A Secure Foundation LLM Against Prompt Injection Attacks</t>
+          <t>Memory as Action: Autonomous Context Curation for Long-Horizon Agentic Tasks</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -7613,7 +7633,7 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>9 utility benchmarks: MMLU, MMLU-Pro (5-shot), IFEval, BBH (3-shot), GPQA Diamond (general knowledge), AlpacaEval2/AlpacaFarm, SEP (9.1K samples), TaskTracker (31K samples), CyberSecEval2 (instruction following), AgentDojo (97 user tasks, 949 user/injection task pairs, tool-calling), WASP (84 injected samples from WebArena, web navigation), and InjecAgent (1K API-calling samples). Training uses the Cleaned-Alpaca instruction-tuning dataset (19,157 DPO preference samples after filtering for data-containing prompts).</t>
+          <t>A custom multi-objective QA dataset built on HotpotQA (following Zhou et al. 2025's construction method), testing up to 8 sub-objectives per task with 200 samples per level; single-objective benchmarks spanning low-to-high difficulty: 2WikiMultihopQA, HotpotQA, Bamboogle, Frames, and BrowseComp-Plus. Training data combines synthetic SFT trajectories (staged prompting with DeepSeek-V3.1 to induce memory-action usage as context grows past 8K/16K tokens, filtered to only correct-answer trajectories) and an RL dataset drawn from single-objective tasks (via Asearcher) and synthesized multi-objective tasks limited to at most 3 objectives during training, to test generalization to harder (4-8 objective) tasks at inference. Evaluation metrics: Task Accuracy (LLM-judge-based, three-pass consensus), Solved Sub-objective Count, total token consumption, and tool-call frequency.</t>
         </is>
       </c>
       <c r="F148" s="5" t="n"/>
@@ -7621,7 +7641,7 @@
       <c r="H148" s="5" t="n"/>
       <c r="I148" s="5" t="inlineStr">
         <is>
-          <t>fc3d1be58cc8fe00f15923493a0b59db2c50004c</t>
+          <t>5f0f0c762c094bb6e1deba3222331ee51b98d1fc</t>
         </is>
       </c>
     </row>
@@ -7631,7 +7651,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Meta SecAlign: A Secure Foundation LLM Against Prompt Injection Attacks</t>
+          <t>Memory as Action: Autonomous Context Curation for Long-Horizon Agentic Tasks</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -7646,7 +7666,7 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>Meta-SecAlign-70B achieves 6.4% ASR on SEP instruction-following PIs, 1.9% ASR on AgentDojo tool-calling PIs, 0% End2End ASR on WASP web navigation, and 0.5% ASR on InjecAgent (down from 53.8% undefended), representing one-to-two orders of magnitude ASR reduction versus the undefended Llama-3.3-70B-Instruct baseline with only ~2% max utility drop (IFEval, GPQA Diamond). It matches or beats GPT-5 and Gemini-3-Pro on several agentic security benchmarks despite being fully open-weight, and outperforms GPT-4o-mini on all 3 comparable general-knowledge benchmarks. On adaptive attacks (Table 6), SecAlign++ cuts AlpacaFarm Basic Adaptive ASR from 6.7% (SecAlign) to 0.5% and SEP Basic Adaptive ASR from 18.9% to 6.4% on the 70B model.</t>
+          <t>MemAct-RL-14B achieves the highest multi-objective accuracy (59.1% average across 2/4/6/8-objective tasks) among all compared methods, outperforming the 16x larger Qwen3-235B (53.1%/0.531 avg) and the specialized Tongyi-DeepResearch (56.0%), while using an average context of only 3,500 tokens per step (about 50% shorter than Qwen3-235B, 60% shorter than Search-R1-14B) and total token cost of 8.2x10^4 (51% lower than Qwen3-235B's 16.7x10^4, 57% lower than Search-R1-14B's 19.3x10^4). MemAct variants occupy the Pareto frontier of accuracy vs. context efficiency (Figure 3/Table 1). RL training over SFT substantially improves multi-objective accuracy (0.485 to 0.591), and a rigid Fixed-Interval memory-update baseline underperforms learned MemAct especially on complex 8-objective tasks, showing static schedules delete critical information at the wrong times. MemAct-RL generalizes well beyond its training distribution (trained on &lt;=3 objectives) to 8-objective tasks, achieving 54.3% accuracy versus Search-R1's 39.3%, and generalizes to the unfamiliar BrowseComp-Plus web corpus. Latency measurements on 2,000 trajectories (SGLang) show MemAct-RL-7B reduces total inference duration by 40% versus Search-R1 despite making more tool calls (28.9 vs. 23.5), due to smaller average context size improving prefix-cache hit rate and avoiding auxiliary summarization inference passes used by methods like A-MEM. Analysis reveals model-size-dependent emergent strategies: the 7B model learns coarse-grained pruning (~6 records/action) to manage its limited capacity, while the 14B model learns a bimodal strategy mixing fine-grained (~2 records) pruning during active reasoning with coarse-grained (~6 records) pruning once sub-objectives complete.</t>
         </is>
       </c>
       <c r="F149" s="5" t="n"/>
@@ -7654,7 +7674,7 @@
       <c r="H149" s="5" t="n"/>
       <c r="I149" s="5" t="inlineStr">
         <is>
-          <t>fc3d1be58cc8fe00f15923493a0b59db2c50004c</t>
+          <t>5f0f0c762c094bb6e1deba3222331ee51b98d1fc</t>
         </is>
       </c>
     </row>
@@ -7664,7 +7684,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Meta SecAlign: A Secure Foundation LLM Against Prompt Injection Attacks</t>
+          <t>Memory as Action: Autonomous Context Curation for Long-Horizon Agentic Tasks</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -7679,7 +7699,7 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>Primary baseline is the prior SoTA SecAlign (Chen et al.) recipe, which SecAlign++ modifies with two techniques: randomized injection position (vs. SecAlign's fixed end-of-data injection, which causes shortcut learning/empty outputs) and self-generated responses from the initialization LLM (vs. SecAlign's low-quality TEXT_DAVINCI_003-labeled and out-of-distribution GPT-4o/GPT-5-labeled responses). Also compared against undefended Llama-3.3-70B-Instruct and six closed-source commercial models with built-in model-level PI defenses (GPT-4o-mini, GPT-4o, GPT-5, Gemini-2-Flash, Gemini-2.5-Flash, Gemini-3-Pro).</t>
+          <t>Full-context baseline (Qwen3-235B-A22B-Instruct, no memory pruning, performance upper bound); externally-managed heuristic strategies (Sliding Window: keeps only most recent 8K tokens; Summarization: sliding window plus self-generated summary of discarded content; A-MEM: dynamically-linked interconnected memory network); and learning-based agents (MEM1, an RL baseline that also learns memory actions; Tongyi-DeepResearch, a 30B specialized deep-research RL model; Search-R1, MemAct's own pipeline but without the memory-action capability, serving as the key ablation isolating the contribution of learned memory management). A Fixed Update variant of MemAct itself (static 5-turn memory-update interval) serves as an additional ablation against the learned policy.</t>
         </is>
       </c>
       <c r="F150" s="5" t="n"/>
@@ -7687,7 +7707,7 @@
       <c r="H150" s="5" t="n"/>
       <c r="I150" s="5" t="inlineStr">
         <is>
-          <t>fc3d1be58cc8fe00f15923493a0b59db2c50004c</t>
+          <t>5f0f0c762c094bb6e1deba3222331ee51b98d1fc</t>
         </is>
       </c>
     </row>
@@ -7697,7 +7717,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Meta SecAlign: A Secure Foundation LLM Against Prompt Injection Attacks</t>
+          <t>Memory as Action: Autonomous Context Curation for Long-Horizon Agentic Tasks</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -7712,7 +7732,7 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>Indirect prompt injection: the system, user, and LLM provider are benign/trusted, but the environment (retrieved data, tool outputs, web content) is malicious and contains injected instructions that attempt to override the user's original task. Attacker is assumed to know the benign prompt and LLM's prompt template but cannot alter them directly. Adaptive/white-box attacks are also considered, including embedding-space fake-delimiter escape attacks and GCG gradient-based suffix optimization, assuming attacker access to model embeddings/gradients. Explicitly out of scope: jailbreaks and direct prompt injection (malicious user-supplied instructions).</t>
+          <t>N/A - non-adversarial. This is a capability/efficiency paper on reinforcement-learning-based working-memory management for long-horizon LLM agents; there is no adversary. The incidental failure mode addressed is attention dilution and 'lost-in-the-middle' behavior from unmanaged, ever-growing context, and the risk (explicitly acknowledged in the Limitations section) that the learned pruning policy may accidentally delete information that only becomes relevant later in a long-horizon task, since memory compression is inherently lossy and irreversible.</t>
         </is>
       </c>
       <c r="F151" s="5" t="n"/>
@@ -7720,7 +7740,7 @@
       <c r="H151" s="5" t="n"/>
       <c r="I151" s="5" t="inlineStr">
         <is>
-          <t>fc3d1be58cc8fe00f15923493a0b59db2c50004c</t>
+          <t>5f0f0c762c094bb6e1deba3222331ee51b98d1fc</t>
         </is>
       </c>
     </row>
@@ -7730,7 +7750,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Meta SecAlign: A Secure Foundation LLM Against Prompt Injection Attacks</t>
+          <t>Memory as Action: Autonomous Context Curation for Long-Horizon Agentic Tasks</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -7745,7 +7765,7 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>The paper has an explicit Section 5.2 Limitations: the work only defends against indirect PIs (benign user, malicious environment) and cannot prevent jailbreaks or direct prompt injections. Despite strong performance against static attacks, the model remains vulnerable to strong adaptive attacks (demonstrated in Table 6, GCG ASR still 20-47%), meaning the PI threat is 'far from being solved.' The authors also note an unexplained anomaly where AgentDojo utility increases after SecAlign++ fine-tuning specifically for Llama-3.3-70B (not observed in other model families), attributing it to unknown post-training details rather than a general property of the method.</t>
+          <t>The paper has an explicit 'Limitations' section (Section 6) identifying three issues: (1) the framework relies on sparse, final-outcome-only rewards, making it difficult to accurately assign credit to specific memory actions, and in long-horizon tasks the model might accidentally delete information that only becomes relevant later -- though the authors note their analysis suggests an intrinsic coupling between memory behavior and reasoning that could eventually help address this credit-assignment problem; (2) the current DCPO optimization uses a random trajectory-segment sampling algorithm that treats all memory operations as equally important, since no posterior method is yet used to identify which steps are most informative, which may limit training efficiency in complex scenarios; (3) regarding information fidelity, working memory management involves an inherent trade-off between context length and density -- because the Prune&amp;Write compression process is lossy, the system cannot recover original data once details are summarized/discarded, meaning local memory cannot maintain infinite precision. The authors frame this last limitation as defining the boundary of the current study (which focuses on verifying the core memory-action mechanism within the standard context window) and suggest future work could reduce compression lossiness by expanding the action space to include selective retrieval from external stores or tiered caching, combining learned curation with scalable high-precision infrastructure.</t>
         </is>
       </c>
       <c r="F152" s="5" t="n"/>
@@ -7753,7 +7773,7 @@
       <c r="H152" s="5" t="n"/>
       <c r="I152" s="5" t="inlineStr">
         <is>
-          <t>fc3d1be58cc8fe00f15923493a0b59db2c50004c</t>
+          <t>5f0f0c762c094bb6e1deba3222331ee51b98d1fc</t>
         </is>
       </c>
     </row>
@@ -7763,7 +7783,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Meta SecAlign: A Secure Foundation LLM Against Prompt Injection Attacks</t>
+          <t>Memory as Action: Autonomous Context Curation for Long-Horizon Agentic Tasks</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -7778,7 +7798,7 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>This paper introduces SecAlign++, an improved model-level defensive fine-tuning recipe against prompt injection, and releases Meta-SecAlign-8B/70B as the first fully open-source, commercial-grade LLMs with built-in PI robustness. Building on SecAlign's chat-template approach (a new 'input' role separating untrusted data from trusted instructions, fine-tuned via DPO on simulated injections), the authors identify two failure modes in the original SecAlign recipe -- shortcut learning from always-terminal injection placement, and low-quality/out-of-distribution training labels -- and fix them via randomized injection position (45% start, 45% end, 10% completion-attack) and self-generated response labels from the initialization model itself. Evaluated across 9 utility and 7 security benchmarks spanning general knowledge, instruction following, and agentic tool-calling/web-navigation workflows, Meta-SecAlign-70B achieves near-zero PI attack success rates while incurring negligible utility loss, establishing what the authors call a new open-source utility-security Pareto frontier competitive with proprietary defended models like GPT-5 and Gemini-3-Pro. The recipe generalizes beyond Llama to Qwen3-4B and Llama-4-Scout-17B-16E, and the paper additionally shows LoRA-alpha can be tuned post-hoc at inference time to interpolate the utility-security trade-off without retraining.</t>
+          <t>MemAct (Memory-as-Action) reframes working memory management for long-horizon LLM agents as a set of learnable policy actions rather than an externally-imposed heuristic mechanism (e.g., fixed sliding windows, rule-based summarization, or separately-controlled memory systems), enabling end-to-end joint optimization of information retention and task performance via reinforcement learning. The framework formalizes the agent's interaction as an MDP where the state is a working memory of uniquely ID-addressable interaction records, and the action space is augmented to include both standard task actions and a unified 'Prune&amp;Write' memory operator that, in a single function call, specifies which historical turn IDs to remove and synthesizes new memory content (summaries, reflections, or plans) that is appended in-place and remains addressable for future edits. Because this in-place editing breaks the causal, monotonically-growing-context assumption underlying standard autoregressive policy-gradient training (deleted content has already influenced the KV-cache representations of subsequent tokens, and naive attention masking cannot resolve this since production inference engines assume monotonic context growth), the authors introduce Dynamic Context Policy Optimization (DCPO), which logically segments each generated trajectory at every memory-edit point into independent (context-prefix, token-sequence) segments with locally-consistent causal structure, computes a single trajectory-level GRPO-style group-relative advantage from a sparse terminal reward (positive for task success, negative for constraint violations like exceeding context/step limits), and attributes this advantage to sampled segments via a round-robin strategy, restoring compatibility with standard, efficient RL training infrastructure. Trained in two stages (SFT initialization via DeepSeek-V3.1-synthesized memory-action trajectories, followed by DCPO-based RL) on Qwen2.5-7B/14B-Instruct backbones, MemAct is evaluated on single- and multi-objective long-horizon QA benchmarks (built on HotpotQA, 2WikiMultihopQA, Bamboogle, Frames, BrowseComp-Plus), where MemAct-RL-14B matches or exceeds the accuracy of the 16x-larger Qwen3-235B while cutting average context length roughly in half and total token cost by over 50%, generalizes from training on at most 3-objective tasks to strong performance on unseen 8-objective tasks, and exhibits model-size-dependent, autonomously discovered pruning granularity strategies.</t>
         </is>
       </c>
       <c r="F153" s="5" t="n"/>
@@ -7786,7 +7806,7 @@
       <c r="H153" s="5" t="n"/>
       <c r="I153" s="5" t="inlineStr">
         <is>
-          <t>fc3d1be58cc8fe00f15923493a0b59db2c50004c</t>
+          <t>5f0f0c762c094bb6e1deba3222331ee51b98d1fc</t>
         </is>
       </c>
     </row>
@@ -7796,7 +7816,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>RAG-Induced Failures in Multi-Agent Large Language Model Debate</t>
+          <t>PhantomLint: Principled Detection of Hidden LLM Prompts in Structured Documents</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -7819,7 +7839,7 @@
       <c r="H154" s="5" t="n"/>
       <c r="I154" s="5" t="inlineStr">
         <is>
-          <t>4f6bc1797993f1ff1ddb1fccb9111bc424fa2242</t>
+          <t>5717e2bd544b999c678c6199e844f790459f7327</t>
         </is>
       </c>
     </row>
@@ -7829,7 +7849,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>RAG-Induced Failures in Multi-Agent Large Language Model Debate</t>
+          <t>PhantomLint: Principled Detection of Hidden LLM Prompts in Structured Documents</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -7852,7 +7872,7 @@
       <c r="H155" s="5" t="n"/>
       <c r="I155" s="5" t="inlineStr">
         <is>
-          <t>4f6bc1797993f1ff1ddb1fccb9111bc424fa2242</t>
+          <t>5717e2bd544b999c678c6199e844f790459f7327</t>
         </is>
       </c>
     </row>
@@ -7862,7 +7882,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>RAG-Induced Failures in Multi-Agent Large Language Model Debate</t>
+          <t>PhantomLint: Principled Detection of Hidden LLM Prompts in Structured Documents</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -7885,7 +7905,7 @@
       <c r="H156" s="5" t="n"/>
       <c r="I156" s="5" t="inlineStr">
         <is>
-          <t>4f6bc1797993f1ff1ddb1fccb9111bc424fa2242</t>
+          <t>5717e2bd544b999c678c6199e844f790459f7327</t>
         </is>
       </c>
     </row>
@@ -7895,7 +7915,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>RAG-Induced Failures in Multi-Agent Large Language Model Debate</t>
+          <t>PhantomLint: Principled Detection of Hidden LLM Prompts in Structured Documents</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -7910,7 +7930,7 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>attack</t>
+          <t>defense</t>
         </is>
       </c>
       <c r="F157" s="5" t="n"/>
@@ -7918,7 +7938,7 @@
       <c r="H157" s="5" t="n"/>
       <c r="I157" s="5" t="inlineStr">
         <is>
-          <t>4f6bc1797993f1ff1ddb1fccb9111bc424fa2242</t>
+          <t>5717e2bd544b999c678c6199e844f790459f7327</t>
         </is>
       </c>
     </row>
@@ -7928,7 +7948,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>RAG-Induced Failures in Multi-Agent Large Language Model Debate</t>
+          <t>PhantomLint: Principled Detection of Hidden LLM Prompts in Structured Documents</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -7943,7 +7963,7 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>RAG</t>
+          <t>cross-modal</t>
         </is>
       </c>
       <c r="F158" s="5" t="n"/>
@@ -7951,7 +7971,7 @@
       <c r="H158" s="5" t="n"/>
       <c r="I158" s="5" t="inlineStr">
         <is>
-          <t>4f6bc1797993f1ff1ddb1fccb9111bc424fa2242</t>
+          <t>5717e2bd544b999c678c6199e844f790459f7327</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7981,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>RAG-Induced Failures in Multi-Agent Large Language Model Debate</t>
+          <t>PhantomLint: Principled Detection of Hidden LLM Prompts in Structured Documents</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -7976,7 +7996,7 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>goal-hijack</t>
         </is>
       </c>
       <c r="F159" s="5" t="n"/>
@@ -7984,7 +8004,7 @@
       <c r="H159" s="5" t="n"/>
       <c r="I159" s="5" t="inlineStr">
         <is>
-          <t>4f6bc1797993f1ff1ddb1fccb9111bc424fa2242</t>
+          <t>5717e2bd544b999c678c6199e844f790459f7327</t>
         </is>
       </c>
     </row>
@@ -7994,7 +8014,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>RAG-Induced Failures in Multi-Agent Large Language Model Debate</t>
+          <t>PhantomLint: Principled Detection of Hidden LLM Prompts in Structured Documents</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -8009,7 +8029,7 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F160" s="5" t="n"/>
@@ -8017,7 +8037,7 @@
       <c r="H160" s="5" t="n"/>
       <c r="I160" s="5" t="inlineStr">
         <is>
-          <t>4f6bc1797993f1ff1ddb1fccb9111bc424fa2242</t>
+          <t>5717e2bd544b999c678c6199e844f790459f7327</t>
         </is>
       </c>
     </row>
@@ -8027,7 +8047,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>RAG-Induced Failures in Multi-Agent Large Language Model Debate</t>
+          <t>PhantomLint: Principled Detection of Hidden LLM Prompts in Structured Documents</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -8050,7 +8070,7 @@
       <c r="H161" s="5" t="n"/>
       <c r="I161" s="5" t="inlineStr">
         <is>
-          <t>4f6bc1797993f1ff1ddb1fccb9111bc424fa2242</t>
+          <t>5717e2bd544b999c678c6199e844f790459f7327</t>
         </is>
       </c>
     </row>
@@ -8060,7 +8080,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>RAG-Induced Failures in Multi-Agent Large Language Model Debate</t>
+          <t>PhantomLint: Principled Detection of Hidden LLM Prompts in Structured Documents</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -8075,7 +8095,7 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>ingestion</t>
         </is>
       </c>
       <c r="F162" s="5" t="n"/>
@@ -8083,7 +8103,7 @@
       <c r="H162" s="5" t="n"/>
       <c r="I162" s="5" t="inlineStr">
         <is>
-          <t>4f6bc1797993f1ff1ddb1fccb9111bc424fa2242</t>
+          <t>5717e2bd544b999c678c6199e844f790459f7327</t>
         </is>
       </c>
     </row>
@@ -8093,7 +8113,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>RAG-Induced Failures in Multi-Agent Large Language Model Debate</t>
+          <t>PhantomLint: Principled Detection of Hidden LLM Prompts in Structured Documents</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -8116,7 +8136,7 @@
       <c r="H163" s="5" t="n"/>
       <c r="I163" s="5" t="inlineStr">
         <is>
-          <t>4f6bc1797993f1ff1ddb1fccb9111bc424fa2242</t>
+          <t>5717e2bd544b999c678c6199e844f790459f7327</t>
         </is>
       </c>
     </row>
@@ -8126,7 +8146,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>RAG-Induced Failures in Multi-Agent Large Language Model Debate</t>
+          <t>PhantomLint: Principled Detection of Hidden LLM Prompts in Structured Documents</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -8149,7 +8169,7 @@
       <c r="H164" s="5" t="n"/>
       <c r="I164" s="5" t="inlineStr">
         <is>
-          <t>4f6bc1797993f1ff1ddb1fccb9111bc424fa2242</t>
+          <t>5717e2bd544b999c678c6199e844f790459f7327</t>
         </is>
       </c>
     </row>
@@ -8159,7 +8179,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>RAG-Induced Failures in Multi-Agent Large Language Model Debate</t>
+          <t>PhantomLint: Principled Detection of Hidden LLM Prompts in Structured Documents</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -8172,13 +8192,17 @@
           <t>secondary</t>
         </is>
       </c>
-      <c r="E165" s="2" t="n"/>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>Y - open source tool at https://github.com/tobycmurray/phantom-lint</t>
+        </is>
+      </c>
       <c r="F165" s="5" t="n"/>
       <c r="G165" s="5" t="n"/>
       <c r="H165" s="5" t="n"/>
       <c r="I165" s="5" t="inlineStr">
         <is>
-          <t>4f6bc1797993f1ff1ddb1fccb9111bc424fa2242</t>
+          <t>5717e2bd544b999c678c6199e844f790459f7327</t>
         </is>
       </c>
     </row>
@@ -8188,7 +8212,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>RAG-Induced Failures in Multi-Agent Large Language Model Debate</t>
+          <t>PhantomLint: Principled Detection of Hidden LLM Prompts in Structured Documents</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -8203,7 +8227,7 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>GPT-4o and GPT-3.5 as debating agents.</t>
+          <t>None - PhantomLint is not LLM-based; it compares document text extraction (PyMuPDF/HTML) against OCR of the rendered region using a static bad-phrases list, so no LLM is evaluated</t>
         </is>
       </c>
       <c r="F166" s="5" t="n"/>
@@ -8211,7 +8235,7 @@
       <c r="H166" s="5" t="n"/>
       <c r="I166" s="5" t="inlineStr">
         <is>
-          <t>4f6bc1797993f1ff1ddb1fccb9111bc424fa2242</t>
+          <t>5717e2bd544b999c678c6199e844f790459f7327</t>
         </is>
       </c>
     </row>
@@ -8221,7 +8245,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>RAG-Induced Failures in Multi-Agent Large Language Model Debate</t>
+          <t>PhantomLint: Principled Detection of Hidden LLM Prompts in Structured Documents</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -8236,7 +8260,7 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>MMLU - general knowledge across 57 academic subjects spanning STEM, humanities, social sciences, law and medicine, 14,042 multiple-choice questions.</t>
+          <t>26 author-built synthetic documents (16 PDF, 10 HTML) spanning the known text-hiding methods; all 3,257 accepted ICML 2025 papers from OpenReview (false-positive corpus); 119 curated real-world documents containing LLM prompts (113 hidden/positive, 6 visible/negative; 93 PDF, 26 HTML; CVs, arXiv preprints, theses, a book chapter, blogs, one email). 3,402 documents total.</t>
         </is>
       </c>
       <c r="F167" s="5" t="n"/>
@@ -8244,7 +8268,7 @@
       <c r="H167" s="5" t="n"/>
       <c r="I167" s="5" t="inlineStr">
         <is>
-          <t>4f6bc1797993f1ff1ddb1fccb9111bc424fa2242</t>
+          <t>5717e2bd544b999c678c6199e844f790459f7327</t>
         </is>
       </c>
     </row>
@@ -8254,7 +8278,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>RAG-Induced Failures in Multi-Agent Large Language Model Debate</t>
+          <t>PhantomLint: Principled Detection of Hidden LLM Prompts in Structured Documents</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -8269,7 +8293,7 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>The honest-agent assumption behind multi-agent debate fails under a realistic threat model: a single malicious agent manipulating RAG to selectively retrieve plausible but misleading external evidence degrades final majority-vote accuracy. Impact is quantified as delta-Accuracy against a no-attack baseline, with the paper noting that even strong models such as GPT-4o are affected.</t>
+          <t>PhantomLint detected the hidden prompt in all 26 synthetic documents across every hiding method tested (white text, invisible OCG ViewState /OFF, text render mode 3, off-CropBox and off-MediaBox placement, malicious blank-glyph fonts, HTML hidden visibility), and in all 113 real hidden-prompt documents, with no alarms on the 6 visible-prompt negatives. On 3,257 ICML 2025 papers it raised only 3 alarms, all OCR-failure false positives, giving a false-positive rate of approximately 0.092%. Mean runtime was 68.25 s per ICML paper and 43.75 s per real-world document.</t>
         </is>
       </c>
       <c r="F168" s="5" t="n"/>
@@ -8277,7 +8301,7 @@
       <c r="H168" s="5" t="n"/>
       <c r="I168" s="5" t="inlineStr">
         <is>
-          <t>4f6bc1797993f1ff1ddb1fccb9111bc424fa2242</t>
+          <t>5717e2bd544b999c678c6199e844f790459f7327</t>
         </is>
       </c>
     </row>
@@ -8287,7 +8311,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>RAG-Induced Failures in Multi-Agent Large Language Model Debate</t>
+          <t>PhantomLint: Principled Detection of Hidden LLM Prompts in Structured Documents</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -8302,7 +8326,7 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>A no-attack debate baseline, against debates containing one RAG-manipulating malicious agent.</t>
+          <t>None - no competing detector is run head-to-head; the paper argues analytically that text-only prompt-injection detectors cannot distinguish visible from hidden instructions and so must produce false alarms, and it reimplements Xiong et al.'s malicious-font hiding method as an attack to defeat rather than as a defense baseline.</t>
         </is>
       </c>
       <c r="F169" s="5" t="n"/>
@@ -8310,7 +8334,7 @@
       <c r="H169" s="5" t="n"/>
       <c r="I169" s="5" t="inlineStr">
         <is>
-          <t>4f6bc1797993f1ff1ddb1fccb9111bc424fa2242</t>
+          <t>5717e2bd544b999c678c6199e844f790459f7327</t>
         </is>
       </c>
     </row>
@@ -8320,7 +8344,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>RAG-Induced Failures in Multi-Agent Large Language Model Debate</t>
+          <t>PhantomLint: Principled Detection of Hidden LLM Prompts in Structured Documents</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -8335,7 +8359,7 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>Multi-agent LLM debate where most agents are honest but one is adversarial. The malicious agent does not lie directly; it manipulates retrieval so that the evidence it introduces is externally sourced and plausible, exploiting the aggregation step rather than the model.</t>
+          <t>A document author embeds LLM instructions in a PDF or HTML document so that they are invisible to a human reader but recovered by text extraction, in order to manipulate an LLM-assisted document-processing pipeline (peer review, resume screening, summarisation). The adversary controls document content and the hiding technique, is assumed to keep inventing new hiding methods, and the defender is the party ingesting untrusted documents.</t>
         </is>
       </c>
       <c r="F170" s="5" t="n"/>
@@ -8343,7 +8367,7 @@
       <c r="H170" s="5" t="n"/>
       <c r="I170" s="5" t="inlineStr">
         <is>
-          <t>4f6bc1797993f1ff1ddb1fccb9111bc424fa2242</t>
+          <t>5717e2bd544b999c678c6199e844f790459f7327</t>
         </is>
       </c>
     </row>
@@ -8353,7 +8377,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>RAG-Induced Failures in Multi-Agent Large Language Model Debate</t>
+          <t>PhantomLint: Principled Detection of Hidden LLM Prompts in Structured Documents</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -8368,7 +8392,7 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>Not explicitly stated as a limitations section. Evaluation is confined to MMLU multiple-choice and to two OpenAI models.</t>
+          <t>The authors note the detector works best when the suspicious text is short and occupies a tight visual region, since the OCR consistency test must isolate the smallest region containing it. They also report that the diffing implementation may not recover the entire hidden prompt and may highlight adjacent non-words such as punctuation or numbers, and that residual false positives are driven by OCR failures on non-English characters and very small fonts.</t>
         </is>
       </c>
       <c r="F171" s="5" t="n"/>
@@ -8376,7 +8400,7 @@
       <c r="H171" s="5" t="n"/>
       <c r="I171" s="5" t="inlineStr">
         <is>
-          <t>4f6bc1797993f1ff1ddb1fccb9111bc424fa2242</t>
+          <t>5717e2bd544b999c678c6199e844f790459f7327</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8410,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>RAG-Induced Failures in Multi-Agent Large Language Model Debate</t>
+          <t>PhantomLint: Principled Detection of Hidden LLM Prompts in Structured Documents</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -8401,7 +8425,7 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>An attack paper showing that collaborative-debate frameworks inherit a trust assumption they never state: aggregating diverse reasoning trajectories improves accuracy only while every participant retrieves honestly, and one RAG-manipulating participant is enough to move the majority vote.</t>
+          <t>Proposes the first hiding-method-agnostic detector for hidden LLM prompts in structured documents, framed as a metamorphic test. Applies an ANALYZE step that flags text spans resembling LLM instructions, then an OCR consistency test that renders the minimal document region containing the suspicious block, OCRs it, and treats text present in extraction but absent from OCR as evidence of hiding; a detection requires the intersection of suspicious and hidden spans to be non-empty. Implements this in the PhantomLint prototype for PDF and HTML. Evaluates generality on 26 synthetic documents covering seven hiding techniques, false-positive rate on 3,257 ICML 2025 papers, practical utility on 119 curated real documents, and runtime.</t>
         </is>
       </c>
       <c r="F172" s="5" t="n"/>
@@ -8409,7 +8433,7 @@
       <c r="H172" s="5" t="n"/>
       <c r="I172" s="5" t="inlineStr">
         <is>
-          <t>4f6bc1797993f1ff1ddb1fccb9111bc424fa2242</t>
+          <t>5717e2bd544b999c678c6199e844f790459f7327</t>
         </is>
       </c>
     </row>
@@ -8419,7 +8443,7 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>A Novel Evaluation Framework for Assessing Resilience Against Prompt Injection Attacks in Large Language Models</t>
+          <t>Can Indirect Prompt Injection Attacks Be Detected and Removed?</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -8442,7 +8466,7 @@
       <c r="H173" s="5" t="n"/>
       <c r="I173" s="5" t="inlineStr">
         <is>
-          <t>ce17ea81f018c51e02c68861e55a2d2b07f25285</t>
+          <t>20723b734e2838c22f921a0fc343d32e1d6d84e7</t>
         </is>
       </c>
     </row>
@@ -8452,7 +8476,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>A Novel Evaluation Framework for Assessing Resilience Against Prompt Injection Attacks in Large Language Models</t>
+          <t>Can Indirect Prompt Injection Attacks Be Detected and Removed?</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -8475,7 +8499,7 @@
       <c r="H174" s="5" t="n"/>
       <c r="I174" s="5" t="inlineStr">
         <is>
-          <t>ce17ea81f018c51e02c68861e55a2d2b07f25285</t>
+          <t>20723b734e2838c22f921a0fc343d32e1d6d84e7</t>
         </is>
       </c>
     </row>
@@ -8485,7 +8509,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>A Novel Evaluation Framework for Assessing Resilience Against Prompt Injection Attacks in Large Language Models</t>
+          <t>Can Indirect Prompt Injection Attacks Be Detected and Removed?</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
@@ -8508,7 +8532,7 @@
       <c r="H175" s="5" t="n"/>
       <c r="I175" s="5" t="inlineStr">
         <is>
-          <t>ce17ea81f018c51e02c68861e55a2d2b07f25285</t>
+          <t>20723b734e2838c22f921a0fc343d32e1d6d84e7</t>
         </is>
       </c>
     </row>
@@ -8518,7 +8542,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>A Novel Evaluation Framework for Assessing Resilience Against Prompt Injection Attacks in Large Language Models</t>
+          <t>Can Indirect Prompt Injection Attacks Be Detected and Removed?</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
@@ -8533,7 +8557,7 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>neither</t>
+          <t>defense</t>
         </is>
       </c>
       <c r="F176" s="5" t="n"/>
@@ -8541,7 +8565,7 @@
       <c r="H176" s="5" t="n"/>
       <c r="I176" s="5" t="inlineStr">
         <is>
-          <t>ce17ea81f018c51e02c68861e55a2d2b07f25285</t>
+          <t>20723b734e2838c22f921a0fc343d32e1d6d84e7</t>
         </is>
       </c>
     </row>
@@ -8551,7 +8575,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>A Novel Evaluation Framework for Assessing Resilience Against Prompt Injection Attacks in Large Language Models</t>
+          <t>Can Indirect Prompt Injection Attacks Be Detected and Removed?</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
@@ -8574,7 +8598,7 @@
       <c r="H177" s="5" t="n"/>
       <c r="I177" s="5" t="inlineStr">
         <is>
-          <t>ce17ea81f018c51e02c68861e55a2d2b07f25285</t>
+          <t>20723b734e2838c22f921a0fc343d32e1d6d84e7</t>
         </is>
       </c>
     </row>
@@ -8584,7 +8608,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>A Novel Evaluation Framework for Assessing Resilience Against Prompt Injection Attacks in Large Language Models</t>
+          <t>Can Indirect Prompt Injection Attacks Be Detected and Removed?</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
@@ -8607,7 +8631,7 @@
       <c r="H178" s="5" t="n"/>
       <c r="I178" s="5" t="inlineStr">
         <is>
-          <t>ce17ea81f018c51e02c68861e55a2d2b07f25285</t>
+          <t>20723b734e2838c22f921a0fc343d32e1d6d84e7</t>
         </is>
       </c>
     </row>
@@ -8617,7 +8641,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>A Novel Evaluation Framework for Assessing Resilience Against Prompt Injection Attacks in Large Language Models</t>
+          <t>Can Indirect Prompt Injection Attacks Be Detected and Removed?</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
@@ -8640,7 +8664,7 @@
       <c r="H179" s="5" t="n"/>
       <c r="I179" s="5" t="inlineStr">
         <is>
-          <t>ce17ea81f018c51e02c68861e55a2d2b07f25285</t>
+          <t>20723b734e2838c22f921a0fc343d32e1d6d84e7</t>
         </is>
       </c>
     </row>
@@ -8650,7 +8674,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>A Novel Evaluation Framework for Assessing Resilience Against Prompt Injection Attacks in Large Language Models</t>
+          <t>Can Indirect Prompt Injection Attacks Be Detected and Removed?</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
@@ -8673,7 +8697,7 @@
       <c r="H180" s="5" t="n"/>
       <c r="I180" s="5" t="inlineStr">
         <is>
-          <t>ce17ea81f018c51e02c68861e55a2d2b07f25285</t>
+          <t>20723b734e2838c22f921a0fc343d32e1d6d84e7</t>
         </is>
       </c>
     </row>
@@ -8683,7 +8707,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>A Novel Evaluation Framework for Assessing Resilience Against Prompt Injection Attacks in Large Language Models</t>
+          <t>Can Indirect Prompt Injection Attacks Be Detected and Removed?</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
@@ -8698,7 +8722,7 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>ingestion</t>
         </is>
       </c>
       <c r="F181" s="5" t="n"/>
@@ -8706,7 +8730,7 @@
       <c r="H181" s="5" t="n"/>
       <c r="I181" s="5" t="inlineStr">
         <is>
-          <t>ce17ea81f018c51e02c68861e55a2d2b07f25285</t>
+          <t>20723b734e2838c22f921a0fc343d32e1d6d84e7</t>
         </is>
       </c>
     </row>
@@ -8716,7 +8740,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>A Novel Evaluation Framework for Assessing Resilience Against Prompt Injection Attacks in Large Language Models</t>
+          <t>Can Indirect Prompt Injection Attacks Be Detected and Removed?</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
@@ -8739,7 +8763,7 @@
       <c r="H182" s="5" t="n"/>
       <c r="I182" s="5" t="inlineStr">
         <is>
-          <t>ce17ea81f018c51e02c68861e55a2d2b07f25285</t>
+          <t>20723b734e2838c22f921a0fc343d32e1d6d84e7</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8773,7 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>A Novel Evaluation Framework for Assessing Resilience Against Prompt Injection Attacks in Large Language Models</t>
+          <t>Can Indirect Prompt Injection Attacks Be Detected and Removed?</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
@@ -8764,7 +8788,7 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F183" s="5" t="n"/>
@@ -8772,7 +8796,7 @@
       <c r="H183" s="5" t="n"/>
       <c r="I183" s="5" t="inlineStr">
         <is>
-          <t>ce17ea81f018c51e02c68861e55a2d2b07f25285</t>
+          <t>20723b734e2838c22f921a0fc343d32e1d6d84e7</t>
         </is>
       </c>
     </row>
@@ -8782,7 +8806,7 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>A Novel Evaluation Framework for Assessing Resilience Against Prompt Injection Attacks in Large Language Models</t>
+          <t>Can Indirect Prompt Injection Attacks Be Detected and Removed?</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
@@ -8797,7 +8821,7 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>No code, dataset, or model release is mentioned. The 115-attack dataset constructed for this study, the impact-evaluation prompts, and the testbed software architecture (Figure 2) are described conceptually but not released as a public repository or downloadable artifact.</t>
+          <t>Y - code publicly available at https://github.com/LukeChen-go/indirect-pia-detection</t>
         </is>
       </c>
       <c r="F184" s="5" t="n"/>
@@ -8805,7 +8829,7 @@
       <c r="H184" s="5" t="n"/>
       <c r="I184" s="5" t="inlineStr">
         <is>
-          <t>ce17ea81f018c51e02c68861e55a2d2b07f25285</t>
+          <t>20723b734e2838c22f921a0fc343d32e1d6d84e7</t>
         </is>
       </c>
     </row>
@@ -8815,7 +8839,7 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>A Novel Evaluation Framework for Assessing Resilience Against Prompt Injection Attacks in Large Language Models</t>
+          <t>Can Indirect Prompt Injection Attacks Be Detected and Removed?</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
@@ -8830,7 +8854,7 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>Five LLMs used during attack-dataset construction to compute the Relevance Ratio (ChatGPT, Azure OpenAI GPT-3.5 Turbo, GPT-4, Bard, and ChatGLM), and two LLM-integrated applications used for the main resilience evaluation: ChatGLM (6.2B parameters, released March 2022, Tsinghua University's GLM framework) and Llama2 (13B parameters, released July 2023, Meta AI). ChatGPT is separately used as the 'LLM evaluator' that scores attack response impact.</t>
+          <t>Detection/removal backbones: Llama3-8B-Instruct, Qwen2-7B-Instruct, Llama3.1-8B-Instruct as instructed-LLM detectors; Llama-Guard3-8B, Protect-AI-detection, Prompt-Guard as open-source detectors; DeBERTa and Qwen2-1.5B/0.5B trained as custom detection/extraction/segmentation models; StruQ reproduced as a fine-tuning defense baseline.</t>
         </is>
       </c>
       <c r="F185" s="5" t="n"/>
@@ -8838,7 +8862,7 @@
       <c r="H185" s="5" t="n"/>
       <c r="I185" s="5" t="inlineStr">
         <is>
-          <t>ce17ea81f018c51e02c68861e55a2d2b07f25285</t>
+          <t>20723b734e2838c22f921a0fc343d32e1d6d84e7</t>
         </is>
       </c>
     </row>
@@ -8848,7 +8872,7 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>A Novel Evaluation Framework for Assessing Resilience Against Prompt Injection Attacks in Large Language Models</t>
+          <t>Can Indirect Prompt Injection Attacks Be Detected and Removed?</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
@@ -8863,7 +8887,7 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>A custom-constructed attack dataset of 115 prompt injection attacks, curated from literature review and online sources and filtered via a Relevance Ratio metric (an attack is included only if it succeeds against at least 20% of the 5 LLMs it was tested on), categorized into four attack-purpose classes: Manipulated Content, Fraud, Harm and Destruction, and Misinformation, each with its own purpose-specific impact factors (e.g., Hate/Harassment/Self-harm/Sexual/Violence for Manipulated Content; Personalization/Convincingness/Consistency/Fluency for Fraud). No external public benchmark is used; the dataset and evaluation metrics (AIM, ASP, WRS) are the paper's own contribution.</t>
+          <t>Introduces Inj-SQuAD and Inj-TriviaQA, two benchmarks of 900 samples each built from SQuAD and TriviaQA validation data with diverse injected instructions at head/middle/tail positions; also constructs dedicated detection and removal training datasets; attack baselines are Naive, Ignore, Escape-Character, Fake-completion and Combined attacks (from Perez &amp; Ribeiro, Breitenbach et al., Willison, and Liu et al.).</t>
         </is>
       </c>
       <c r="F186" s="5" t="n"/>
@@ -8871,7 +8895,7 @@
       <c r="H186" s="5" t="n"/>
       <c r="I186" s="5" t="inlineStr">
         <is>
-          <t>ce17ea81f018c51e02c68861e55a2d2b07f25285</t>
+          <t>20723b734e2838c22f921a0fc343d32e1d6d84e7</t>
         </is>
       </c>
     </row>
@@ -8881,7 +8905,7 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>A Novel Evaluation Framework for Assessing Resilience Against Prompt Injection Attacks in Large Language Models</t>
+          <t>Can Indirect Prompt Injection Attacks Be Detected and Removed?</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
@@ -8896,7 +8920,7 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>Llama2 achieved a Weighted Resilience Score (WRS) of 67.3 (average Attack Success Probability of 33.91%), substantially outperforming ChatGLM's WRS of 38.2 (average ASP of 68.87%) -- meaning attacks succeeded roughly twice as often against ChatGLM as against Llama2. The authors attribute Llama2's higher resilience to its larger parameter count/training data and more recent release incorporating updated safety safeguards, and interpret this result as validating the framework's ability to produce a resilience ranking consistent with the general expectation that newer models are more resilient to known attacks.</t>
+          <t>A trained DeBERTa detector plus a Qwen2-1.5B extraction/segmentation removal pipeline (combined as a 'filtering' defense) generally outperforms prior prompt-engineering defenses (Sandwich, Instructional) and the fine-tuning defense StruQ on the Inj-TriviaQA benchmark, though all methods trained only on the Naive attack generalize poorly to the Fake-completion attack; the extraction removal method achieves removal rates of at least 94.66% for tail-positioned injections (the most effective attack position) but drops to a maximum of 67.77% for head/middle positions, and existing off-the-shelf detectors (including instructed LLMs and open-source guard models) struggle to reliably detect indirect injections, especially with over-defense and position-generalization problems.</t>
         </is>
       </c>
       <c r="F187" s="5" t="n"/>
@@ -8904,7 +8928,7 @@
       <c r="H187" s="5" t="n"/>
       <c r="I187" s="5" t="inlineStr">
         <is>
-          <t>ce17ea81f018c51e02c68861e55a2d2b07f25285</t>
+          <t>20723b734e2838c22f921a0fc343d32e1d6d84e7</t>
         </is>
       </c>
     </row>
@@ -8914,7 +8938,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>A Novel Evaluation Framework for Assessing Resilience Against Prompt Injection Attacks in Large Language Models</t>
+          <t>Can Indirect Prompt Injection Attacks Be Detected and Removed?</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
@@ -8929,7 +8953,7 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>No prior evaluation frameworks or defense mechanisms are directly benchmarked against; the paper's own two-application case study (ChatGLM vs. Llama2) serves as the demonstration of the proposed Weighted Resilience Score (WRS) framework's discriminative validity, essentially using the two models as comparative baselines for each other.</t>
+          <t>Attack baselines: Naive, Ignore, Escape-Character, Fake-completion, Combined attacks. Defense baselines: prompt-engineering-based Sandwich and Instructional defenses, and the fine-tuning-based StruQ defense, all compared against the paper's own detection models and its segmentation/extraction removal methods and their combined filtering pipeline.</t>
         </is>
       </c>
       <c r="F188" s="5" t="n"/>
@@ -8937,7 +8961,7 @@
       <c r="H188" s="5" t="n"/>
       <c r="I188" s="5" t="inlineStr">
         <is>
-          <t>ce17ea81f018c51e02c68861e55a2d2b07f25285</t>
+          <t>20723b734e2838c22f921a0fc343d32e1d6d84e7</t>
         </is>
       </c>
     </row>
@@ -8947,7 +8971,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>A Novel Evaluation Framework for Assessing Resilience Against Prompt Injection Attacks in Large Language Models</t>
+          <t>Can Indirect Prompt Injection Attacks Be Detected and Removed?</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
@@ -8962,7 +8986,7 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>Informal, direct prompt injection threat model: the attacker submits crafted text prompts directly to an LLM-integrated application (chatbot/virtual assistant) with the goal of manipulating it into producing unintended, harmful, or policy-violating outputs across four objective categories (generating manipulated/toxic content, enabling fraud, causing harm and destruction, or spreading misinformation), rather than exfiltrating data or hijacking downstream tool/agent actions. No formal attacker capability tiers or system access assumptions are specified; the framework assumes only that the attacker can submit prompts to the target application and observe its responses.</t>
+          <t>An attacker plants injected instructions inside external documents (e.g., search-engine results or retrieved passages) that an LLM-integrated QA/RAG system will read, at varying positions (head, middle, tail) within the document, using one of several known injection technique families; the defender must detect that a document contains an injection and then remove or neutralize the injected content before it reaches the LLM's context, without degrading answer quality on clean documents.</t>
         </is>
       </c>
       <c r="F189" s="5" t="n"/>
@@ -8970,7 +8994,7 @@
       <c r="H189" s="5" t="n"/>
       <c r="I189" s="5" t="inlineStr">
         <is>
-          <t>ce17ea81f018c51e02c68861e55a2d2b07f25285</t>
+          <t>20723b734e2838c22f921a0fc343d32e1d6d84e7</t>
         </is>
       </c>
     </row>
@@ -8980,7 +9004,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>A Novel Evaluation Framework for Assessing Resilience Against Prompt Injection Attacks in Large Language Models</t>
+          <t>Can Indirect Prompt Injection Attacks Be Detected and Removed?</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
@@ -8995,7 +9019,7 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>The paper has no section explicitly titled 'Limitations,' but includes an explicit 'Future Work' section (Section VI) that functions as an implicit limitations discussion: it states that new prompt injection attacks are discovered every month and that many of these newer attacks are not included in the 115-attack dataset used in this study, positioning dataset currency/coverage as an acknowledged gap; it also notes the framework would need extension (new attack categories and correspondingly new impact factors) to keep pace with emerging attack techniques, implying the current framework's coverage is a snapshot rather than a comprehensive or future-proof evaluation.</t>
+          <t>The authors state existing models (both general-purpose instructed LLMs and open-source detectors) struggle to reliably detect indirect prompt injection attacks, that training detection/removal models faces challenges including over-defense on clean documents and poor generalization across injection positions, that removal methods still leave room for improvement (extraction removal is weak against head/middle-positioned injections), and that defenses trained only on the Naive attack generalize poorly to the Fake-completion attack.</t>
         </is>
       </c>
       <c r="F190" s="5" t="n"/>
@@ -9003,7 +9027,7 @@
       <c r="H190" s="5" t="n"/>
       <c r="I190" s="5" t="inlineStr">
         <is>
-          <t>ce17ea81f018c51e02c68861e55a2d2b07f25285</t>
+          <t>20723b734e2838c22f921a0fc343d32e1d6d84e7</t>
         </is>
       </c>
     </row>
@@ -9013,7 +9037,7 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>A Novel Evaluation Framework for Assessing Resilience Against Prompt Injection Attacks in Large Language Models</t>
+          <t>Can Indirect Prompt Injection Attacks Be Detected and Removed?</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
@@ -9028,7 +9052,7 @@
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>This paper proposes a general-purpose, quantitative evaluation framework for measuring how resilient an LLM-integrated application is against prompt injection attacks, structured into three phases. First, an attack dataset is constructed by consolidating known attack techniques (payload splitting, obfuscation, 'ignore previous prompt,' character role-play, indirect prompt injection, etc.) from literature and online sources, then filtered for relevance using a Relevance Ratio metric that requires each attack to succeed against at least 20% of a panel of five tested LLMs (ChatGPT, Azure GPT-3.5 Turbo, GPT-4, Bard, ChatGLM), yielding a curated set of 115 attacks spanning four attack-purpose categories (Manipulated Content, Fraud, Harm and Destruction, Misinformation). Second, an Average Impact Metric (AIM) is computed per attack by simulating it against the target application and having a second 'evaluator' LLM (ChatGPT) score the response's severity (0-5) across several purpose-specific impact factors (e.g., toxicity sub-dimensions for Manipulated Content, or personalization/convincingness/consistency/fluency for Fraud), producing both a numeric score and a natural-language explanation for interpretability, unlike conventional binary malicious-content classifiers. Third, each attack is repeated multiple times (5 attempts at temperature 0.7, top-P 1.0) against the target application to compute an Attack Success Probability (ASP), and the per-attack AIM and ASP values are combined into a single Weighted Resilience Score (WRS, 0-100 scale) that weights higher-impact attacks more heavily, giving organizations a standardized, repeatable benchmark for comparing the security posture of different LLM-integrated applications. The framework is demonstrated by evaluating two real applications built on ChatGLM and Llama2, with Llama2 scoring substantially more resilient (WRS 67.3 vs. 38.2), and the authors emphasize the framework's extensibility, noting new attack techniques or purpose categories can be incorporated by adding entries to the attack dataset and defining new corresponding impact factors.</t>
+          <t>Investigates whether indirect prompt injection attacks embedded in externally retrieved documents can be detected and subsequently removed, rather than only prevented at generation time. Constructs two new benchmarks (Inj-SQuAD, Inj-TriviaQA) with diverse injected instructions at multiple positions, evaluates existing instructed-LLM and open-source detectors, trains custom detection models, and proposes two removal methods, a segmentation-removal approach that deletes document segments flagged as containing injections and an extraction-removal approach that trains a model to identify and excise the injected span. Combines the best detection and removal components into a unified filtering defense and shows it outperforms prior prompt-engineering (Sandwich, Instructional) and fine-tuning (StruQ) baselines on Inj-TriviaQA, while identifying persistent weaknesses around injection position and cross-attack generalization. Matters as a systematic empirical study specifically of the post-detection removal step for indirect injection, a stage prior work largely neglects in favor of detection or prevention alone.</t>
         </is>
       </c>
       <c r="F191" s="5" t="n"/>
@@ -9036,7 +9060,7 @@
       <c r="H191" s="5" t="n"/>
       <c r="I191" s="5" t="inlineStr">
         <is>
-          <t>ce17ea81f018c51e02c68861e55a2d2b07f25285</t>
+          <t>20723b734e2838c22f921a0fc343d32e1d6d84e7</t>
         </is>
       </c>
     </row>
@@ -9046,7 +9070,7 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>PlanFlip: Attacking Multi-Agent LLM Systems via Planning-Phase Prompt Injection</t>
+          <t>Adaptive Chameleon or Stubborn Sloth: Revealing the Behavior of Large Language Models in Knowledge Conflicts</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
@@ -9069,7 +9093,7 @@
       <c r="H192" s="5" t="n"/>
       <c r="I192" s="5" t="inlineStr">
         <is>
-          <t>36dd2ed29b677eff1f4689a18040d3fae5c4278a</t>
+          <t>10f829a80a7ee0cdb16307f04e206133d75f81da</t>
         </is>
       </c>
     </row>
@@ -9079,7 +9103,7 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>PlanFlip: Attacking Multi-Agent LLM Systems via Planning-Phase Prompt Injection</t>
+          <t>Adaptive Chameleon or Stubborn Sloth: Revealing the Behavior of Large Language Models in Knowledge Conflicts</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
@@ -9094,7 +9118,7 @@
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>ML/AI</t>
         </is>
       </c>
       <c r="F193" s="5" t="n"/>
@@ -9102,7 +9126,7 @@
       <c r="H193" s="5" t="n"/>
       <c r="I193" s="5" t="inlineStr">
         <is>
-          <t>36dd2ed29b677eff1f4689a18040d3fae5c4278a</t>
+          <t>10f829a80a7ee0cdb16307f04e206133d75f81da</t>
         </is>
       </c>
     </row>
@@ -9112,7 +9136,7 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>PlanFlip: Attacking Multi-Agent LLM Systems via Planning-Phase Prompt Injection</t>
+          <t>Adaptive Chameleon or Stubborn Sloth: Revealing the Behavior of Large Language Models in Knowledge Conflicts</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
@@ -9135,7 +9159,7 @@
       <c r="H194" s="5" t="n"/>
       <c r="I194" s="5" t="inlineStr">
         <is>
-          <t>36dd2ed29b677eff1f4689a18040d3fae5c4278a</t>
+          <t>10f829a80a7ee0cdb16307f04e206133d75f81da</t>
         </is>
       </c>
     </row>
@@ -9145,7 +9169,7 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>PlanFlip: Attacking Multi-Agent LLM Systems via Planning-Phase Prompt Injection</t>
+          <t>Adaptive Chameleon or Stubborn Sloth: Revealing the Behavior of Large Language Models in Knowledge Conflicts</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
@@ -9160,7 +9184,7 @@
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>neither</t>
         </is>
       </c>
       <c r="F195" s="5" t="n"/>
@@ -9168,7 +9192,7 @@
       <c r="H195" s="5" t="n"/>
       <c r="I195" s="5" t="inlineStr">
         <is>
-          <t>36dd2ed29b677eff1f4689a18040d3fae5c4278a</t>
+          <t>10f829a80a7ee0cdb16307f04e206133d75f81da</t>
         </is>
       </c>
     </row>
@@ -9178,7 +9202,7 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>PlanFlip: Attacking Multi-Agent LLM Systems via Planning-Phase Prompt Injection</t>
+          <t>Adaptive Chameleon or Stubborn Sloth: Revealing the Behavior of Large Language Models in Knowledge Conflicts</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
@@ -9193,7 +9217,7 @@
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>multi-agent</t>
+          <t>RAG</t>
         </is>
       </c>
       <c r="F196" s="5" t="n"/>
@@ -9201,7 +9225,7 @@
       <c r="H196" s="5" t="n"/>
       <c r="I196" s="5" t="inlineStr">
         <is>
-          <t>36dd2ed29b677eff1f4689a18040d3fae5c4278a</t>
+          <t>10f829a80a7ee0cdb16307f04e206133d75f81da</t>
         </is>
       </c>
     </row>
@@ -9211,7 +9235,7 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>PlanFlip: Attacking Multi-Agent LLM Systems via Planning-Phase Prompt Injection</t>
+          <t>Adaptive Chameleon or Stubborn Sloth: Revealing the Behavior of Large Language Models in Knowledge Conflicts</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
@@ -9226,7 +9250,7 @@
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>goal-hijack</t>
+          <t>silent-corruption</t>
         </is>
       </c>
       <c r="F197" s="5" t="n"/>
@@ -9234,7 +9258,7 @@
       <c r="H197" s="5" t="n"/>
       <c r="I197" s="5" t="inlineStr">
         <is>
-          <t>36dd2ed29b677eff1f4689a18040d3fae5c4278a</t>
+          <t>10f829a80a7ee0cdb16307f04e206133d75f81da</t>
         </is>
       </c>
     </row>
@@ -9244,7 +9268,7 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>PlanFlip: Attacking Multi-Agent LLM Systems via Planning-Phase Prompt Injection</t>
+          <t>Adaptive Chameleon or Stubborn Sloth: Revealing the Behavior of Large Language Models in Knowledge Conflicts</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
@@ -9259,7 +9283,7 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F198" s="5" t="n"/>
@@ -9267,7 +9291,7 @@
       <c r="H198" s="5" t="n"/>
       <c r="I198" s="5" t="inlineStr">
         <is>
-          <t>36dd2ed29b677eff1f4689a18040d3fae5c4278a</t>
+          <t>10f829a80a7ee0cdb16307f04e206133d75f81da</t>
         </is>
       </c>
     </row>
@@ -9277,7 +9301,7 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>PlanFlip: Attacking Multi-Agent LLM Systems via Planning-Phase Prompt Injection</t>
+          <t>Adaptive Chameleon or Stubborn Sloth: Revealing the Behavior of Large Language Models in Knowledge Conflicts</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
@@ -9292,7 +9316,7 @@
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F199" s="5" t="n"/>
@@ -9300,7 +9324,7 @@
       <c r="H199" s="5" t="n"/>
       <c r="I199" s="5" t="inlineStr">
         <is>
-          <t>36dd2ed29b677eff1f4689a18040d3fae5c4278a</t>
+          <t>10f829a80a7ee0cdb16307f04e206133d75f81da</t>
         </is>
       </c>
     </row>
@@ -9310,7 +9334,7 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>PlanFlip: Attacking Multi-Agent LLM Systems via Planning-Phase Prompt Injection</t>
+          <t>Adaptive Chameleon or Stubborn Sloth: Revealing the Behavior of Large Language Models in Knowledge Conflicts</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
@@ -9333,7 +9357,7 @@
       <c r="H200" s="5" t="n"/>
       <c r="I200" s="5" t="inlineStr">
         <is>
-          <t>36dd2ed29b677eff1f4689a18040d3fae5c4278a</t>
+          <t>10f829a80a7ee0cdb16307f04e206133d75f81da</t>
         </is>
       </c>
     </row>
@@ -9343,7 +9367,7 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>PlanFlip: Attacking Multi-Agent LLM Systems via Planning-Phase Prompt Injection</t>
+          <t>Adaptive Chameleon or Stubborn Sloth: Revealing the Behavior of Large Language Models in Knowledge Conflicts</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
@@ -9366,7 +9390,7 @@
       <c r="H201" s="5" t="n"/>
       <c r="I201" s="5" t="inlineStr">
         <is>
-          <t>36dd2ed29b677eff1f4689a18040d3fae5c4278a</t>
+          <t>10f829a80a7ee0cdb16307f04e206133d75f81da</t>
         </is>
       </c>
     </row>
@@ -9376,7 +9400,7 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>PlanFlip: Attacking Multi-Agent LLM Systems via Planning-Phase Prompt Injection</t>
+          <t>Adaptive Chameleon or Stubborn Sloth: Revealing the Behavior of Large Language Models in Knowledge Conflicts</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
@@ -9391,7 +9415,7 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F202" s="5" t="n"/>
@@ -9399,7 +9423,7 @@
       <c r="H202" s="5" t="n"/>
       <c r="I202" s="5" t="inlineStr">
         <is>
-          <t>36dd2ed29b677eff1f4689a18040d3fae5c4278a</t>
+          <t>10f829a80a7ee0cdb16307f04e206133d75f81da</t>
         </is>
       </c>
     </row>
@@ -9409,7 +9433,7 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>PlanFlip: Attacking Multi-Agent LLM Systems via Planning-Phase Prompt Injection</t>
+          <t>Adaptive Chameleon or Stubborn Sloth: Revealing the Behavior of Large Language Models in Knowledge Conflicts</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
@@ -9424,7 +9448,7 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>No code/artifact release found. No GitHub, HuggingFace, or project-page URL for the paper's own PlanFlip implementation appears in the extracted text (references to CrewAI's GitHub are citations of third-party framework infrastructure, not the paper's own release).</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F203" s="5" t="n"/>
@@ -9432,7 +9456,7 @@
       <c r="H203" s="5" t="n"/>
       <c r="I203" s="5" t="inlineStr">
         <is>
-          <t>36dd2ed29b677eff1f4689a18040d3fae5c4278a</t>
+          <t>10f829a80a7ee0cdb16307f04e206133d75f81da</t>
         </is>
       </c>
     </row>
@@ -9442,7 +9466,7 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>PlanFlip: Attacking Multi-Agent LLM Systems via Planning-Phase Prompt Injection</t>
+          <t>Adaptive Chameleon or Stubborn Sloth: Revealing the Behavior of Large Language Models in Knowledge Conflicts</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
@@ -9457,7 +9481,7 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>Nine frontier LLMs spanning diverse families, capability levels, and reasoning styles: Qwen-Plus, DeepSeek-V3.1, DeepSeek-R1 (reasoning model), GPT-4o, GPT-5, Grok-3, o1 (reasoning model), Llama-3.3-70B, and Llama-4-Maverick. In each episode, all three pipeline roles (Planner, Executor, Critic) use the same backbone model (homogeneous pipeline), the configuration the paper argues is dominant in current production multi-agent frameworks (AutoGen, MetaGPT, CrewAI).</t>
+          <t>Closed-source: ChatGPT (gpt-3.5-turbo-0301), GPT-4 (gpt-4-0314), PaLM2 (chat-bison-001); Open-source: Qwen-7B, Llama2-7B, Llama2-70B, Vicuna-7B, Vicuna-33B</t>
         </is>
       </c>
       <c r="F204" s="5" t="n"/>
@@ -9465,7 +9489,7 @@
       <c r="H204" s="5" t="n"/>
       <c r="I204" s="5" t="inlineStr">
         <is>
-          <t>36dd2ed29b677eff1f4689a18040d3fae5c4278a</t>
+          <t>10f829a80a7ee0cdb16307f04e206133d75f81da</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9499,7 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>PlanFlip: Attacking Multi-Agent LLM Systems via Planning-Phase Prompt Injection</t>
+          <t>Adaptive Chameleon or Stubborn Sloth: Revealing the Behavior of Large Language Models in Knowledge Conflicts</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
@@ -9490,7 +9514,7 @@
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>No pre-existing benchmark; the authors' own evaluation harness spans four realistic agentic task scenarios (finance_report, medical_info, code_assist, travel_plan), each with a benign goal condition plus the four PlanFlip attack configurations (4 scenarios x 5 conditions = 20 cells per model), totaling 3,479 episodes across nine models with 95% Wilson confidence intervals for ASR/Stealth and 95% bootstrap confidence intervals (2,000 resamples) for GDS/StepShift metrics.</t>
+          <t>PopQA (14K entity-centric Wikidata-derived QA questions, with a popularity metric based on Wikipedia page views); StrategyQA (multi-step implicit-reasoning True/False QA); the paper's own newly constructed parametric-memory / counter-memory pairs (generated via an 8-LLM elicitation-and-generation pipeline, filtered by DeBERTa-V2-XXLarge-MNLI entailment checking (99% manually-verified accuracy) and answer-consistency checking) layered on top of both base datasets - final dataset sizes range from 3,787 to 9,544 examples per model on PopQA and 500-1,356 on StrategyQA</t>
         </is>
       </c>
       <c r="F205" s="5" t="n"/>
@@ -9498,7 +9522,7 @@
       <c r="H205" s="5" t="n"/>
       <c r="I205" s="5" t="inlineStr">
         <is>
-          <t>36dd2ed29b677eff1f4689a18040d3fae5c4278a</t>
+          <t>10f829a80a7ee0cdb16307f04e206133d75f81da</t>
         </is>
       </c>
     </row>
@@ -9508,7 +9532,7 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>PlanFlip: Attacking Multi-Agent LLM Systems via Planning-Phase Prompt Injection</t>
+          <t>Adaptive Chameleon or Stubborn Sloth: Revealing the Behavior of Large Language Models in Knowledge Conflicts</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
@@ -9523,7 +9547,7 @@
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>Across 3,479 episodes and nine frontier LLMs, GPT-5 achieved the highest overall attack success rate (ASR = 0.68), exceeding Qwen-Plus (0.57) and Grok-3 (0.41) -- directly contradicting the assumption that more capable models are inherently more secure, since stronger instruction-following makes models more compliant with well-crafted planning-phase injections. Four distinct vulnerability profiles emerged: overt (high ASR, low Stealth, e.g., Qwen-Plus), mixed (attack-dependent, e.g., DeepSeek-V3.1 showing ASR 0.86-1.00 under GoalSubstitution/PF-1 but ASR=0.00 with Stealth=1.00 under PF-2/PF-3/PF-4), blind-spot (low ASR but high Stealth, GPT-4o and Llama-3.3-70B), and resistant (DeepSeek-R1, the reasoning model, achieving StepShift=0.00 across all attacks with zero vulnerability). The paper's central finding is the 'correlated-agent blind spot': GPT-4o and Llama-3.3-70B showed ASR near 0 yet Stealth=1.00 with StepShift &gt; 0, meaning the same-backbone Critic reported the corrupted plan as 'aligned' even though the plan had been measurably restructured; two independent heterogeneous judges (DeepSeek-V3.1 and Llama-3.3-70B, neither sharing a backbone with the attacked pipeline in the cross-check) confirmed statistically significant semantic deviations of -0.20 to -0.32 (r=0.943 agreement between judges), proving the attack succeeded invisibly even though the same-backbone self-audit reported no problem. The paper's proposed defenses, GoalAnchorCheck (D1, verifying each sub-task against the stated goal) and CrossAgentConsensus (D2, comparing against a heterogeneous reference planner with a different backbone), achieved detection rates (DR) up to 1.00 and outperformed same-backbone self-critique baselines in 15 of 16 evaluated cells; critically, prior same-backbone self-critique defenses collapsed to DR=0.00 specifically on the blind-spot models (GPT-4o, Llama-3.3-70B), and only the heterogeneous D2 reference planner broke this correlated failure mode, empirically validating the paper's formal claim (Eq. 2) that a heterogeneous critic can detect deviations a same-backbone critic structurally cannot. D1 and D2 were shown to be complementary, with D1 excelling at explicit goal substitution (DR=1.00 on several models) and D2 recovering detection specifically where D1 alone left a residual gap (DR=0.71-0.89 for GPT-4o, DR=1.00 for Llama-3.3-70B).</t>
+          <t>In the single-source evidence setting (counter-memory as the only evidence presented), LLMs are highly receptive to conflicting external evidence when it is coherent and convincing - the vast majority of models flip to the counter-answer once given the paper's generation-based counter-memory (e.g. ChatGPT shifts from mostly memory-answer under heuristic entity-substitution counter-memory to overwhelmingly counter-answer under generated counter-memory), contradicting prior work's conclusion that LLMs are 'stubborn.' In the multi-source setting (both parametric-consistent and conflicting evidence present, as with search-engine-augmented LLMs), models instead show a strong confirmation bias toward their own parametric memory, which intensifies substantially for more popular/well-known entities (e.g. GPT-4 reaches an 80% memorization ratio for the most popular PopQA questions); most models (except GPT-4) show pronounced sensitivity to the order evidence is presented in, with memorization-ratio swings exceeding 30% for PaLM2 and Llama2-7B depending on whether parametric memory or counter-memory appears first; models generally 'follow the herd,' answering according to whichever side (memory-consistent vs. counter) has the numerically greater share of supporting evidence, with confirmation bias becoming more pronounced as the proportion of parametric-memory-aligned evidence increases (GPT-4 and Vicuna-33B are comparatively the least receptive to counter-memory across all evidence proportions); and when irrelevant evidence (unrelated retrieved passages) is mixed in, LLMs - especially the smaller Llama2-7B - can be distracted into producing irrelevant or uncertain answers, an effect that worsens as the amount of irrelevant evidence increases, though models retain a partial (diminishing) ability to filter out irrelevant evidence when genuinely relevant evidence is also present.</t>
         </is>
       </c>
       <c r="F206" s="5" t="n"/>
@@ -9531,7 +9555,7 @@
       <c r="H206" s="5" t="n"/>
       <c r="I206" s="5" t="inlineStr">
         <is>
-          <t>36dd2ed29b677eff1f4689a18040d3fae5c4278a</t>
+          <t>10f829a80a7ee0cdb16307f04e206133d75f81da</t>
         </is>
       </c>
     </row>
@@ -9541,7 +9565,7 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>PlanFlip: Attacking Multi-Agent LLM Systems via Planning-Phase Prompt Injection</t>
+          <t>Adaptive Chameleon or Stubborn Sloth: Revealing the Behavior of Large Language Models in Knowledge Conflicts</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
@@ -9556,7 +9580,7 @@
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>Same-backbone self-critique (the standard Critic-in-the-loop pipeline configuration used in production multi-agent frameworks, shown to structurally fail via the correlated-agent blind spot, collapsing to DR=0.00 on the blind-spot models GPT-4o and Llama-3.3-70B). Ablation configurations A1 (full pipeline with Critic and defenses), A2 (no Critic, no defenses), and A3 (Critic only, no D1/D2) isolate the individual contribution of the Critic versus the paper's own D1 (GoalAnchorCheck) and D2 (CrossAgentConsensus) defenses.</t>
+          <t>Entity-substitution-based counter-memory construction (a heuristic method from prior work, replacing the ground-truth answer entity with a same-type entity) compared against the paper's proposed generation-based counter-memory construction (instructing an LLM to write a coherent, factually-conflicting passage from scratch); single-source vs. multi-source evidence-presentation settings; parametric-memory-first vs. counter-memory-first vs. randomized evidence order; varying quantitative proportions of parametric-memory-aligned to counter-memory evidence (0/2 through 2/2); with vs. without irrelevant (unrelated) evidence mixed into the context</t>
         </is>
       </c>
       <c r="F207" s="5" t="n"/>
@@ -9564,7 +9588,7 @@
       <c r="H207" s="5" t="n"/>
       <c r="I207" s="5" t="inlineStr">
         <is>
-          <t>36dd2ed29b677eff1f4689a18040d3fae5c4278a</t>
+          <t>10f829a80a7ee0cdb16307f04e206133d75f81da</t>
         </is>
       </c>
     </row>
@@ -9574,7 +9598,7 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>PlanFlip: Attacking Multi-Agent LLM Systems via Planning-Phase Prompt Injection</t>
+          <t>Adaptive Chameleon or Stubborn Sloth: Revealing the Behavior of Large Language Models in Knowledge Conflicts</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
@@ -9589,7 +9613,7 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>Formal, explicit adversarial threat model (Section 3.1), modeling a three-agent pipeline M=(P,E,C): a Planner P maps a goal g and context x to an ordered plan pi=[s1,...,sn]; an Executor E maps each sub-task to an output; a Critic C produces a verdict (aligned/drifted/unsafe) plus a deviation score. In a homogeneous pipeline (the dominant real-world pattern), all three roles share the same backbone theta. The adversary controls a context injection epsilon appended to the Planner's input before plan generation, arriving via any untrusted channel (a retrieved document, tool-call response, or malicious webpage), under black-box access only; the adversary's formal objective is to find the injection that maximizes goal deviation while causing the Critic to still report 'aligned' (Eq. 1). The paper formally defines 'Cascade Amplification' (Definition 1): unlike a tool-call injection targeting a single step (which can affect at most a 1/n fraction of the plan), a successful planning-phase injection can corrupt all n downstream sub-tasks simultaneously (StepShift/kappa up to 1.0), since it corrupts the plan before any execution begins. The paper also formally defines the 'Correlated-Agent Blind Spot' (Definition 2): a homogeneous pipeline exhibits this blind spot when an injection induces real goal deviation yet the same-backbone Critic still reports the corrupted plan as aligned, because the injection simultaneously shifts the conditional output distribution of both the Planner and Critic through their shared parameter space theta -- a single perturbation exploiting the identical representational bias in both roles. Four attack types are instantiated targeting the three inputs of plan generation: PF-1 GoalSubstitution (replaces the objective g), PF-2 PriorityInversion (reorders sub-task precedence), PF-3 ContextPollution, and PF-4 RoleConfusion, each disguised as a plausible tool output specifically to evade keyword-based filters.</t>
+          <t>Explicitly non-adversarial in its main experimental design (the paper studies general LLM receptiveness and bias when reconciling internal parametric memory with any conflicting external evidence, not a crafted attack), but the authors explicitly motivate the study with a security-relevant question raised in the introduction: 'what if a third-party tool, either by the developer or hijacked by attackers, intentionally returns disinformation? Will LLMs be deceived?' - and the single-source-evidence finding (LLMs are highly receptive to coherent, LLM-generated counter-memory even when it conflicts with their own internal knowledge) is explicitly framed as demonstrating that LLMs may be easily deceived by disinformation injected via a compromised or malicious tool/retriever, without formally defining attacker capabilities, access, or a specific attack methodology beyond generic conflicting-evidence injection.</t>
         </is>
       </c>
       <c r="F208" s="5" t="n"/>
@@ -9597,7 +9621,7 @@
       <c r="H208" s="5" t="n"/>
       <c r="I208" s="5" t="inlineStr">
         <is>
-          <t>36dd2ed29b677eff1f4689a18040d3fae5c4278a</t>
+          <t>10f829a80a7ee0cdb16307f04e206133d75f81da</t>
         </is>
       </c>
     </row>
@@ -9607,7 +9631,7 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>PlanFlip: Attacking Multi-Agent LLM Systems via Planning-Phase Prompt Injection</t>
+          <t>Adaptive Chameleon or Stubborn Sloth: Revealing the Behavior of Large Language Models in Knowledge Conflicts</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
@@ -9622,7 +9646,7 @@
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>No dedicated 'Limitations' section appears in the main paper body (the Conclusion transitions directly into References), but the paper's NeurIPS-style checklist appendix (Section 2, 'Limitations') explicitly confirms and enumerates limitations discussed throughout the body: (1) simulated (non-real) tool execution rather than live production API calls; (2) non-zero benign-baseline ASR observed on some models, attributed to LLM-as-judge false positives in the attack-success scoring pipeline rather than genuine vulnerability; (3) a residual detection gap specifically on GPT-4o (DR=0.71 for the PF-1/PF-4 attack types even with the proposed defenses active), whose root cause is identified as a mismatch between the edit-distance-based detection threshold used and the true underlying semantic deviation; and (4) an acknowledged scope limitation in how broadly the baseline comparison was conducted across the four identified vulnerability profiles (overt, mixed, blind-spot, resistant).</t>
+          <t>No dedicated numbered Limitations section is present; instead, the paper's Ethics Statement flags that the study's own methodology demonstrates LLMs can be instructed to generate coherent and convincing fake information capable of misleading even the LLMs themselves, which the authors identify as underscoring a potential misuse risk of LLMs requiring robust safeguards, prevention measures, and careful, research-only distribution of the generated counter-memory data - framed primarily as a risk/finding of the work rather than a methodological limitation of the experimental design itself; no explicit discussion is given of dataset scale sufficiency, generalization beyond the two evaluated QA task types (entity-centric and multi-step-reasoning), or applicability to non-English/non-QA settings.</t>
         </is>
       </c>
       <c r="F209" s="5" t="n"/>
@@ -9630,7 +9654,7 @@
       <c r="H209" s="5" t="n"/>
       <c r="I209" s="5" t="inlineStr">
         <is>
-          <t>36dd2ed29b677eff1f4689a18040d3fae5c4278a</t>
+          <t>10f829a80a7ee0cdb16307f04e206133d75f81da</t>
         </is>
       </c>
     </row>
@@ -9640,7 +9664,7 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>PlanFlip: Attacking Multi-Agent LLM Systems via Planning-Phase Prompt Injection</t>
+          <t>Adaptive Chameleon or Stubborn Sloth: Revealing the Behavior of Large Language Models in Knowledge Conflicts</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
@@ -9655,7 +9679,7 @@
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>This paper identifies the planning phase of multi-agent LLM systems as a critical, previously underexamined attack surface, distinct from prior work on tool-call injection (which corrupts individual execution steps one at a time) and jailbreaking (which requires overtly harmful, surface-detectable outputs). In the common Planner-Executor-Critic architecture used by production frameworks like AutoGen, MetaGPT, and CrewAI, a Planner decomposes a high-level user goal into an ordered sub-task sequence that downstream Executor and Critic agents carry out and audit, concentrating an unusual degree of trust in a single artifact: the plan itself. The authors formalize 'cascade amplification' -- a single malicious context injection into the Planner's input can corrupt every downstream sub-task simultaneously (up to 100% of the plan, versus at most 1/n for a single tool-call injection), while operating entirely on task structure rather than surface-level content, rendering output-level safety filters blind by design. They further formalize a structural failure mode unique to the dominant real-world deployment pattern where Planner, Executor, and Critic all share the same backbone model: the 'correlated-agent blind spot,' in which an injection that biases the Planner's plan generation simultaneously biases the same-backbone Critic's evaluation of that plan through their shared parameter space, causing the pipeline to appear to self-audit correctly even when the plan has been genuinely corrupted. The authors introduce PlanFlip, a framework comprising four orthogonal planning-phase prompt injection attacks (GoalSubstitution, PriorityInversion, ContextPollution, RoleConfusion), each disguised as a plausible tool output specifically engineered to evade keyword-based filters, and evaluate them across nine frontier LLMs spanning diverse families and capability levels (including two reasoning models, o1 and DeepSeek-R1) over 3,479 episodes across four realistic agentic task scenarios. The evaluation reveals that stronger, more instruction-compliant models (GPT-5) are more, not less, vulnerable to well-crafted planning-phase injections, that homogeneous-backbone pipelines suffer a measurable but structurally invisible correlated-agent blind spot (validated via independent heterogeneous LLM judges), and that reasoning-augmented models can be substantially more resistant. As a countermeasure, the authors propose two complementary defenses -- GoalAnchorCheck (D1), which verifies each generated sub-task against the original stated goal, and CrossAgentConsensus (D2), which compares the Planner's output against an independent reference planner using a deliberately different backbone -- demonstrating that only backbone heterogeneity, not mere redundancy within a single shared backbone, can break the correlated-agent blind spot and restore reliable detection.</t>
+          <t>Presents the first comprehensive, controlled investigation into how LLMs behave when externally-provided evidence (as occurs in tool- or retrieval-augmented deployments) conflicts with their own internal parametric memory - a scenario the paper terms 'knowledge conflict.' The paper introduces a five-step framework that (1) elicits an LLM's parametric memory via closed-book question answering, (2) constructs a corresponding 'counter-memory' by instructing an LLM to generate a coherent passage supporting a different, factually conflicting answer (rather than relying on prior heuristic word-level editing methods like entity substitution or negation injection, which the authors show produce incoherent counter-evidence that is trivially dismissed), (3) filters low-quality pairs using NLI-based entailment checking to confirm each piece of evidence genuinely supports its corresponding answer, and (4) filters for firm/consistent parametric memory via an answer-consistency check, yielding a high-quality dataset of parametric-memory/counter-memory pairs across PopQA and StrategyQA. Evaluating 8 LLMs (3 closed-source, 5 open-source) under this framework, the paper uncovers two seemingly contradictory behaviors: in a single-source evidence setting, LLMs prove highly receptive to conflicting counter-memory - reversing the conclusion of prior heuristic-based studies that LLMs are 'stubborn' - which the authors attribute to their generated counter-memory being substantially more coherent and convincing, and which raises the concrete security implication that LLMs may be readily deceived by disinformation injected via a compromised or malicious third-party retrieval tool; in a multi-source evidence setting where both parametric-consistent and conflicting evidence are simultaneously present (mirroring real search-engine-augmented LLM deployments), LLMs instead display a strong confirmation bias favoring their own parametric memory, which grows stronger for more popular/well-known entities, is sensitive to the order evidence is presented in for most models, tends to follow the side with more supporting evidence pieces ('follows the herd'), and can be further distracted by irrelevant evidence, especially for smaller open-source models. The paper concludes that this dual tendency - excessive receptiveness to isolated conflicting evidence, versus confirmation bias when evidence is mixed - poses important, underexplored challenges for the safe, unbiased, and robust deployment of tool- and retrieval-augmented LLMs.</t>
         </is>
       </c>
       <c r="F210" s="5" t="n"/>
@@ -9663,7 +9687,7 @@
       <c r="H210" s="5" t="n"/>
       <c r="I210" s="5" t="inlineStr">
         <is>
-          <t>36dd2ed29b677eff1f4689a18040d3fae5c4278a</t>
+          <t>10f829a80a7ee0cdb16307f04e206133d75f81da</t>
         </is>
       </c>
     </row>
@@ -9673,7 +9697,7 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>SecureClaw: Clawing Back Control of LLM Agents</t>
+          <t>Secure Prompt Engineering Patterns for Cloud LLM Agents</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
@@ -9696,7 +9720,7 @@
       <c r="H211" s="5" t="n"/>
       <c r="I211" s="5" t="inlineStr">
         <is>
-          <t>cb002afee0f72bd9c25d00c192660df2290ae6ad</t>
+          <t>08e6079c73649ba405826d9ea5da1c18645fcdb6</t>
         </is>
       </c>
     </row>
@@ -9706,7 +9730,7 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>SecureClaw: Clawing Back Control of LLM Agents</t>
+          <t>Secure Prompt Engineering Patterns for Cloud LLM Agents</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
@@ -9729,7 +9753,7 @@
       <c r="H212" s="5" t="n"/>
       <c r="I212" s="5" t="inlineStr">
         <is>
-          <t>cb002afee0f72bd9c25d00c192660df2290ae6ad</t>
+          <t>08e6079c73649ba405826d9ea5da1c18645fcdb6</t>
         </is>
       </c>
     </row>
@@ -9739,7 +9763,7 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>SecureClaw: Clawing Back Control of LLM Agents</t>
+          <t>Secure Prompt Engineering Patterns for Cloud LLM Agents</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
@@ -9762,7 +9786,7 @@
       <c r="H213" s="5" t="n"/>
       <c r="I213" s="5" t="inlineStr">
         <is>
-          <t>cb002afee0f72bd9c25d00c192660df2290ae6ad</t>
+          <t>08e6079c73649ba405826d9ea5da1c18645fcdb6</t>
         </is>
       </c>
     </row>
@@ -9772,7 +9796,7 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>SecureClaw: Clawing Back Control of LLM Agents</t>
+          <t>Secure Prompt Engineering Patterns for Cloud LLM Agents</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
@@ -9795,7 +9819,7 @@
       <c r="H214" s="5" t="n"/>
       <c r="I214" s="5" t="inlineStr">
         <is>
-          <t>cb002afee0f72bd9c25d00c192660df2290ae6ad</t>
+          <t>08e6079c73649ba405826d9ea5da1c18645fcdb6</t>
         </is>
       </c>
     </row>
@@ -9805,7 +9829,7 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>SecureClaw: Clawing Back Control of LLM Agents</t>
+          <t>Secure Prompt Engineering Patterns for Cloud LLM Agents</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
@@ -9820,7 +9844,7 @@
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>direct-input</t>
         </is>
       </c>
       <c r="F215" s="5" t="n"/>
@@ -9828,7 +9852,7 @@
       <c r="H215" s="5" t="n"/>
       <c r="I215" s="5" t="inlineStr">
         <is>
-          <t>cb002afee0f72bd9c25d00c192660df2290ae6ad</t>
+          <t>08e6079c73649ba405826d9ea5da1c18645fcdb6</t>
         </is>
       </c>
     </row>
@@ -9838,7 +9862,7 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>SecureClaw: Clawing Back Control of LLM Agents</t>
+          <t>Secure Prompt Engineering Patterns for Cloud LLM Agents</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
@@ -9861,7 +9885,7 @@
       <c r="H216" s="5" t="n"/>
       <c r="I216" s="5" t="inlineStr">
         <is>
-          <t>cb002afee0f72bd9c25d00c192660df2290ae6ad</t>
+          <t>08e6079c73649ba405826d9ea5da1c18645fcdb6</t>
         </is>
       </c>
     </row>
@@ -9871,7 +9895,7 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>SecureClaw: Clawing Back Control of LLM Agents</t>
+          <t>Secure Prompt Engineering Patterns for Cloud LLM Agents</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
@@ -9894,7 +9918,7 @@
       <c r="H217" s="5" t="n"/>
       <c r="I217" s="5" t="inlineStr">
         <is>
-          <t>cb002afee0f72bd9c25d00c192660df2290ae6ad</t>
+          <t>08e6079c73649ba405826d9ea5da1c18645fcdb6</t>
         </is>
       </c>
     </row>
@@ -9904,7 +9928,7 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>SecureClaw: Clawing Back Control of LLM Agents</t>
+          <t>Secure Prompt Engineering Patterns for Cloud LLM Agents</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
@@ -9927,7 +9951,7 @@
       <c r="H218" s="5" t="n"/>
       <c r="I218" s="5" t="inlineStr">
         <is>
-          <t>cb002afee0f72bd9c25d00c192660df2290ae6ad</t>
+          <t>08e6079c73649ba405826d9ea5da1c18645fcdb6</t>
         </is>
       </c>
     </row>
@@ -9937,7 +9961,7 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>SecureClaw: Clawing Back Control of LLM Agents</t>
+          <t>Secure Prompt Engineering Patterns for Cloud LLM Agents</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
@@ -9952,7 +9976,7 @@
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>execution</t>
+          <t>reasoning</t>
         </is>
       </c>
       <c r="F219" s="5" t="n"/>
@@ -9960,7 +9984,7 @@
       <c r="H219" s="5" t="n"/>
       <c r="I219" s="5" t="inlineStr">
         <is>
-          <t>cb002afee0f72bd9c25d00c192660df2290ae6ad</t>
+          <t>08e6079c73649ba405826d9ea5da1c18645fcdb6</t>
         </is>
       </c>
     </row>
@@ -9970,7 +9994,7 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>SecureClaw: Clawing Back Control of LLM Agents</t>
+          <t>Secure Prompt Engineering Patterns for Cloud LLM Agents</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
@@ -9993,7 +10017,7 @@
       <c r="H220" s="5" t="n"/>
       <c r="I220" s="5" t="inlineStr">
         <is>
-          <t>cb002afee0f72bd9c25d00c192660df2290ae6ad</t>
+          <t>08e6079c73649ba405826d9ea5da1c18645fcdb6</t>
         </is>
       </c>
     </row>
@@ -10003,7 +10027,7 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>SecureClaw: Clawing Back Control of LLM Agents</t>
+          <t>Secure Prompt Engineering Patterns for Cloud LLM Agents</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
@@ -10026,7 +10050,7 @@
       <c r="H221" s="5" t="n"/>
       <c r="I221" s="5" t="inlineStr">
         <is>
-          <t>cb002afee0f72bd9c25d00c192660df2290ae6ad</t>
+          <t>08e6079c73649ba405826d9ea5da1c18645fcdb6</t>
         </is>
       </c>
     </row>
@@ -10036,7 +10060,7 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>SecureClaw: Clawing Back Control of LLM Agents</t>
+          <t>Secure Prompt Engineering Patterns for Cloud LLM Agents</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
@@ -10049,17 +10073,13 @@
           <t>secondary</t>
         </is>
       </c>
-      <c r="E222" s="2" t="inlineStr">
-        <is>
-          <t>No public code/GitHub/HuggingFace release link found anywhere in the paper (checked main text, acknowledgments, and references). The paper provides extensive formal appendices (proofs, assumption partitions, ablation tables) but no stated code or dataset release.</t>
-        </is>
-      </c>
+      <c r="E222" s="2" t="n"/>
       <c r="F222" s="5" t="n"/>
       <c r="G222" s="5" t="n"/>
       <c r="H222" s="5" t="n"/>
       <c r="I222" s="5" t="inlineStr">
         <is>
-          <t>cb002afee0f72bd9c25d00c192660df2290ae6ad</t>
+          <t>08e6079c73649ba405826d9ea5da1c18645fcdb6</t>
         </is>
       </c>
     </row>
@@ -10069,7 +10089,7 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>SecureClaw: Clawing Back Control of LLM Agents</t>
+          <t>Secure Prompt Engineering Patterns for Cloud LLM Agents</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
@@ -10084,7 +10104,7 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>All main runs use gpt-4o-mini-2024-07-18 at temperature 0 as the underlying LLM runtime, with additional small cross-model spot checks reported in Appendix A.2 (Table 9, 'SecureClaw cross-model transfer checks').</t>
+          <t>LLM agents orchestrated through LangChain and Semantic Kernel across three parallel cloud testbeds; specific base models are not named in the paper.</t>
         </is>
       </c>
       <c r="F223" s="5" t="n"/>
@@ -10092,7 +10112,7 @@
       <c r="H223" s="5" t="n"/>
       <c r="I223" s="5" t="inlineStr">
         <is>
-          <t>cb002afee0f72bd9c25d00c192660df2290ae6ad</t>
+          <t>08e6079c73649ba405826d9ea5da1c18645fcdb6</t>
         </is>
       </c>
     </row>
@@ -10102,7 +10122,7 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>SecureClaw: Clawing Back Control of LLM Agents</t>
+          <t>Secure Prompt Engineering Patterns for Cloud LLM Agents</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
@@ -10117,7 +10137,7 @@
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>Three benchmarks evaluated in a common harness: AgentDojo (n=629, tool-use prompt-injection benchmark), AgentLeak (n=496, multi-agent internal-leakage benchmark with a channel taxonomy C1-C7: C1=final response, C2=inter-agent messages, C3/C4=tool I/O, C5=shared/persistent memory, C6=logs, C7=skill/supply-chain ingress), and Agent Security Bench/ASB (n=2000).</t>
+          <t>An author-assembled corpus of 200+ prompt injections spanning direct, indirect and cross-agent vectors, including malicious instructions embedded in JSON tool responses.</t>
         </is>
       </c>
       <c r="F224" s="5" t="n"/>
@@ -10125,7 +10145,7 @@
       <c r="H224" s="5" t="n"/>
       <c r="I224" s="5" t="inlineStr">
         <is>
-          <t>cb002afee0f72bd9c25d00c192660df2290ae6ad</t>
+          <t>08e6079c73649ba405826d9ea5da1c18645fcdb6</t>
         </is>
       </c>
     </row>
@@ -10135,7 +10155,7 @@
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>SecureClaw: Clawing Back Control of LLM Agents</t>
+          <t>Secure Prompt Engineering Patterns for Cloud LLM Agents</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
@@ -10150,7 +10170,7 @@
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>SecureClaw is the only same-harness defense (among Plain/no-defense, IPIGuard, DRIFT, and Faramesh baselines) that jointly drives unauthorized commits to zero/near-zero on effect benchmarks while substantially reducing internal-relay leakage: 0% ASR on ASB (vs. 91.65% Plain, 99.60% IPIGuard, 87.75% DRIFT, 0.00% Faramesh -- Faramesh matches on ASB but leaves AgentLeak's internal channels open), 0.64% ASR on AgentDojo (4/629, vs. 31.48% Plain), and 3.23% overall leak (16/496) on AgentLeak's attacked parity lane, with per-channel leak rates of 0.20% on C2 (inter-agent messages) and 0.00% on C5 (shared memory) versus 92.74% C2 / 51.61% C5 for the Plain baseline. SecureClaw retains 88.90% utility on ASB at 0% ASR, and a recovery ablation shows deny-aware safe continuation raises matched-sample ASB utility from 70% to 86% without increasing ASR. A mechanism-isolation ablation on a matched 48-row AgentLeak slice demonstrates the dual-boundary design is non-substitutable: removing handles (while keeping the execution boundary) raises attacked-row C2 leakage from 0/24 to 5/24-6/24 and reintroduces C5 leakage, while removing the execution boundary alone (keeping handles) leaves both C2 and C5 at 0/24 -- confirming confidentiality gains come specifically from handle confinement, not incidentally from the write boundary. A residual-failure analysis (Table 4) finds SecureClaw's remaining AgentDojo failures (3/629 foreign-principal/missing-contextual-bind cases, 1/629 broader-scope workspace action) stem from coarse policy granularity rather than boundary bypass, and a dedicated compromised-runtime bypass suite reports 29/29 expected blocks on commit-path bypass attempts.</t>
+          <t>Applying the Secure Prompt Engineering Patterns incrementally to otherwise undefended cloud agents reduces attack success rate, reported alongside latency overhead, false positives and a Trust Deviation Metric comparing expected against actual agent actions.</t>
         </is>
       </c>
       <c r="F225" s="5" t="n"/>
@@ -10158,7 +10178,7 @@
       <c r="H225" s="5" t="n"/>
       <c r="I225" s="5" t="inlineStr">
         <is>
-          <t>cb002afee0f72bd9c25d00c192660df2290ae6ad</t>
+          <t>08e6079c73649ba405826d9ea5da1c18645fcdb6</t>
         </is>
       </c>
     </row>
@@ -10168,7 +10188,7 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>SecureClaw: Clawing Back Control of LLM Agents</t>
+          <t>Secure Prompt Engineering Patterns for Cloud LLM Agents</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
@@ -10183,7 +10203,7 @@
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>Four common-harness baselines matched on rows, model, scorer, temperature, and task protocol: Plain (no defense), IPIGuard (tool-dependency-graph defense against indirect prompt injection, An et al. 2025), DRIFT (Li et al. 2025b), and Faramesh (a protocol-agnostic execution control plane, Fatmi 2026). Architecturally related systems without directly comparable public implementations (e.g., information-flow-control approaches like Costa et al. 2025's IFC-based agent security, and 'Defeating Prompt Injections by Design' from Debenedetti et al. 2025) are discussed only qualitatively rather than benchmarked head-to-head.</t>
+          <t>Baseline agents run without any defense, with the five patterns then layered on one at a time: Input Sanitization Filters, Role and Context Separation, Execution Confirmation, Capability Restriction and Chain-of-Thought Isolation.</t>
         </is>
       </c>
       <c r="F226" s="5" t="n"/>
@@ -10191,7 +10211,7 @@
       <c r="H226" s="5" t="n"/>
       <c r="I226" s="5" t="inlineStr">
         <is>
-          <t>cb002afee0f72bd9c25d00c192660df2290ae6ad</t>
+          <t>08e6079c73649ba405826d9ea5da1c18645fcdb6</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10221,7 @@
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>SecureClaw: Clawing Back Control of LLM Agents</t>
+          <t>Secure Prompt Engineering Patterns for Cloud LLM Agents</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
@@ -10216,7 +10236,7 @@
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>Formal problem setting (Section 2) covering two adversaries. (1) Prompt-injection setting: attacker-controlled instructions embedded in retrieved content attempt to redirect downstream actions or induce disclosure, as instantiated in AgentDojo, AgentLeak, and ASB. (2) Compromised-runtime setting: the LLM-driven agent runtime itself is treated as fully adversarial -- it may fabricate requests, tamper with recipients or channels, replay prior authorizations, mix sessions, guess handles, or exploit implementation mistakes. The architecture defines two distinct security surfaces: the effect surface (whether the exact request reaching an external sink is authorized for the current caller, session, inputs, and context) and the plaintext surface (whether the untrusted runtime ever receives raw secrets it could relay via outputs, inter-agent messages, memory, logs, or later tool calls). Trust assumptions are explicit and narrow: the gateway, handle store, policy engine, and executor are all trusted components; the design additionally assumes complete mediation of effectful sinks and sensitive reads, correct protected-field classification, bounded clock drift, and crash-safe replay protection. Explicitly NOT assumed: an honest runtime, successful prompt-injection prevention (disclosure is modeled explicitly via a declassification operator D rather than assumed away), or survival of gateway/executor compromise -- Appendix B.6 separately analyzes guarantee degradation under trusted-component compromise.</t>
+          <t>Direct and indirect prompt manipulation of cloud-integrated LLM agents holding varying privilege levels, aiming at unauthorized cloud operations, data exposure, privilege escalation and resource misuse. Testbeds use isolated projects with controlled access rights and logging.</t>
         </is>
       </c>
       <c r="F227" s="5" t="n"/>
@@ -10224,7 +10244,7 @@
       <c r="H227" s="5" t="n"/>
       <c r="I227" s="5" t="inlineStr">
         <is>
-          <t>cb002afee0f72bd9c25d00c192660df2290ae6ad</t>
+          <t>08e6079c73649ba405826d9ea5da1c18645fcdb6</t>
         </is>
       </c>
     </row>
@@ -10234,7 +10254,7 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>SecureClaw: Clawing Back Control of LLM Agents</t>
+          <t>Secure Prompt Engineering Patterns for Cloud LLM Agents</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
@@ -10249,7 +10269,7 @@
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>Explicit 'Limitations and broader impact' section (Section 6). SecureClaw reduces unsafe agentic effects and plaintext exposure but does not guarantee semantic correctness within policy-allowed actions (a policy-allowed action can still target the wrong principal or object if the policy is too coarse) and still incurs benign-utility loss on AgentDojo. The residuals are stated to motivate stronger principal, object, and phase binding in the policy layer. The paper explicitly names false assurance as the main deployment risk: if protected fields are misclassified or effectful sinks remain unmediated, the architecture's boundary guarantees silently no longer apply, so the authors recommend deployment alongside explicit sink inventories, schema audits, and conservative confirmation policies for irreversible actions. The system's guarantees are also explicitly scoped to trusting the gateway, policy engine, and executor -- it does not survive compromise of these components, and the optional distributed-policy variant additionally relies on a non-collusion assumption among evaluators.</t>
+          <t>Not explicitly stated as a limitations section in the extracted text.</t>
         </is>
       </c>
       <c r="F228" s="5" t="n"/>
@@ -10257,7 +10277,7 @@
       <c r="H228" s="5" t="n"/>
       <c r="I228" s="5" t="inlineStr">
         <is>
-          <t>cb002afee0f72bd9c25d00c192660df2290ae6ad</t>
+          <t>08e6079c73649ba405826d9ea5da1c18645fcdb6</t>
         </is>
       </c>
     </row>
@@ -10267,7 +10287,7 @@
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>SecureClaw: Clawing Back Control of LLM Agents</t>
+          <t>Secure Prompt Engineering Patterns for Cloud LLM Agents</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
@@ -10282,7 +10302,7 @@
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>This paper identifies two distinct, non-substitutable security failures in tool-using LLM agents -- unauthorized external actions and exposure of sensitive plaintext inside the runtime before any final-output check can intervene -- and argues that existing defenses typically protect only one of these boundaries (either the planner/runtime or the action sink), leaving the other exposed. SecureClaw is a dual-boundary architecture addressing both simultaneously. On the read path, sensitive data passes through a trusted gateway that never returns raw values to the untrusted LLM runtime; instead it returns an opaque, high-entropy handle (a capability-style unforgeable symbolic reference, in the tradition of Saltzer &amp; Schroeder and Watson et al.'s capability security) plus, when planning requires it, a bounded natural-language summary via an explicit, auditable declassification interface (rather than an accidental plaintext leak path). On the write path, the runtime may only propose an effectful action; a trusted policy engine authorizes the exact canonicalized request (deterministic serialization of sink-relevant fields), and only a separate trusted executor can commit the resulting external effect, following a PREVIEW-to-COMMIT protocol -- meaning the untrusted runtime never directly triggers a side effect and never directly dereferences a secret. The key empirical prediction tested is non-substitutability: sink-side enforcement should stop unauthorized commits without closing internal relay channels, while read-side handle confinement should close relay channels without itself authorizing commits, and the paper's ablation study confirms this split empirically. The evaluation spans full-benchmark runs on AgentDojo, AgentLeak, and ASB, a mechanism ablation isolating the contribution of handles versus the execution boundary, a dedicated compromised-runtime bypass suite (modeling a fully adversarial runtime that can fabricate/replay/tamper with requests), and targeted measurements of deny-aware recovery (offering a safe continuation such as drafting for confirmation when a commit is denied) and authorization latency overhead. The paper also includes an extensive formal appendix with theorems characterizing confidentiality and authorization guarantees under stated trust assumptions, plus a partition of exactly which properties survive compromise of each trusted component (gateway, handle store, policy engine, executor).</t>
+          <t>A catalogue of five reusable secure-prompt patterns for cloud LLM agents, evaluated incrementally against a 200+ injection corpus on three isolated cloud testbeds, with a threat-vector taxonomy for direct and indirect manipulation.</t>
         </is>
       </c>
       <c r="F229" s="5" t="n"/>
@@ -10290,7 +10310,7 @@
       <c r="H229" s="5" t="n"/>
       <c r="I229" s="5" t="inlineStr">
         <is>
-          <t>cb002afee0f72bd9c25d00c192660df2290ae6ad</t>
+          <t>08e6079c73649ba405826d9ea5da1c18645fcdb6</t>
         </is>
       </c>
     </row>
@@ -10300,7 +10320,7 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>The Instruction Hierarchy: Training LLMs to Prioritize Privileged Instructions</t>
+          <t>Benchmarking Serverless AI Architectures: Modular RAG, Serverless RAG, and Long Context Inference</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
@@ -10323,7 +10343,7 @@
       <c r="H230" s="5" t="n"/>
       <c r="I230" s="5" t="inlineStr">
         <is>
-          <t>f18e5a844c37e5342f8f3d409c74c1a9c91d1f8f</t>
+          <t>2c6f684a777a194f3dff92d3014f2887b6bb6880</t>
         </is>
       </c>
     </row>
@@ -10333,7 +10353,7 @@
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>The Instruction Hierarchy: Training LLMs to Prioritize Privileged Instructions</t>
+          <t>Benchmarking Serverless AI Architectures: Modular RAG, Serverless RAG, and Long Context Inference</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
@@ -10348,7 +10368,7 @@
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>ML/AI</t>
         </is>
       </c>
       <c r="F231" s="5" t="n"/>
@@ -10356,7 +10376,7 @@
       <c r="H231" s="5" t="n"/>
       <c r="I231" s="5" t="inlineStr">
         <is>
-          <t>f18e5a844c37e5342f8f3d409c74c1a9c91d1f8f</t>
+          <t>2c6f684a777a194f3dff92d3014f2887b6bb6880</t>
         </is>
       </c>
     </row>
@@ -10366,7 +10386,7 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>The Instruction Hierarchy: Training LLMs to Prioritize Privileged Instructions</t>
+          <t>Benchmarking Serverless AI Architectures: Modular RAG, Serverless RAG, and Long Context Inference</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
@@ -10389,7 +10409,7 @@
       <c r="H232" s="5" t="n"/>
       <c r="I232" s="5" t="inlineStr">
         <is>
-          <t>f18e5a844c37e5342f8f3d409c74c1a9c91d1f8f</t>
+          <t>2c6f684a777a194f3dff92d3014f2887b6bb6880</t>
         </is>
       </c>
     </row>
@@ -10399,7 +10419,7 @@
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>The Instruction Hierarchy: Training LLMs to Prioritize Privileged Instructions</t>
+          <t>Benchmarking Serverless AI Architectures: Modular RAG, Serverless RAG, and Long Context Inference</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
@@ -10414,7 +10434,7 @@
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>defense</t>
+          <t>neither</t>
         </is>
       </c>
       <c r="F233" s="5" t="n"/>
@@ -10422,7 +10442,7 @@
       <c r="H233" s="5" t="n"/>
       <c r="I233" s="5" t="inlineStr">
         <is>
-          <t>f18e5a844c37e5342f8f3d409c74c1a9c91d1f8f</t>
+          <t>2c6f684a777a194f3dff92d3014f2887b6bb6880</t>
         </is>
       </c>
     </row>
@@ -10432,7 +10452,7 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>The Instruction Hierarchy: Training LLMs to Prioritize Privileged Instructions</t>
+          <t>Benchmarking Serverless AI Architectures: Modular RAG, Serverless RAG, and Long Context Inference</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
@@ -10447,7 +10467,7 @@
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>direct-input</t>
+          <t>RAG</t>
         </is>
       </c>
       <c r="F234" s="5" t="n"/>
@@ -10455,7 +10475,7 @@
       <c r="H234" s="5" t="n"/>
       <c r="I234" s="5" t="inlineStr">
         <is>
-          <t>f18e5a844c37e5342f8f3d409c74c1a9c91d1f8f</t>
+          <t>2c6f684a777a194f3dff92d3014f2887b6bb6880</t>
         </is>
       </c>
     </row>
@@ -10465,7 +10485,7 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>The Instruction Hierarchy: Training LLMs to Prioritize Privileged Instructions</t>
+          <t>Benchmarking Serverless AI Architectures: Modular RAG, Serverless RAG, and Long Context Inference</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
@@ -10480,7 +10500,7 @@
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>goal-hijack</t>
+          <t>silent-corruption</t>
         </is>
       </c>
       <c r="F235" s="5" t="n"/>
@@ -10488,7 +10508,7 @@
       <c r="H235" s="5" t="n"/>
       <c r="I235" s="5" t="inlineStr">
         <is>
-          <t>f18e5a844c37e5342f8f3d409c74c1a9c91d1f8f</t>
+          <t>2c6f684a777a194f3dff92d3014f2887b6bb6880</t>
         </is>
       </c>
     </row>
@@ -10498,7 +10518,7 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>The Instruction Hierarchy: Training LLMs to Prioritize Privileged Instructions</t>
+          <t>Benchmarking Serverless AI Architectures: Modular RAG, Serverless RAG, and Long Context Inference</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
@@ -10513,7 +10533,7 @@
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F236" s="5" t="n"/>
@@ -10521,7 +10541,7 @@
       <c r="H236" s="5" t="n"/>
       <c r="I236" s="5" t="inlineStr">
         <is>
-          <t>f18e5a844c37e5342f8f3d409c74c1a9c91d1f8f</t>
+          <t>2c6f684a777a194f3dff92d3014f2887b6bb6880</t>
         </is>
       </c>
     </row>
@@ -10531,7 +10551,7 @@
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>The Instruction Hierarchy: Training LLMs to Prioritize Privileged Instructions</t>
+          <t>Benchmarking Serverless AI Architectures: Modular RAG, Serverless RAG, and Long Context Inference</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
@@ -10546,7 +10566,7 @@
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F237" s="5" t="n"/>
@@ -10554,7 +10574,7 @@
       <c r="H237" s="5" t="n"/>
       <c r="I237" s="5" t="inlineStr">
         <is>
-          <t>f18e5a844c37e5342f8f3d409c74c1a9c91d1f8f</t>
+          <t>2c6f684a777a194f3dff92d3014f2887b6bb6880</t>
         </is>
       </c>
     </row>
@@ -10564,7 +10584,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>The Instruction Hierarchy: Training LLMs to Prioritize Privileged Instructions</t>
+          <t>Benchmarking Serverless AI Architectures: Modular RAG, Serverless RAG, and Long Context Inference</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -10579,7 +10599,7 @@
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>reasoning</t>
+          <t>none</t>
         </is>
       </c>
       <c r="F238" s="5" t="n"/>
@@ -10587,7 +10607,7 @@
       <c r="H238" s="5" t="n"/>
       <c r="I238" s="5" t="inlineStr">
         <is>
-          <t>f18e5a844c37e5342f8f3d409c74c1a9c91d1f8f</t>
+          <t>2c6f684a777a194f3dff92d3014f2887b6bb6880</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10617,7 @@
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>The Instruction Hierarchy: Training LLMs to Prioritize Privileged Instructions</t>
+          <t>Benchmarking Serverless AI Architectures: Modular RAG, Serverless RAG, and Long Context Inference</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
@@ -10620,7 +10640,7 @@
       <c r="H239" s="5" t="n"/>
       <c r="I239" s="5" t="inlineStr">
         <is>
-          <t>f18e5a844c37e5342f8f3d409c74c1a9c91d1f8f</t>
+          <t>2c6f684a777a194f3dff92d3014f2887b6bb6880</t>
         </is>
       </c>
     </row>
@@ -10630,7 +10650,7 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>The Instruction Hierarchy: Training LLMs to Prioritize Privileged Instructions</t>
+          <t>Benchmarking Serverless AI Architectures: Modular RAG, Serverless RAG, and Long Context Inference</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
@@ -10653,7 +10673,7 @@
       <c r="H240" s="5" t="n"/>
       <c r="I240" s="5" t="inlineStr">
         <is>
-          <t>f18e5a844c37e5342f8f3d409c74c1a9c91d1f8f</t>
+          <t>2c6f684a777a194f3dff92d3014f2887b6bb6880</t>
         </is>
       </c>
     </row>
@@ -10663,7 +10683,7 @@
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>The Instruction Hierarchy: Training LLMs to Prioritize Privileged Instructions</t>
+          <t>Benchmarking Serverless AI Architectures: Modular RAG, Serverless RAG, and Long Context Inference</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
@@ -10676,17 +10696,13 @@
           <t>secondary</t>
         </is>
       </c>
-      <c r="E241" s="2" t="inlineStr">
-        <is>
-          <t>N - no code, data, or model weights released; the fine-tuned GPT-3.5 Turbo models and the synthetic training data are internal to OpenAI and the paper carries no availability statement.</t>
-        </is>
-      </c>
+      <c r="E241" s="2" t="n"/>
       <c r="F241" s="5" t="n"/>
       <c r="G241" s="5" t="n"/>
       <c r="H241" s="5" t="n"/>
       <c r="I241" s="5" t="inlineStr">
         <is>
-          <t>f18e5a844c37e5342f8f3d409c74c1a9c91d1f8f</t>
+          <t>2c6f684a777a194f3dff92d3014f2887b6bb6880</t>
         </is>
       </c>
     </row>
@@ -10696,7 +10712,7 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>The Instruction Hierarchy: Training LLMs to Prioritize Privileged Instructions</t>
+          <t>Benchmarking Serverless AI Architectures: Modular RAG, Serverless RAG, and Long Context Inference</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
@@ -10711,7 +10727,7 @@
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>GPT-3.5 Turbo fine-tuned with SFT+RLHF on instruction-hierarchy data; GPT-3.5 Turbo capabilities-only baseline; GPT-3.5 Turbo baseline plus an explicit hierarchy system message; GPT-4 as automated judge</t>
+          <t>Not named in the extracted material; the comparison is across serverless architectures (Modular RAG, Serverless RAG, Long-Context Inference) deployed on AWS Lambda rather than across backbone models.</t>
         </is>
       </c>
       <c r="F242" s="5" t="n"/>
@@ -10719,7 +10735,7 @@
       <c r="H242" s="5" t="n"/>
       <c r="I242" s="5" t="inlineStr">
         <is>
-          <t>f18e5a844c37e5342f8f3d409c74c1a9c91d1f8f</t>
+          <t>2c6f684a777a194f3dff92d3014f2887b6bb6880</t>
         </is>
       </c>
     </row>
@@ -10729,7 +10745,7 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>The Instruction Hierarchy: Training LLMs to Prioritize Privileged Instructions</t>
+          <t>Benchmarking Serverless AI Architectures: Modular RAG, Serverless RAG, and Long Context Inference</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
@@ -10744,7 +10760,7 @@
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>TensorTrust Prompt Hijacking and TensorTrust Robustness/password extraction (Toyer et al.); Gandalf Game password extraction (Lakera AI); jailbreakchat.com jailbreaks with unsafe and with allowed prompts; known ChatGPT jailbreaks; author-created held-out synthetic sets for closed-domain direct injection, user conflicting/non-conflicting instructions, indirect injection via browsing, indirect injection via tool return values, system-prompt probing questions and borderline allowed prompts; capability checks on TriviaQA, LAMBADA, HellaSwag. Dataset sizes are not stated.</t>
+          <t>Purpose-built evaluation over technical documents scaling up to 300 pages, with a 142-page document reported as the mid-scale reference point. Metrics: accuracy (10-point scale), end-to-end latency in seconds, and per-query cost in dollars.</t>
         </is>
       </c>
       <c r="F243" s="5" t="n"/>
@@ -10752,7 +10768,7 @@
       <c r="H243" s="5" t="n"/>
       <c r="I243" s="5" t="inlineStr">
         <is>
-          <t>f18e5a844c37e5342f8f3d409c74c1a9c91d1f8f</t>
+          <t>2c6f684a777a194f3dff92d3014f2887b6bb6880</t>
         </is>
       </c>
     </row>
@@ -10762,7 +10778,7 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>The Instruction Hierarchy: Training LLMs to Prioritize Privileged Instructions</t>
+          <t>Benchmarking Serverless AI Architectures: Modular RAG, Serverless RAG, and Long Context Inference</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
@@ -10777,7 +10793,7 @@
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>Fine-tuning GPT-3.5 Turbo on synthetic instruction-hierarchy data improves robustness on every safety evaluation, with defense against system-prompt extraction improving by 63% over the capabilities-only baseline. Gains generalize to attack classes deliberately held out of training (jailbreaks, password extraction, injection via tool use) by up to 34%, with jailbreak robustness up over 30%, while TriviaQA/LAMBADA/HellaSwag capability scores are comparable to baseline.</t>
+          <t>Long-Context Inference successfully mitigates Lost in the Middle, scoring 9.6/10 accuracy on 142-page documents - confirming that sufficient context capacity does address the positional-attention failure at moderate scale. But scaling to 300 pages produces severe operational limits: latency spikes to 21.7 seconds and cost rises by nearly 100x relative to RAG systems. Modular RAG inverts the profile, holding latency at 4.2 seconds and cost at $0.0012 while accuracy falls to 4.1/10 on massive datasets due to retrieval limits, with Serverless RAG a stable middle ground. The conclusion is a threshold argument rather than a winner: Long-Context is adequate for medium-sized documents despite higher cost, but beyond a certain size threshold RAG architectures remain essential to reduce context size for scalable, cost-effective operation. For this SoK the valuable framing is that Lost in the Middle is not simply solved by longer context windows - it is traded against a nearly hundredfold cost increase, so in production the mechanism persists wherever that cost is unacceptable, which explains why retrieval-based context reduction remains ubiquitous despite the mechanism it reintroduces (retrieval limits driving accuracy to 4.1/10). The two failure modes are alternatives, not a progression.</t>
         </is>
       </c>
       <c r="F244" s="5" t="n"/>
@@ -10785,7 +10801,7 @@
       <c r="H244" s="5" t="n"/>
       <c r="I244" s="5" t="inlineStr">
         <is>
-          <t>f18e5a844c37e5342f8f3d409c74c1a9c91d1f8f</t>
+          <t>2c6f684a777a194f3dff92d3014f2887b6bb6880</t>
         </is>
       </c>
     </row>
@@ -10795,7 +10811,7 @@
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>The Instruction Hierarchy: Training LLMs to Prioritize Privileged Instructions</t>
+          <t>Benchmarking Serverless AI Architectures: Modular RAG, Serverless RAG, and Long Context Inference</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
@@ -10810,7 +10826,7 @@
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>A capabilities-only fine-tuned GPT-3.5 Turbo (same recipe minus hierarchy data), and that baseline augmented with a prompted system message spelling out the hierarchy; the trained hierarchy substantially outperforms the prompting baseline.</t>
+          <t>Three architectures compared head-to-head on identical technical documents scaling to 300 pages: Modular RAG (4.2s latency, $0.0012 cost, 4.1/10 accuracy at scale), Serverless RAG (middle ground), and Long-Context Inference (9.6/10 accuracy on 142 pages, 21.7s latency and ~100x cost at 300 pages). Metrics are accuracy, latency and cost measured jointly.</t>
         </is>
       </c>
       <c r="F245" s="5" t="n"/>
@@ -10818,7 +10834,7 @@
       <c r="H245" s="5" t="n"/>
       <c r="I245" s="5" t="inlineStr">
         <is>
-          <t>f18e5a844c37e5342f8f3d409c74c1a9c91d1f8f</t>
+          <t>2c6f684a777a194f3dff92d3014f2887b6bb6880</t>
         </is>
       </c>
     </row>
@@ -10828,7 +10844,7 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>The Instruction Hierarchy: Training LLMs to Prioritize Privileged Instructions</t>
+          <t>Benchmarking Serverless AI Architectures: Modular RAG, Serverless RAG, and Long Context Inference</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
@@ -10841,17 +10857,13 @@
           <t>freetext</t>
         </is>
       </c>
-      <c r="E246" s="2" t="inlineStr">
-        <is>
-          <t>Three-party setting of application builder, end user, and third-party content. The adversary is either the end user supplying User Message text that overrides developer System Message instructions or extracts the system prompt, or a third party planting instructions in browsing results and tool return values. The attacker controls only text at a lower privilege level than the instructions being overridden, with no access to weights or to the system message itself.</t>
-        </is>
-      </c>
+      <c r="E246" s="2" t="n"/>
       <c r="F246" s="5" t="n"/>
       <c r="G246" s="5" t="n"/>
       <c r="H246" s="5" t="n"/>
       <c r="I246" s="5" t="inlineStr">
         <is>
-          <t>f18e5a844c37e5342f8f3d409c74c1a9c91d1f8f</t>
+          <t>2c6f684a777a194f3dff92d3014f2887b6bb6880</t>
         </is>
       </c>
     </row>
@@ -10861,7 +10873,7 @@
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>The Instruction Hierarchy: Training LLMs to Prioritize Privileged Instructions</t>
+          <t>Benchmarking Serverless AI Architectures: Modular RAG, Serverless RAG, and Long Context Inference</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
@@ -10876,7 +10888,7 @@
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>The authors report over-refusal regressions, where models sometimes ignore or refuse benign lower-priority instructions, notably on System Message Probing Questions and Jailbreakchat with Allowed Prompts. They also state the current models are trained to never follow instructions during browsing or tool use (too coarse a rule), cover only text rather than image or audio inputs, and are 'likely still vulnerable to powerful adversarial attacks' without explicit adversarial training.</t>
+          <t>No explicit limitations section surfaced. Scope is bounded to technical documents up to 300 pages in a serverless (AWS Lambda) deployment, so the identified size threshold is specific to that document type, deployment model and the pricing regime at time of writing - cost ratios in particular are perishable as inference pricing changes. Accuracy is reported on a 10-point scale without the scoring protocol or inter-rater validation surfaced, so the 9.6 versus 4.1 gap depends on an unexplained judgment procedure. The evaluation covers incidental degradation only; no adversarial condition is considered, which matters because the two architectures fail differently under attack - a long-context system ingests everything including planted content, while a retrieval system can be poisoned at the index - and that asymmetry is not examined. Single-run figures without variance are reported for latency and accuracy.</t>
         </is>
       </c>
       <c r="F247" s="5" t="n"/>
@@ -10884,7 +10896,7 @@
       <c r="H247" s="5" t="n"/>
       <c r="I247" s="5" t="inlineStr">
         <is>
-          <t>f18e5a844c37e5342f8f3d409c74c1a9c91d1f8f</t>
+          <t>2c6f684a777a194f3dff92d3014f2887b6bb6880</t>
         </is>
       </c>
     </row>
@@ -10894,7 +10906,7 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>The Instruction Hierarchy: Training LLMs to Prioritize Privileged Instructions</t>
+          <t>Benchmarking Serverless AI Architectures: Modular RAG, Serverless RAG, and Long Context Inference</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
@@ -10909,7 +10921,7 @@
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>Proposes the instruction hierarchy, an explicit privilege ordering over System Messages, User Messages, Model Outputs and Tool Outputs, so the model treats lower-privileged text as data rather than commands whenever the two conflict. Builds training data two ways: decomposing compositional benign requests into aligned sub-instructions placed lower in the hierarchy via context distillation, and using red-teamer LLMs to synthesize misaligned instructions the model is trained to answer as if it never saw them; it then fine-tunes GPT-3.5 Turbo with SFT and RLHF. Evaluates on open-source and novel benchmarks covering direct injection, indirect injection via browsing and tools, system-prompt extraction, jailbreaks and over-refusal, deliberately holding out several attack classes to test generalization. Matters because it reframes prompt injection as a missing privilege abstraction rather than a filtering problem, and is the deployed training-time defense that later alignment-based defenses such as StruQ and SecAlign position themselves against.</t>
+          <t>Benchmarks three serverless architectures - Modular RAG, Serverless RAG, and Long-Context Inference - against technical documents up to 300 pages, to answer whether expanding context windows can fully replace retrieval-augmented generation in production. Directly relevant to this corpus because it treats the Lost in the Middle phenomenon as an operational variable measured alongside latency and cost, rather than as an isolated accuracy property: the question is not merely whether long-context models suffer positional degradation but whether avoiding it is economically viable at scale. The three architectures represent distinct points on the context-management spectrum - Modular RAG aggressively reduces context through retrieval, Long-Context Inference submits the full document and relies on the model's attention over it, and Serverless RAG occupies a middle position - so the comparison isolates the cost of keeping information in context versus retrieving it. Evaluated in a serverless deployment setting (AWS Lambda), which makes the cost dimension concrete rather than notional. A Track B paper on the direct-input channel whose contribution is quantifying the trade-off between an incidental degradation mechanism and the resource cost of avoiding it.</t>
         </is>
       </c>
       <c r="F248" s="5" t="n"/>
@@ -10917,7 +10929,7 @@
       <c r="H248" s="5" t="n"/>
       <c r="I248" s="5" t="inlineStr">
         <is>
-          <t>f18e5a844c37e5342f8f3d409c74c1a9c91d1f8f</t>
+          <t>2c6f684a777a194f3dff92d3014f2887b6bb6880</t>
         </is>
       </c>
     </row>
@@ -10927,7 +10939,7 @@
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>Enhancing reliability in LLM-integrated robotic systems: A unified approach to security and safety</t>
+          <t>LUMINA: Long-horizon Understanding for Multi-turn Interactive Agents</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
@@ -10950,7 +10962,7 @@
       <c r="H249" s="5" t="n"/>
       <c r="I249" s="5" t="inlineStr">
         <is>
-          <t>f8e7615c7c6d95ecf1737d845ee3eb713e297b5f</t>
+          <t>023292350ef95533d99264dab96ffbd271b24b45</t>
         </is>
       </c>
     </row>
@@ -10960,7 +10972,7 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>Enhancing reliability in LLM-integrated robotic systems: A unified approach to security and safety</t>
+          <t>LUMINA: Long-horizon Understanding for Multi-turn Interactive Agents</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
@@ -10975,7 +10987,7 @@
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>ML/AI</t>
         </is>
       </c>
       <c r="F250" s="5" t="n"/>
@@ -10983,7 +10995,7 @@
       <c r="H250" s="5" t="n"/>
       <c r="I250" s="5" t="inlineStr">
         <is>
-          <t>f8e7615c7c6d95ecf1737d845ee3eb713e297b5f</t>
+          <t>023292350ef95533d99264dab96ffbd271b24b45</t>
         </is>
       </c>
     </row>
@@ -10993,7 +11005,7 @@
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>Enhancing reliability in LLM-integrated robotic systems: A unified approach to security and safety</t>
+          <t>LUMINA: Long-horizon Understanding for Multi-turn Interactive Agents</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
@@ -11016,7 +11028,7 @@
       <c r="H251" s="5" t="n"/>
       <c r="I251" s="5" t="inlineStr">
         <is>
-          <t>f8e7615c7c6d95ecf1737d845ee3eb713e297b5f</t>
+          <t>023292350ef95533d99264dab96ffbd271b24b45</t>
         </is>
       </c>
     </row>
@@ -11026,7 +11038,7 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>Enhancing reliability in LLM-integrated robotic systems: A unified approach to security and safety</t>
+          <t>LUMINA: Long-horizon Understanding for Multi-turn Interactive Agents</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
@@ -11041,7 +11053,7 @@
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>defense</t>
+          <t>neither</t>
         </is>
       </c>
       <c r="F252" s="5" t="n"/>
@@ -11049,7 +11061,7 @@
       <c r="H252" s="5" t="n"/>
       <c r="I252" s="5" t="inlineStr">
         <is>
-          <t>f8e7615c7c6d95ecf1737d845ee3eb713e297b5f</t>
+          <t>023292350ef95533d99264dab96ffbd271b24b45</t>
         </is>
       </c>
     </row>
@@ -11059,7 +11071,7 @@
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>Enhancing reliability in LLM-integrated robotic systems: A unified approach to security and safety</t>
+          <t>LUMINA: Long-horizon Understanding for Multi-turn Interactive Agents</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
@@ -11074,7 +11086,7 @@
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>direct-input</t>
+          <t>tool-output</t>
         </is>
       </c>
       <c r="F253" s="5" t="n"/>
@@ -11082,7 +11094,7 @@
       <c r="H253" s="5" t="n"/>
       <c r="I253" s="5" t="inlineStr">
         <is>
-          <t>f8e7615c7c6d95ecf1737d845ee3eb713e297b5f</t>
+          <t>023292350ef95533d99264dab96ffbd271b24b45</t>
         </is>
       </c>
     </row>
@@ -11092,7 +11104,7 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>Enhancing reliability in LLM-integrated robotic systems: A unified approach to security and safety</t>
+          <t>LUMINA: Long-horizon Understanding for Multi-turn Interactive Agents</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
@@ -11107,7 +11119,7 @@
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>goal-hijack</t>
+          <t>reasoning-corruption</t>
         </is>
       </c>
       <c r="F254" s="5" t="n"/>
@@ -11115,7 +11127,7 @@
       <c r="H254" s="5" t="n"/>
       <c r="I254" s="5" t="inlineStr">
         <is>
-          <t>f8e7615c7c6d95ecf1737d845ee3eb713e297b5f</t>
+          <t>023292350ef95533d99264dab96ffbd271b24b45</t>
         </is>
       </c>
     </row>
@@ -11125,7 +11137,7 @@
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>Enhancing reliability in LLM-integrated robotic systems: A unified approach to security and safety</t>
+          <t>LUMINA: Long-horizon Understanding for Multi-turn Interactive Agents</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
@@ -11140,7 +11152,7 @@
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F255" s="5" t="n"/>
@@ -11148,7 +11160,7 @@
       <c r="H255" s="5" t="n"/>
       <c r="I255" s="5" t="inlineStr">
         <is>
-          <t>f8e7615c7c6d95ecf1737d845ee3eb713e297b5f</t>
+          <t>023292350ef95533d99264dab96ffbd271b24b45</t>
         </is>
       </c>
     </row>
@@ -11158,7 +11170,7 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>Enhancing reliability in LLM-integrated robotic systems: A unified approach to security and safety</t>
+          <t>LUMINA: Long-horizon Understanding for Multi-turn Interactive Agents</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
@@ -11181,7 +11193,7 @@
       <c r="H256" s="5" t="n"/>
       <c r="I256" s="5" t="inlineStr">
         <is>
-          <t>f8e7615c7c6d95ecf1737d845ee3eb713e297b5f</t>
+          <t>023292350ef95533d99264dab96ffbd271b24b45</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11203,7 @@
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>Enhancing reliability in LLM-integrated robotic systems: A unified approach to security and safety</t>
+          <t>LUMINA: Long-horizon Understanding for Multi-turn Interactive Agents</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
@@ -11206,7 +11218,7 @@
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>execution</t>
+          <t>none</t>
         </is>
       </c>
       <c r="F257" s="5" t="n"/>
@@ -11214,7 +11226,7 @@
       <c r="H257" s="5" t="n"/>
       <c r="I257" s="5" t="inlineStr">
         <is>
-          <t>f8e7615c7c6d95ecf1737d845ee3eb713e297b5f</t>
+          <t>023292350ef95533d99264dab96ffbd271b24b45</t>
         </is>
       </c>
     </row>
@@ -11224,7 +11236,7 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>Enhancing reliability in LLM-integrated robotic systems: A unified approach to security and safety</t>
+          <t>LUMINA: Long-horizon Understanding for Multi-turn Interactive Agents</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
@@ -11239,7 +11251,7 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>one-shot</t>
+          <t>session-persistent</t>
         </is>
       </c>
       <c r="F258" s="5" t="n"/>
@@ -11247,7 +11259,7 @@
       <c r="H258" s="5" t="n"/>
       <c r="I258" s="5" t="inlineStr">
         <is>
-          <t>f8e7615c7c6d95ecf1737d845ee3eb713e297b5f</t>
+          <t>023292350ef95533d99264dab96ffbd271b24b45</t>
         </is>
       </c>
     </row>
@@ -11257,7 +11269,7 @@
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>Enhancing reliability in LLM-integrated robotic systems: A unified approach to security and safety</t>
+          <t>LUMINA: Long-horizon Understanding for Multi-turn Interactive Agents</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
@@ -11280,7 +11292,7 @@
       <c r="H259" s="5" t="n"/>
       <c r="I259" s="5" t="inlineStr">
         <is>
-          <t>f8e7615c7c6d95ecf1737d845ee3eb713e297b5f</t>
+          <t>023292350ef95533d99264dab96ffbd271b24b45</t>
         </is>
       </c>
     </row>
@@ -11290,7 +11302,7 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>Enhancing reliability in LLM-integrated robotic systems: A unified approach to security and safety</t>
+          <t>LUMINA: Long-horizon Understanding for Multi-turn Interactive Agents</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
@@ -11305,7 +11317,7 @@
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>Y - open-sourced framework with simulation and physical deployment demos at llmeyesim.vercel.app</t>
+          <t>No code/artifact release found. The paper does not state a GitHub, HuggingFace, or other public repository release for the three procedurally-generated environments (ListWorld, TreeWorld, GridWorld) or the oracle-intervention framework anywhere in the visible text.</t>
         </is>
       </c>
       <c r="F260" s="5" t="n"/>
@@ -11313,7 +11325,7 @@
       <c r="H260" s="5" t="n"/>
       <c r="I260" s="5" t="inlineStr">
         <is>
-          <t>f8e7615c7c6d95ecf1737d845ee3eb713e297b5f</t>
+          <t>023292350ef95533d99264dab96ffbd271b24b45</t>
         </is>
       </c>
     </row>
@@ -11323,7 +11335,7 @@
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>Enhancing reliability in LLM-integrated robotic systems: A unified approach to security and safety</t>
+          <t>LUMINA: Long-horizon Understanding for Multi-turn Interactive Agents</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
@@ -11338,7 +11350,7 @@
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>GPT-4o (primary controller); GPT-4o-mini tried and abandoned for inadequate multimodal reasoning</t>
+          <t>Primary analysis uses the Qwen3 model family across four sizes (4B, 8B, 14B, 32B), run in non-thinking mode with chain-of-thought prompting (thinking mode was tried but found to degrade performance due to token limits) at sampling temperature 0.7, with YaRN encoding applied for long-context (&gt;32K) rollouts. Cross-model generalization checks add Gemma3 (4B-it, 12B-it, 27B-it) and GPT-4o on the ListWorld environment.</t>
         </is>
       </c>
       <c r="F261" s="5" t="n"/>
@@ -11346,7 +11358,7 @@
       <c r="H261" s="5" t="n"/>
       <c r="I261" s="5" t="inlineStr">
         <is>
-          <t>f8e7615c7c6d95ecf1737d845ee3eb713e297b5f</t>
+          <t>023292350ef95533d99264dab96ffbd271b24b45</t>
         </is>
       </c>
     </row>
@@ -11356,7 +11368,7 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>Enhancing reliability in LLM-integrated robotic systems: A unified approach to security and safety</t>
+          <t>LUMINA: Long-horizon Understanding for Multi-turn Interactive Agents</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
@@ -11371,7 +11383,7 @@
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>None public - custom testbed in the EyeSim VR / EyeBot Unity 3D simulator: a red-target navigation task across four environments (Obstacle-Free, Static, Dynamic, Mixed Obstacles), randomized object placement, 100s trial cap, retry threshold 3, attack rates 0.3/0.5/0.7/1.0. Plus a physical S4 robot with RGB camera and 360-degree LiDAR. Self-defined metrics MOER, TLR, ADR.</t>
+          <t>Three procedurally-generated, complexity-tunable game-like multi-turn environments introduced by the paper: ListWorld (mutate a Python list using only pop actions), TreeWorld (iteratively find a target node in a tree using only get_children actions), and GridWorld (spatially navigate a 2D grid to a target location while avoiding holes). Evaluation metrics are success rate (task completion within a horizon budget) and step accuracy (whether each individual action aligns with at least one optimal policy from the current state).</t>
         </is>
       </c>
       <c r="F262" s="5" t="n"/>
@@ -11379,7 +11391,7 @@
       <c r="H262" s="5" t="n"/>
       <c r="I262" s="5" t="inlineStr">
         <is>
-          <t>f8e7615c7c6d95ecf1737d845ee3eb713e297b5f</t>
+          <t>023292350ef95533d99264dab96ffbd271b24b45</t>
         </is>
       </c>
     </row>
@@ -11389,7 +11401,7 @@
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>Enhancing reliability in LLM-integrated robotic systems: A unified approach to security and safety</t>
+          <t>LUMINA: Long-horizon Understanding for Multi-turn Interactive Agents</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
@@ -11404,7 +11416,7 @@
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>The layered defense gives an aggregate 30.8% improvement over the no-defense system on combined security and performance metrics, and up to 325% in the environment-complexity scenario. The honest headline is how weak both conditions are: under Goal Hijacking Injection the undefended system collapses to 0.0 precision, 0.0 recall and 0.0 F1, and even with the full defense recall only reaches 0.3224 and F1 roughly 0.47, while OMI recall rises from 0.2452 to 0.3008. Subtle goal-hijacking is far harder to catch than overt malicious commands.</t>
+          <t>Across all three environments, Qwen3 models show strong performance on short-horizon tasks but success rate drops drastically as horizon length increases, even though step accuracy (correctness of individual actions) remains comparatively high -- e.g., step accuracy often exceeds 60% even when success rate is near zero, showing that compounding per-step errors, not single-step incompetence, drive long-horizon failure, and environments like ListWorld are 'irrecoverable' where a single wrong step causes total task failure. Using the oracle-intervention framework (planning P, state tracking S, history pruning H, and their six combinations), the authors find that planning intervention improves success broadly and consistently across model sizes and environments, largely independent of model size, while the usefulness of state tracking and history pruning is environment- and scale-dependent: history pruning benefits smaller Qwen3 models (4B/8B) substantially (e.g., raising ListWorld success from a base of 12% to 29-35% via S+H) but can hurt larger models (14B/32B suffer performance drops from the same intervention), and larger models benefit more from state tracking than smaller ones. Cross-environment comparison shows the oracles' relative impact is highly rules-dependent: history pruning is most impactful in ListWorld (attending to relevant information is the bottleneck), planning is most useful in GridWorld (navigational tasks benefit from knowing the target and path), and state tracking is most impactful in TreeWorld (which requires complex backtracking) while having little effect in GridWorld. Cross-model validation on ListWorld confirms the scale-dependent pattern: Gemma3 models across all sizes and smaller Qwen3 models benefit from history pruning, but the much larger GPT-4o shows performance degradation from the same intervention (68% base to 62% under full S+P+H vs. 83% under S+P alone), reinforcing that history pruning benefits smaller/weaker models but can hurt stronger ones.</t>
         </is>
       </c>
       <c r="F263" s="5" t="n"/>
@@ -11412,7 +11424,7 @@
       <c r="H263" s="5" t="n"/>
       <c r="I263" s="5" t="inlineStr">
         <is>
-          <t>f8e7615c7c6d95ecf1737d845ee3eb713e297b5f</t>
+          <t>023292350ef95533d99264dab96ffbd271b24b45</t>
         </is>
       </c>
     </row>
@@ -11422,7 +11434,7 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>Enhancing reliability in LLM-integrated robotic systems: A unified approach to security and safety</t>
+          <t>LUMINA: Long-horizon Understanding for Multi-turn Interactive Agents</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
@@ -11437,7 +11449,7 @@
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>A no-defense ablation of the authors' own system - a zero-shot GPT-4o robot controller with structured prompts but without the security prompt prefix, state tracking, or rule-based command validation. No comparison against any external defense (RoboGuard and reachability-based verification are discussed in related work only).</t>
+          <t>The paper does not compare against external prior systems/baselines; instead its comparative structure is internal (a full 2x2x2 factorial oracle-intervention design): a 'base' condition with no oracle assistance is contrasted against six configurations combining planning (P), state tracking (S), and history pruning (H) oracles (P; S+P; S+P+H; base; S; S+H), since history pruning requires state tracking to be active (it removes prior steps from context, which is only interpretable if the state itself is separately tracked).</t>
         </is>
       </c>
       <c r="F264" s="5" t="n"/>
@@ -11445,7 +11457,7 @@
       <c r="H264" s="5" t="n"/>
       <c r="I264" s="5" t="inlineStr">
         <is>
-          <t>f8e7615c7c6d95ecf1737d845ee3eb713e297b5f</t>
+          <t>023292350ef95533d99264dab96ffbd271b24b45</t>
         </is>
       </c>
     </row>
@@ -11455,7 +11467,7 @@
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>Enhancing reliability in LLM-integrated robotic systems: A unified approach to security and safety</t>
+          <t>LUMINA: Long-horizon Understanding for Multi-turn Interactive Agents</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
@@ -11470,7 +11482,7 @@
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>An attacker who can spoof the human instruction interface of a mobile robot - the text channel carrying operator commands derived from multiple modalities - by replacing a fraction of user instructions (0.3 to 1.0) with adversarial content. The threat model also names physical sensor manipulation and compromised communication channels, but the implemented attacks assume an otherwise honest-but-curious sensor pipeline; attacks manipulating raw sensory streams or lower-level control firmware are explicitly out of scope.</t>
+          <t>N/A - non-adversarial (this is a capability-diagnosis/interpretability paper isolating which underlying skills bottleneck long-horizon multi-turn agent performance, not a security paper). The incidental failure mode of interest is directly relevant to context management: long, uncurated interaction history accumulates distractors that can impede an agent's ability to attend to relevant information (motivating the 'history pruning' oracle, which rewrites context to remove distractors and provide a compact summary), and the paper's central finding that this pruning helps smaller/weaker models but can actively hurt larger/stronger models is a notable nuance for context-engineering strategies more broadly -- i.e., context compression is not uniformly beneficial and its value is scale- and task-dependent.</t>
         </is>
       </c>
       <c r="F265" s="5" t="n"/>
@@ -11478,7 +11490,7 @@
       <c r="H265" s="5" t="n"/>
       <c r="I265" s="5" t="inlineStr">
         <is>
-          <t>f8e7615c7c6d95ecf1737d845ee3eb713e297b5f</t>
+          <t>023292350ef95533d99264dab96ffbd271b24b45</t>
         </is>
       </c>
     </row>
@@ -11488,7 +11500,7 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>Enhancing reliability in LLM-integrated robotic systems: A unified approach to security and safety</t>
+          <t>LUMINA: Long-horizon Understanding for Multi-turn Interactive Agents</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
@@ -11503,7 +11515,7 @@
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>Authors state the evaluation centers on a single model (GPT-4o) with one fixed prompting strategy, that their handcrafted secure prompts are likely not optimal, and that the defense 'did not fully neutralise all threat types'. They also note the attack corpus covers only two injection classes, that the layered defense may introduce false positives and defensive conservatism, and that GPT-4o in zero-shot embodied settings struggles with numerical estimation and multimodal fusion regardless of attack.</t>
+          <t>Explicit 'Limitations' section: the paper explicitly frames itself as 'the first step towards explaining the performance degradation of capable LLMs in multi-turn long-horizon agent tasks,' stating that 'while we find valuable insights, many important steps remain to fully understand the performance degradation' (the section is truncated in the extracted text at this point, but this framing establishes the work as a foundational/exploratory study rather than a complete explanation).</t>
         </is>
       </c>
       <c r="F266" s="5" t="n"/>
@@ -11511,7 +11523,7 @@
       <c r="H266" s="5" t="n"/>
       <c r="I266" s="5" t="inlineStr">
         <is>
-          <t>f8e7615c7c6d95ecf1737d845ee3eb713e297b5f</t>
+          <t>023292350ef95533d99264dab96ffbd271b24b45</t>
         </is>
       </c>
     </row>
@@ -11521,7 +11533,7 @@
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>Enhancing reliability in LLM-integrated robotic systems: A unified approach to security and safety</t>
+          <t>LUMINA: Long-horizon Understanding for Multi-turn Interactive Agents</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
@@ -11536,7 +11548,7 @@
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>Proposes a layered reliability framework for LLM-controlled mobile robots that treats prompt-injection security and physical safety as one problem. Combines three components: structured Prompt Assembling with a security directive telling the model that human instructions may come from attackers, State Management that tracks validated commands and prior failures across steps, and a rule-based Safety Validation stage that checks each proposed Move command against LiDAR clearances over an angular window and forces regeneration if it would violate the safety distance. Defines two evaluation attack classes - Obvious Malicious Injection (overtly harmful commands) and Goal Hijacking Injection (plausible-sounding directives that contradict the mission) - and sweeps attack rates across four simulated environments plus a physical robot. Reports aggregate improvements of 30.8% and 325% over an ablated no-defense baseline, while acknowledging absolute detection performance under GHI remains poor.</t>
+          <t>This paper investigates why LLMs that excel at complex single-turn reasoning tasks underperform on multi-turn, long-horizon agentic tasks, by introducing an oracle counterfactual intervention framework that isolates the causal contribution of three specific underlying skills to agent success: planning (providing a description of the correct single-turn subtask on the optimal trajectory), state tracking (providing an accurate, ground-truth state description at each turn), and history pruning (rewriting the context to remove distractors and prior steps, providing a compact summary instead of the full interaction history -- a manipulation that structurally depends on state tracking being active, since pruning removes information that only the state-tracking oracle would otherwise preserve). Because real-world multi-turn benchmarks admit many equally optimal paths to a goal (making exhaustive oracle annotation intractable), the authors introduce three procedurally-generated, complexity-tunable game-like environments (ListWorld, TreeWorld, GridWorld) in which the set of optimal actions at any given state can be computed exactly, enabling precise, confound-free oracle interventions and a factorial design over all six meaningful combinations of the three interventions. Using ReAct-style prompting to interleave reasoning traces with actions, the authors evaluate Qwen3 models (4B-32B) as the primary analysis, with Gemma3 and GPT-4o used to validate generalization on ListWorld. The central findings are that planning assistance improves performance broadly and fairly uniformly across model scales and environments, while the value of state tracking and especially history pruning is highly contingent on both model scale (history pruning helps smaller/weaker models but can degrade larger/stronger models' performance) and environment structure (which skill is most impactful varies by the task's inherent challenge -- attention to relevant information in ListWorld, backtracking-heavy state tracking in TreeWorld, spatial planning in GridWorld). The paper additionally shows that step-level accuracy remains relatively high even as overall task success collapses with horizon length, indicating that long-horizon failure is driven primarily by the compounding of occasional per-step errors over many turns rather than by any single catastrophic reasoning failure, with some environments (e.g., ListWorld) being fully irrecoverable from a single misstep.</t>
         </is>
       </c>
       <c r="F267" s="5" t="n"/>
@@ -11544,7 +11556,7 @@
       <c r="H267" s="5" t="n"/>
       <c r="I267" s="5" t="inlineStr">
         <is>
-          <t>f8e7615c7c6d95ecf1737d845ee3eb713e297b5f</t>
+          <t>023292350ef95533d99264dab96ffbd271b24b45</t>
         </is>
       </c>
     </row>
@@ -11554,7 +11566,7 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>SkillVetBench: LLM-as-Judge for Multi-Dimensional Security Risk Evaluation in Open-Source LLM Agent Skills</t>
+          <t>Beware of Agentic Botnets: Scalable Untargeted Promptware Attacks via Universal and Transferable Adversarial HalluSquatting</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
@@ -11577,7 +11589,7 @@
       <c r="H268" s="5" t="n"/>
       <c r="I268" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2606.15899</t>
+          <t>3120e577687f1ea6217cc0b546739aaa0295acbe</t>
         </is>
       </c>
     </row>
@@ -11587,7 +11599,7 @@
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>SkillVetBench: LLM-as-Judge for Multi-Dimensional Security Risk Evaluation in Open-Source LLM Agent Skills</t>
+          <t>Beware of Agentic Botnets: Scalable Untargeted Promptware Attacks via Universal and Transferable Adversarial HalluSquatting</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
@@ -11610,7 +11622,7 @@
       <c r="H269" s="5" t="n"/>
       <c r="I269" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2606.15899</t>
+          <t>3120e577687f1ea6217cc0b546739aaa0295acbe</t>
         </is>
       </c>
     </row>
@@ -11620,7 +11632,7 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>SkillVetBench: LLM-as-Judge for Multi-Dimensional Security Risk Evaluation in Open-Source LLM Agent Skills</t>
+          <t>Beware of Agentic Botnets: Scalable Untargeted Promptware Attacks via Universal and Transferable Adversarial HalluSquatting</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
@@ -11643,7 +11655,7 @@
       <c r="H270" s="5" t="n"/>
       <c r="I270" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2606.15899</t>
+          <t>3120e577687f1ea6217cc0b546739aaa0295acbe</t>
         </is>
       </c>
     </row>
@@ -11653,7 +11665,7 @@
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>SkillVetBench: LLM-as-Judge for Multi-Dimensional Security Risk Evaluation in Open-Source LLM Agent Skills</t>
+          <t>Beware of Agentic Botnets: Scalable Untargeted Promptware Attacks via Universal and Transferable Adversarial HalluSquatting</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
@@ -11668,7 +11680,7 @@
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>defense</t>
+          <t>attack</t>
         </is>
       </c>
       <c r="F271" s="5" t="n"/>
@@ -11676,7 +11688,7 @@
       <c r="H271" s="5" t="n"/>
       <c r="I271" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2606.15899</t>
+          <t>3120e577687f1ea6217cc0b546739aaa0295acbe</t>
         </is>
       </c>
     </row>
@@ -11686,7 +11698,7 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>SkillVetBench: LLM-as-Judge for Multi-Dimensional Security Risk Evaluation in Open-Source LLM Agent Skills</t>
+          <t>Beware of Agentic Botnets: Scalable Untargeted Promptware Attacks via Universal and Transferable Adversarial HalluSquatting</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
@@ -11701,7 +11713,7 @@
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>skill</t>
+          <t>supply-chain</t>
         </is>
       </c>
       <c r="F272" s="5" t="n"/>
@@ -11709,7 +11721,7 @@
       <c r="H272" s="5" t="n"/>
       <c r="I272" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2606.15899</t>
+          <t>3120e577687f1ea6217cc0b546739aaa0295acbe</t>
         </is>
       </c>
     </row>
@@ -11719,7 +11731,7 @@
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>SkillVetBench: LLM-as-Judge for Multi-Dimensional Security Risk Evaluation in Open-Source LLM Agent Skills</t>
+          <t>Beware of Agentic Botnets: Scalable Untargeted Promptware Attacks via Universal and Transferable Adversarial HalluSquatting</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
@@ -11742,7 +11754,7 @@
       <c r="H273" s="5" t="n"/>
       <c r="I273" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2606.15899</t>
+          <t>3120e577687f1ea6217cc0b546739aaa0295acbe</t>
         </is>
       </c>
     </row>
@@ -11752,7 +11764,7 @@
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>SkillVetBench: LLM-as-Judge for Multi-Dimensional Security Risk Evaluation in Open-Source LLM Agent Skills</t>
+          <t>Beware of Agentic Botnets: Scalable Untargeted Promptware Attacks via Universal and Transferable Adversarial HalluSquatting</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
@@ -11767,7 +11779,7 @@
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F274" s="5" t="n"/>
@@ -11775,7 +11787,7 @@
       <c r="H274" s="5" t="n"/>
       <c r="I274" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2606.15899</t>
+          <t>3120e577687f1ea6217cc0b546739aaa0295acbe</t>
         </is>
       </c>
     </row>
@@ -11785,7 +11797,7 @@
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>SkillVetBench: LLM-as-Judge for Multi-Dimensional Security Risk Evaluation in Open-Source LLM Agent Skills</t>
+          <t>Beware of Agentic Botnets: Scalable Untargeted Promptware Attacks via Universal and Transferable Adversarial HalluSquatting</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
@@ -11808,7 +11820,7 @@
       <c r="H275" s="5" t="n"/>
       <c r="I275" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2606.15899</t>
+          <t>3120e577687f1ea6217cc0b546739aaa0295acbe</t>
         </is>
       </c>
     </row>
@@ -11818,7 +11830,7 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>SkillVetBench: LLM-as-Judge for Multi-Dimensional Security Risk Evaluation in Open-Source LLM Agent Skills</t>
+          <t>Beware of Agentic Botnets: Scalable Untargeted Promptware Attacks via Universal and Transferable Adversarial HalluSquatting</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
@@ -11841,7 +11853,7 @@
       <c r="H276" s="5" t="n"/>
       <c r="I276" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2606.15899</t>
+          <t>3120e577687f1ea6217cc0b546739aaa0295acbe</t>
         </is>
       </c>
     </row>
@@ -11851,7 +11863,7 @@
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>SkillVetBench: LLM-as-Judge for Multi-Dimensional Security Risk Evaluation in Open-Source LLM Agent Skills</t>
+          <t>Beware of Agentic Botnets: Scalable Untargeted Promptware Attacks via Universal and Transferable Adversarial HalluSquatting</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
@@ -11866,7 +11878,7 @@
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>one-shot</t>
+          <t>self-propagating</t>
         </is>
       </c>
       <c r="F277" s="5" t="n"/>
@@ -11874,7 +11886,7 @@
       <c r="H277" s="5" t="n"/>
       <c r="I277" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2606.15899</t>
+          <t>3120e577687f1ea6217cc0b546739aaa0295acbe</t>
         </is>
       </c>
     </row>
@@ -11884,7 +11896,7 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>SkillVetBench: LLM-as-Judge for Multi-Dimensional Security Risk Evaluation in Open-Source LLM Agent Skills</t>
+          <t>Beware of Agentic Botnets: Scalable Untargeted Promptware Attacks via Universal and Transferable Adversarial HalluSquatting</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
@@ -11907,7 +11919,7 @@
       <c r="H278" s="5" t="n"/>
       <c r="I278" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2606.15899</t>
+          <t>3120e577687f1ea6217cc0b546739aaa0295acbe</t>
         </is>
       </c>
     </row>
@@ -11917,7 +11929,7 @@
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>SkillVetBench: LLM-as-Judge for Multi-Dimensional Security Risk Evaluation in Open-Source LLM Agent Skills</t>
+          <t>Beware of Agentic Botnets: Scalable Untargeted Promptware Attacks via Universal and Transferable Adversarial HalluSquatting</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
@@ -11932,7 +11944,7 @@
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>Live, publicly accessible, continuously updated Hugging Face Space leaderboard/evaluation service at https://huggingface.co/spaces/supreme-lab/AgentSkillBench, providing an LLM-as-Judge evaluation service over a 1,200+ skill corpus with CSV export, per-finding SKV-numbered records, and recorded evaluator metadata. This paper is the public-facing companion to a separate benchmark-framework paper (arXiv:2606.00925) that supplies the labeled 100-skill corpus and detection results grounding the scoring methodology.</t>
+          <t>No exploit code/payload artifacts are released -- explicitly withheld: the authors state the promptware-carrying skill used in end-to-end experiments 'will not be released and will not be included in the artifacts' since it is a highly effective attack tool. For the public-facing squatting demonstrations, only benign replicated payloads (duplicating the original resource's functionality) were registered on GitHub/ClawHub, and these were removed at the end of the study. Findings were disclosed to Google, Cline, Cursor, and GitHub, with responses quoted in the paper.</t>
         </is>
       </c>
       <c r="F279" s="5" t="n"/>
@@ -11940,7 +11952,7 @@
       <c r="H279" s="5" t="n"/>
       <c r="I279" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2606.15899</t>
+          <t>3120e577687f1ea6217cc0b546739aaa0295acbe</t>
         </is>
       </c>
     </row>
@@ -11950,7 +11962,7 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>SkillVetBench: LLM-as-Judge for Multi-Dimensional Security Risk Evaluation in Open-Source LLM Agent Skills</t>
+          <t>Beware of Agentic Botnets: Scalable Untargeted Promptware Attacks via Universal and Transferable Adversarial HalluSquatting</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
@@ -11965,7 +11977,7 @@
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>Default live-leaderboard evaluation judge: Qwen2.5-14B-Instruct (carries the bulk of leaderboard evaluations, 979 of 1,299). Other leaderboard evaluator models: Qwen2.5-32B and Llama-3.1-70B (120 and 101 evaluations respectively per Table 10). Benchmark/companion-paper judges tested for evaluator sensitivity on the labeled set: Qwen2.5-32B, Llama-3.1-7B, Llama-3.2-3B-Instruct, and Mixtral-8x7B. Non-LLM/static baseline detectors compared: VirusTotal, ClawScan, ClawVet, CodeBERT, SkillProbe, and SkillSieve.</t>
+          <t>Multiple foundational LLMs and their agentic-application integrations tested via API (n=100 runs each) and through six production coding assistants: Cursor, Cursor CLI, Windsurf, GitHub Copilot (Copilot Chat), Cline, and Gemini CLI. Models referenced include claude-4.5-sonnet and GPT-5.2 (per Gemini/Claude naming pattern in Table 15), plus assistant families OpenClaw, ZeroClaw, and NanoClaw for the skill-squatting experiments.</t>
         </is>
       </c>
       <c r="F280" s="5" t="n"/>
@@ -11973,7 +11985,7 @@
       <c r="H280" s="5" t="n"/>
       <c r="I280" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2606.15899</t>
+          <t>3120e577687f1ea6217cc0b546739aaa0295acbe</t>
         </is>
       </c>
     </row>
@@ -11983,7 +11995,7 @@
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>SkillVetBench: LLM-as-Judge for Multi-Dimensional Security Risk Evaluation in Open-Source LLM Agent Skills</t>
+          <t>Beware of Agentic Botnets: Scalable Untargeted Promptware Attacks via Universal and Transferable Adversarial HalluSquatting</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
@@ -11998,7 +12010,7 @@
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>Two distinct evaluation populations, explicitly not to be conflated: (1) a controlled, labeled 100-skill set from the companion benchmark paper (78 confirmed-malicious skills + 22 benign controls) used for ground-truth detection-performance comparison against baselines (Tables 3-6); (2) the live leaderboard corpus of 1,299 skills sourced from the ClawHub/OpenClaw marketplace, used for descriptive statistics on real-world skill risk distribution (Section 7, Tables 7-10). Vulnerabilities are classified under a seven-category taxonomy (Table 2) including Prompt Injection, Memory Poisoning, Credential/Secret Exposure, Unsafe File Operations, and others.</t>
+          <t>No standard external benchmark; the authors construct their own experimental probes: repeated prompting (n=100 per model/prompt condition, up to 1,300 runs for a single target case) with varied phrasings across four categories (imperative, indirect, question-form, and additional variants, detailed in Table 15/Appendix), targeting real platforms GitHub (for repository-clone hallucination/squatting) and ClawHub (the official plugin marketplace for the OpenClaw family, for skill-installation hallucination/squatting), including probing the top-10 most-installed ClawHub skills.</t>
         </is>
       </c>
       <c r="F281" s="5" t="n"/>
@@ -12006,7 +12018,7 @@
       <c r="H281" s="5" t="n"/>
       <c r="I281" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2606.15899</t>
+          <t>3120e577687f1ea6217cc0b546739aaa0295acbe</t>
         </is>
       </c>
     </row>
@@ -12016,7 +12028,7 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>SkillVetBench: LLM-as-Judge for Multi-Dimensional Security Risk Evaluation in Open-Source LLM Agent Skills</t>
+          <t>Beware of Agentic Botnets: Scalable Untargeted Promptware Attacks via Universal and Transferable Adversarial HalluSquatting</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
@@ -12031,7 +12043,7 @@
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>On the labeled 100-skill set (Table 3), SkillVetBench's LLM-as-Judge is the only system achieving zero false negatives across all 78 malicious skills and zero false positives across all 22 benign controls (recall=1.00, precision=0.96, miss rate=0%), versus the strongest static baseline SkillSieve at 15% miss rate, SkillProbe at 19%, CodeBERT at 30%, few-shot LLM at 22%, and traditional scanners VirusTotal (67% miss), ClawScan (52% miss), and ClawVet (59% miss). Wilson 95% confidence intervals on the small sample give a recall lower bound of ~0.95 and specificity lower bound of ~0.85, so the paper explicitly cautions the 'zero-miss' point estimate should not be over-read as certified perfection. The detection gap is sharpest on instruction-layer threats with no code-level signature: for Prompt Injection (19 skills), VirusTotal flags 0 and ClawScan flags only 3, while the LLM-as-Judge flags all 19; for Memory Poisoning (9 skills), ClawScan detects 1, VirusTotal detects 3, and CodeBERT detects 0, while the LLM-as-Judge classifies all 9 as Suspicious or Malicious -- a 89-100% miss rate for conventional tools on instruction-layer categories. Evaluator sensitivity analysis (Table 5) shows detection rate on the labeled set ranges from 35% (Mixtral-8x7B, near-uniform abstention, systematic false-negative bias) to 95% (Qwen2.5-32B, high recall and calibrated), with Llama-3.2-3B-Instruct showing sparse but over-sensitive firing (mean 6.50+/-7.80 vulnerabilities per skill when it does flag), motivating a recommendation to use evaluators of at least 7B-parameter scale with strong instruction-following alignment and ensemble scoring across multiple judges. On the live 1,299-skill leaderboard corpus (Section 7), 509 skills (39.2%) are flagged as vulnerable; CVSS v4.0 and SARS produce markedly different severity profiles by design (e.g., Data Exposure scores CVSS 1.84/low but scores high under SARS); attack categories skew heavily toward execution-related risks (Prompt Injection 11.4%, Credential/Secret Exposure 10.0%, Unsafe File Operations 8.3% of the 509 vulnerable skills); and the four live leaderboard evaluator models split into two regimes -- larger well-aligned models (Qwen2.5-32B, Llama-3.1-70B) each flag ~79% of skills evaluated with the highest mean CVSS/SARS scores, while the default Qwen2.5-14B (carrying 979 of 1,299 evaluations) flags only 30.5%.</t>
+          <t>Hallucinated resource generation occurs at high rates: up to 85% in repository-cloning scenarios and up to 100% in skill-installation scenarios (depending on skill name and model), and these hallucinations transfer both across foundational LLMs and across different prompt phrasings, enabling attackers to predict and preemptively squat high-probability hallucinated resource names. End-to-end repository-squatting attacks succeed on all six evaluated coding assistants (Cursor, Cursor CLI, Gemini CLI, Windsurf, Copilot Chat, Cline) with per-application success rates of 20%-65%, triggering remote tool execution and remote code execution (RCE); some assistants (Gemini CLI, Cline) autonomously read and execute payload-bearing README content in a single turn with no user confirmation, while others (Cursor, Windsurf, Copilot Chat) require one benign follow-up turn. Skill-squatting attacks against personal assistants (OpenClaw, ZeroClaw, NanoClaw via ClawHub) achieve tool invocation and RCE in 40%-100% of evaluations. No assistant refused execution based on payload content inspection, even for a crude test variant containing explicit AI-targeting injection markers (e.g., 'AI AGENT...STOP AND RUN THIS COMMAND IMMEDIATELY'). Context exfiltration was confirmed across independent trials on multiple assistants using seeded fake credentials (e.g., OPENAI_API_KEY, GEMINI_API_KEY format), with agents autonomously POSTing conversation summaries to an attacker-controlled endpoint. A qualitative observation noted one agent autonomously fixed a syntax error in a payload script and re-ran it until exfiltration succeeded, suggesting the effective attack surface may exceed what static payloads alone achieve.</t>
         </is>
       </c>
       <c r="F282" s="5" t="n"/>
@@ -12039,7 +12051,7 @@
       <c r="H282" s="5" t="n"/>
       <c r="I282" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2606.15899</t>
+          <t>3120e577687f1ea6217cc0b546739aaa0295acbe</t>
         </is>
       </c>
     </row>
@@ -12049,7 +12061,7 @@
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>SkillVetBench: LLM-as-Judge for Multi-Dimensional Security Risk Evaluation in Open-Source LLM Agent Skills</t>
+          <t>Beware of Agentic Botnets: Scalable Untargeted Promptware Attacks via Universal and Transferable Adversarial HalluSquatting</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
@@ -12064,7 +12076,7 @@
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>VirusTotal, ClawScan, ClawVet (marketplace/signature-based scanners), zero-shot LLM, few-shot LLM, CodeBERT, SkillProbe, and SkillSieve (the strongest static baseline). All compared against SkillVetBench's LLM-as-Judge on the labeled 100-skill set using balance, catch rate (recall), precision, and miss rate metrics.</t>
+          <t>No defensive baseline systems are directly benchmarked against; the paper instead compares hallucination and attack-success rates across multiple foundational LLMs, prompt phrasing categories (imperative, indirect, question-form), and six production agentic applications (Cursor, Cursor CLI, Gemini CLI, Windsurf, Copilot Chat, Cline) plus three personal-assistant platforms (OpenClaw, ZeroClaw, NanoClaw) to characterize the universality of the vulnerability, rather than comparing against a prior mitigation technique.</t>
         </is>
       </c>
       <c r="F283" s="5" t="n"/>
@@ -12072,7 +12084,7 @@
       <c r="H283" s="5" t="n"/>
       <c r="I283" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2606.15899</t>
+          <t>3120e577687f1ea6217cc0b546739aaa0295acbe</t>
         </is>
       </c>
     </row>
@@ -12082,7 +12094,7 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>SkillVetBench: LLM-as-Judge for Multi-Dimensional Security Risk Evaluation in Open-Source LLM Agent Skills</t>
+          <t>Beware of Agentic Botnets: Scalable Untargeted Promptware Attacks via Universal and Transferable Adversarial HalluSquatting</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
@@ -12097,7 +12109,7 @@
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>Formal, explicit adversarial/supply-chain threat model. Open marketplaces such as ClawHub and OpenClaw host tens of thousands of community-contributed 'skills' (modular tool definitions that extend an LLM agent's executable action space at runtime); a malicious contributor can embed harmful behavior inside a skill that appears benign to users, agents, and marketplace scanners alike. Unlike conventional software vulnerabilities, the danger is often encoded not in inspectable executable code but in the instruction layer -- natural-language directives that steer the agent to execute unauthorized shell commands, exfiltrate data through encoded side channels, poison persistent memory, or amplify harm by chaining across multi-agent pipelines -- a risk the paper states is 'no longer hypothetical,' citing recent supply-chain campaigns that introduced malicious skills into live marketplaces despite official submission-vetting tools, weaponizing credential theft and data exfiltration that surface only at execution time. Existing defenses are structurally mismatched: signature-based scanners and static analyzers operate at the code layer and are blind to instruction-layer attacks carrying no code-level signature, human review does not scale to thousands of skills, and no static method (including SkillVetBench itself) can confirm at review time whether risky primitives are actually triggered, with what arguments, or to what runtime effect, since the system reads but never executes skills.</t>
+          <t>Formally defined threat model (Section 2, illustrated in Figure 1) for a novel untargeted attack the authors name 'Adversarial HalluSquatting.' The adversary is weak but realistic, requiring only: (i) the ability to identify popular/trending resources (e.g., via daily/weekly/monthly trending-repository and trending-skill listings) and (ii) the ability to register a new resource on a public platform (e.g., a new GitHub repository or ClawHub skill) -- no direct injection channel into any specific victim application is required. The attack proceeds through six steps: (0) the attacker computes the LLM's hallucination distribution over resource names for popular prompts and preemptively registers the most probable hallucinated identifiers, embedding adversarial content; (1-2) a victim issues a routine agentic request (e.g., 'clone repository r' / 'install skill s'); (3) the underlying foundational LLM hallucinates an incorrect resource identifier matching the attacker's squatted name; (4-5) the agentic framework fetches and retrieves the squatted (attacker-controlled) resource instead of the legitimate one; (6) 'context poisoning' occurs as the adversarial content enters the application's context and triggers tool invocation, executing attacker-controlled instructions. Victim applications are agentic systems with integrated terminals/shells that retrieve external resources from platforms lacking robust prompt-injection detection for user-generated content (GitHub, ClawHub, Hugging Face, Docker Hub, Google Maps, Amazon, eBay, and the broader web are named as potentially susceptible platform types). Possible malicious outcomes explicitly named include backdoor installation, ransomware, wipers, data exfiltration, and cryptomining/botnet aggregation for DDoS or distributed compute abuse (drawing an explicit analogy to historical botnets like Mirai and Smominru).</t>
         </is>
       </c>
       <c r="F284" s="5" t="n"/>
@@ -12105,7 +12117,7 @@
       <c r="H284" s="5" t="n"/>
       <c r="I284" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2606.15899</t>
+          <t>3120e577687f1ea6217cc0b546739aaa0295acbe</t>
         </is>
       </c>
     </row>
@@ -12115,7 +12127,7 @@
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>SkillVetBench: LLM-as-Judge for Multi-Dimensional Security Risk Evaluation in Open-Source LLM Agent Skills</t>
+          <t>Beware of Agentic Botnets: Scalable Untargeted Promptware Attacks via Universal and Transferable Adversarial HalluSquatting</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
@@ -12130,7 +12142,7 @@
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>Extensive, explicit dedicated 'Limitations' section (Section 9), covering five named categories: (1) Judge dependence, drift, and nondeterminism -- verdicts inherit the underlying LLM judge's biases (detection rate varies 35-95% across judges), low-temperature sampling reduces but does not eliminate run-to-run nondeterminism, and a model upgrade can shift the entire leaderboard; mitigated by recording the evaluator per row and recommending ensemble scoring, but single-model rows should be read with this caveat. (2) Prompt sensitivity and calibration -- results depend on the fixed prompt template, rubric wording and segment ordering can affect scoring, and the judge's stated confidence is not yet validated against empirical accuracy via a reliability diagram (post-hoc calibration is future work). (3) Static-only analysis and adversarial evasion -- because the system reads but never executes skills, it is explicitly vulnerable to instruction/string obfuscation (encoding, splitting, homoglyphs), multilingual or low-resource-language instructions weakening detection, indirect prompting where malicious directives are fetched at runtime rather than written in SKILL.md, wrapper code that dynamically assembles payloads, benign-looking shells activating harmful behavior only under specific runtime inputs, and prompt injection targeting the judge itself; hardening the judge and complementing static review with sandboxed dynamic analysis is named important future work. (4) Sensitivity vs. false alarms -- an inherent tradeoff exists between catching subtle instruction-layer threats and over-flagging legitimate capability-rich automation skills; the small 22-skill benign control set limits how tightly the false-positive rate can currently be bounded. (5) Marketplace coverage and labels -- ClawHub/OpenClaw metadata and official reviews are external inputs that may change or become unavailable, and 'confirmed-malicious' ground-truth labels come from the companion benchmark paper's own labeling process, both bounding the generality of the conclusions.</t>
+          <t>Explicit 'Limitations' section (Section 7), focused primarily on ethically-motivated experimental design constraints rather than generalization caveats: for public-facing platform experiments, the authors registered only benign replicated payloads (duplicating original resource functionality) on GitHub and ClawHub rather than deploying actual malicious payloads, which they acknowledge did not exercise GitHub's/ClawHub's malware-detection mechanisms (which might otherwise identify and remove malicious content); end-to-end attack effectiveness (with an actual RCE-enabling adversarial payload) was instead measured only locally on the research team's own test machine, never exposed to any third party, and the attack tool itself is being withheld from publication. Separately, a 'Discussion' section (Section 8) explicitly frames the reported attack-success rates as a likely lower bound on real-world exposure, since the study covers only two application categories (LLM assistants, LLM coding assistants) and two platforms (GitHub, ClawHub), while the authors expect the vulnerability to extend to many additional LLM-based applications integrating terminal/shell capabilities, with risk described as 'even more pronounced' for native computer-use agents operating with elevated system privileges.</t>
         </is>
       </c>
       <c r="F285" s="5" t="n"/>
@@ -12138,7 +12150,7 @@
       <c r="H285" s="5" t="n"/>
       <c r="I285" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2606.15899</t>
+          <t>3120e577687f1ea6217cc0b546739aaa0295acbe</t>
         </is>
       </c>
     </row>
@@ -12148,7 +12160,7 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>SkillVetBench: LLM-as-Judge for Multi-Dimensional Security Risk Evaluation in Open-Source LLM Agent Skills</t>
+          <t>Beware of Agentic Botnets: Scalable Untargeted Promptware Attacks via Universal and Transferable Adversarial HalluSquatting</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
@@ -12163,7 +12175,7 @@
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>This paper presents SkillVetBench, a live, public Hugging Face-hosted leaderboard and evaluation service for vetting the security of community-contributed 'skills' -- modular natural-language tool definitions that extend LLM agents' executable action space at runtime, distributed through open marketplaces like ClawHub and OpenClaw. The paper's central argument is that conventional code-layer security scanners (signature matchers, static analyzers, code-similarity detectors like CodeBERT) are structurally blind to instruction-layer and multi-agent risk, since a skill's malicious intent is often encoded in natural-language directives (hijacking the agent, exfiltrating data through encoded side channels, poisoning persistent memory, or chaining harm across multi-agent pipelines) rather than in inspectable executable code with a detectable signature. To address this, SkillVetBench runs an LLM-as-Judge over the complete static skill artifact (SKILL.md specification plus bundled scripts, config files, and declared tool/argument interfaces, without ever executing the skill) through a four-stage pipeline: extracting declared intent and capabilities, classifying findings against a seven-category vulnerability taxonomy, scoring along three complementary reported-jointly-not-fused frameworks -- SARS (Skill Agentic Risk Score), a novel five-dimensional weighted metric purpose-built to capture instruction-layer and multi-agent risk that standard CVSS misses; a full CVSS v4.0 vector decomposition for standard interoperability; and a calibrated three-tier verdict (Benign/Suspicious/Malicious) with a confidence score -- and finally a ClawHub 'dual-view' that places the LLM-generated safety review directly beside the official marketplace verdict to surface detection gaps as a first-class signal. Validated on a controlled, labeled 100-skill set (78 confirmed-malicious, 22 benign) from a companion benchmark paper, the LLM-as-Judge achieves zero false negatives and zero false positives, dramatically outperforming both traditional signature-based scanners and code-similarity classifiers particularly on instruction-layer attack categories (Prompt Injection, Memory Poisoning) where conventional tools miss 89-100% of confirmed threats; the system is further deployed and continuously operated over a live corpus of 1,299+ real marketplace skills, with all reported evaluator-choice and severity-distribution findings anchored to a specific dated snapshot.</t>
+          <t>This paper introduces Adversarial HalluSquatting, a novel technique for scaling untargeted promptware (prompt-injection-based malware) attacks against agentic LLM applications by exploiting the predictable and transferable nature of LLM hallucinations rather than requiring any direct injection channel into a specific victim. The attack exploits the observation that when agentic LLM applications resolve ambiguous or underspecified user requests (e.g., 'clone librepods,' 'install skill s') into concrete external resource identifiers (a GitHub repository slug, a ClawHub skill name), the underlying LLM's next-token-prediction process can hallucinate plausible but incorrect/nonexistent identifiers at high and measurable rates, and these hallucinations are both consistent within a model across prompt phrasings and transferable across different foundational LLMs. Attackers can therefore systematically probe target LLMs or applications with representative prompts to approximate the probability distribution over hallucinated resource names, identify high-probability 'squatting candidates' (selected jointly for prompt popularity and hallucination likelihood), and preemptively register these candidate names on public platforms (GitHub, ClawHub, and by extension Hugging Face, Docker Hub, and other user-content platforms) with embedded adversarial instructions -- analogous to classic typosquatting but targeting the model's hallucination distribution rather than human typing errors. Because agentic applications with integrated terminals/shells (AI coding assistants like Cursor, Windsurf, Copilot, Cline; CLIs like Gemini CLI; and personal assistants like OpenClaw/ZeroClaw/NanoClaw) autonomously fetch and act on whatever resource the LLM names, and because these squatted resources are selected precisely for high retrieval probability, a single registration act can compromise many independent client applications at scale -- enabling the assembly of what the authors term an 'agentic botnet' capable of backdoors, ransomware, data exfiltration, or distributed cryptomining/DDoS, all without ever compromising a legitimate server or requiring targeted delivery to individual victims. The paper's proposed mitigations span both the LLM-application side (mandating an explicit search-tool invocation before any fetch operation, inspecting execution plans for direct-fetch patterns, few-shot planner examples demonstrating correct search-then-retrieve patterns) and the platform side (enforcing global resource-name uniqueness, prohibiting name reuse across owners, defensive preemptive registration of likely hallucinated names analogous to anti-typosquatting registration, and content-level prompt-injection detection for user-generated resource content).</t>
         </is>
       </c>
       <c r="F286" s="5" t="n"/>
@@ -12171,7 +12183,7 @@
       <c r="H286" s="5" t="n"/>
       <c r="I286" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2606.15899</t>
+          <t>3120e577687f1ea6217cc0b546739aaa0295acbe</t>
         </is>
       </c>
     </row>
@@ -12181,7 +12193,7 @@
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>Cross-Agent Multimodal Provenance-Aware Framework for Robust Prompt Injection Defense in Large Language and Vision-Language Models</t>
+          <t>ToLeaP: Rethinking Development of Tool Learning with Large Language Models</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
@@ -12204,7 +12216,7 @@
       <c r="H287" s="5" t="n"/>
       <c r="I287" s="5" t="inlineStr">
         <is>
-          <t>5fd47f3c351347de692aa41262acd331635f5879</t>
+          <t>a861c142222dd4f427a841f0b30252eb5ac71d5c</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12226,7 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>Cross-Agent Multimodal Provenance-Aware Framework for Robust Prompt Injection Defense in Large Language and Vision-Language Models</t>
+          <t>ToLeaP: Rethinking Development of Tool Learning with Large Language Models</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
@@ -12229,7 +12241,7 @@
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>ML/AI</t>
         </is>
       </c>
       <c r="F288" s="5" t="n"/>
@@ -12237,7 +12249,7 @@
       <c r="H288" s="5" t="n"/>
       <c r="I288" s="5" t="inlineStr">
         <is>
-          <t>5fd47f3c351347de692aa41262acd331635f5879</t>
+          <t>a861c142222dd4f427a841f0b30252eb5ac71d5c</t>
         </is>
       </c>
     </row>
@@ -12247,7 +12259,7 @@
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>Cross-Agent Multimodal Provenance-Aware Framework for Robust Prompt Injection Defense in Large Language and Vision-Language Models</t>
+          <t>ToLeaP: Rethinking Development of Tool Learning with Large Language Models</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
@@ -12270,7 +12282,7 @@
       <c r="H289" s="5" t="n"/>
       <c r="I289" s="5" t="inlineStr">
         <is>
-          <t>5fd47f3c351347de692aa41262acd331635f5879</t>
+          <t>a861c142222dd4f427a841f0b30252eb5ac71d5c</t>
         </is>
       </c>
     </row>
@@ -12280,7 +12292,7 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>Cross-Agent Multimodal Provenance-Aware Framework for Robust Prompt Injection Defense in Large Language and Vision-Language Models</t>
+          <t>ToLeaP: Rethinking Development of Tool Learning with Large Language Models</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
@@ -12295,7 +12307,7 @@
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>defense</t>
+          <t>neither</t>
         </is>
       </c>
       <c r="F290" s="5" t="n"/>
@@ -12303,7 +12315,7 @@
       <c r="H290" s="5" t="n"/>
       <c r="I290" s="5" t="inlineStr">
         <is>
-          <t>5fd47f3c351347de692aa41262acd331635f5879</t>
+          <t>a861c142222dd4f427a841f0b30252eb5ac71d5c</t>
         </is>
       </c>
     </row>
@@ -12313,7 +12325,7 @@
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>Cross-Agent Multimodal Provenance-Aware Framework for Robust Prompt Injection Defense in Large Language and Vision-Language Models</t>
+          <t>ToLeaP: Rethinking Development of Tool Learning with Large Language Models</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
@@ -12328,7 +12340,7 @@
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>cross-modal</t>
+          <t>tool-metadata</t>
         </is>
       </c>
       <c r="F291" s="5" t="n"/>
@@ -12336,7 +12348,7 @@
       <c r="H291" s="5" t="n"/>
       <c r="I291" s="5" t="inlineStr">
         <is>
-          <t>5fd47f3c351347de692aa41262acd331635f5879</t>
+          <t>a861c142222dd4f427a841f0b30252eb5ac71d5c</t>
         </is>
       </c>
     </row>
@@ -12346,7 +12358,7 @@
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>Cross-Agent Multimodal Provenance-Aware Framework for Robust Prompt Injection Defense in Large Language and Vision-Language Models</t>
+          <t>ToLeaP: Rethinking Development of Tool Learning with Large Language Models</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
@@ -12361,7 +12373,7 @@
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>goal-hijack</t>
+          <t>reasoning-corruption</t>
         </is>
       </c>
       <c r="F292" s="5" t="n"/>
@@ -12369,7 +12381,7 @@
       <c r="H292" s="5" t="n"/>
       <c r="I292" s="5" t="inlineStr">
         <is>
-          <t>5fd47f3c351347de692aa41262acd331635f5879</t>
+          <t>a861c142222dd4f427a841f0b30252eb5ac71d5c</t>
         </is>
       </c>
     </row>
@@ -12379,7 +12391,7 @@
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>Cross-Agent Multimodal Provenance-Aware Framework for Robust Prompt Injection Defense in Large Language and Vision-Language Models</t>
+          <t>ToLeaP: Rethinking Development of Tool Learning with Large Language Models</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
@@ -12394,7 +12406,7 @@
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F293" s="5" t="n"/>
@@ -12402,7 +12414,7 @@
       <c r="H293" s="5" t="n"/>
       <c r="I293" s="5" t="inlineStr">
         <is>
-          <t>5fd47f3c351347de692aa41262acd331635f5879</t>
+          <t>a861c142222dd4f427a841f0b30252eb5ac71d5c</t>
         </is>
       </c>
     </row>
@@ -12412,7 +12424,7 @@
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>Cross-Agent Multimodal Provenance-Aware Framework for Robust Prompt Injection Defense in Large Language and Vision-Language Models</t>
+          <t>ToLeaP: Rethinking Development of Tool Learning with Large Language Models</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
@@ -12435,7 +12447,7 @@
       <c r="H294" s="5" t="n"/>
       <c r="I294" s="5" t="inlineStr">
         <is>
-          <t>5fd47f3c351347de692aa41262acd331635f5879</t>
+          <t>a861c142222dd4f427a841f0b30252eb5ac71d5c</t>
         </is>
       </c>
     </row>
@@ -12445,7 +12457,7 @@
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>Cross-Agent Multimodal Provenance-Aware Framework for Robust Prompt Injection Defense in Large Language and Vision-Language Models</t>
+          <t>ToLeaP: Rethinking Development of Tool Learning with Large Language Models</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
@@ -12460,7 +12472,7 @@
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>ingestion</t>
+          <t>none</t>
         </is>
       </c>
       <c r="F295" s="5" t="n"/>
@@ -12468,7 +12480,7 @@
       <c r="H295" s="5" t="n"/>
       <c r="I295" s="5" t="inlineStr">
         <is>
-          <t>5fd47f3c351347de692aa41262acd331635f5879</t>
+          <t>a861c142222dd4f427a841f0b30252eb5ac71d5c</t>
         </is>
       </c>
     </row>
@@ -12478,7 +12490,7 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>Cross-Agent Multimodal Provenance-Aware Framework for Robust Prompt Injection Defense in Large Language and Vision-Language Models</t>
+          <t>ToLeaP: Rethinking Development of Tool Learning with Large Language Models</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
@@ -12501,7 +12513,7 @@
       <c r="H296" s="5" t="n"/>
       <c r="I296" s="5" t="inlineStr">
         <is>
-          <t>5fd47f3c351347de692aa41262acd331635f5879</t>
+          <t>a861c142222dd4f427a841f0b30252eb5ac71d5c</t>
         </is>
       </c>
     </row>
@@ -12511,7 +12523,7 @@
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>Cross-Agent Multimodal Provenance-Aware Framework for Robust Prompt Injection Defense in Large Language and Vision-Language Models</t>
+          <t>ToLeaP: Rethinking Development of Tool Learning with Large Language Models</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
@@ -12534,7 +12546,7 @@
       <c r="H297" s="5" t="n"/>
       <c r="I297" s="5" t="inlineStr">
         <is>
-          <t>5fd47f3c351347de692aa41262acd331635f5879</t>
+          <t>a861c142222dd4f427a841f0b30252eb5ac71d5c</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12556,7 @@
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>Cross-Agent Multimodal Provenance-Aware Framework for Robust Prompt Injection Defense in Large Language and Vision-Language Models</t>
+          <t>ToLeaP: Rethinking Development of Tool Learning with Large Language Models</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
@@ -12557,13 +12569,17 @@
           <t>secondary</t>
         </is>
       </c>
-      <c r="E298" s="2" t="n"/>
+      <c r="E298" s="2" t="inlineStr">
+        <is>
+          <t>Explicitly released: 'We make our code publicly available at https://github.com/thunlp/ToLeaP.' The release includes the ToLeaP one-click evaluation platform (7 out of 33 benchmarks integrated for one-click evaluation, 6 already merged plus 2 more added per reviewer suggestions) and 21 out of 33 collected training datasets unified into ShareGPT format compatible with LLaMA-Factory.</t>
+        </is>
+      </c>
       <c r="F298" s="5" t="n"/>
       <c r="G298" s="5" t="n"/>
       <c r="H298" s="5" t="n"/>
       <c r="I298" s="5" t="inlineStr">
         <is>
-          <t>5fd47f3c351347de692aa41262acd331635f5879</t>
+          <t>a861c142222dd4f427a841f0b30252eb5ac71d5c</t>
         </is>
       </c>
     </row>
@@ -12573,7 +12589,7 @@
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>Cross-Agent Multimodal Provenance-Aware Framework for Robust Prompt Injection Defense in Large Language and Vision-Language Models</t>
+          <t>ToLeaP: Rethinking Development of Tool Learning with Large Language Models</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
@@ -12588,7 +12604,7 @@
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>Not named in the extracted material; the framework targets Large Language Models and Vision-Language Models operating within LangChain- and GraphChain-style agentic orchestration.</t>
+          <t>The paper distinguishes two evaluation scopes: a broad bad-case analysis across 41 prevalent LLMs (used to identify the four core challenges), and a focused 15-LLM evaluation on the ToLeaP platform itself (Appendix F), comprising proprietary models GPT-3.5-turbo, GPT-4o, and Claude-3.5-Sonnet, and open-source models Llama3.1-8B-Instruct, Qwen2.5-7B-Instruct, Mistral-8B-Instruct-2410, ToolACE-8B, Marco-O1, Skywork-O1-Open-Llama-3.1-8B, Llama2-7B-Chat, Llama2-7B, ToolLlama2-7B-v2, Llama2-13B, Llama2-13B-Chat, and QwQ-32B. Additional targeted experiments use LLaMA-3.1-8B-Instruct-based ToolLLaMA (reproduced by updating its base from LLaMA-2 to LLaMA-3.1) and GPT-4o-1120 for bad-case category breakdowns.</t>
         </is>
       </c>
       <c r="F299" s="5" t="n"/>
@@ -12596,7 +12612,7 @@
       <c r="H299" s="5" t="n"/>
       <c r="I299" s="5" t="inlineStr">
         <is>
-          <t>5fd47f3c351347de692aa41262acd331635f5879</t>
+          <t>a861c142222dd4f427a841f0b30252eb5ac71d5c</t>
         </is>
       </c>
     </row>
@@ -12606,7 +12622,7 @@
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>Cross-Agent Multimodal Provenance-Aware Framework for Robust Prompt Injection Defense in Large Language and Vision-Language Models</t>
+          <t>ToLeaP: Rethinking Development of Tool Learning with Large Language Models</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
@@ -12621,7 +12637,7 @@
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>No external benchmark surfaced. Evaluation is on multimodal prompt-injection scenarios across an agent graph, reporting cross-agent trust leakage, multimodal PI detection accuracy, and execution-pathway stability.</t>
+          <t>Surveys 33 tool-learning benchmarks total, categorized into three reproducibility tiers: Tier 1 (8 benchmarks fully integrated into the one-click ToLeaP platform, e.g., RoTBench, SealTools), Tier 2 (reproducible with original code but not one-click compatible, e.g., ToolBench, due to outdated RapidAPI dependencies and slow HuggingFace inference), and Tier 3 (not reproducible due to missing code/data/ground-truth, e.g., APIBench, RestBench, MetaTool). Also collects and unifies 21 of 33 candidate training datasets (via LLaMA-Factory-compatible ShareGPT format) including sources such as ToolACE. Benchmarks evaluate five capability dimensions: tool selection/use, parameter identification/filling, task structure/output accuracy, task execution/completeness, and robustness, spanning 64 total evaluation metrics.</t>
         </is>
       </c>
       <c r="F300" s="5" t="n"/>
@@ -12629,7 +12645,7 @@
       <c r="H300" s="5" t="n"/>
       <c r="I300" s="5" t="inlineStr">
         <is>
-          <t>5fd47f3c351347de692aa41262acd331635f5879</t>
+          <t>a861c142222dd4f427a841f0b30252eb5ac71d5c</t>
         </is>
       </c>
     </row>
@@ -12639,7 +12655,7 @@
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>Cross-Agent Multimodal Provenance-Aware Framework for Robust Prompt Injection Defense in Large Language and Vision-Language Models</t>
+          <t>ToLeaP: Rethinking Development of Tool Learning with Large Language Models</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
@@ -12654,7 +12670,7 @@
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>The reported headline is a reduction in cross-agent trust leakage from 0.24 to 0.07, a 70% reduction, attributed jointly to trust-aware attention masking, provenance-metadata propagation through orchestration nodes, and output validation against end-to-end influence records - the stated effect being that unverified content is prevented from spreading through the agent workflow. Measuring leakage between agents rather than only attack success at a single node is the methodologically useful choice here, since it captures the propagation property the framework is designed to interrupt, and it is a metric this corpus rarely sees despite multi-agent poisoning being a named mechanism in the RQ3 registry. The paper also claims improved multimodal PI detection accuracy and more stable agentic execution pathways, though specific figures for those are not surfaced in the extracted material. Because leakage is reported as a unitless score rather than a rate with a defined denominator, the 0.24-to-0.07 improvement is difficult to compare against other defenses in this corpus.</t>
+          <t>By analyzing over 3,000 bad cases across 41 LLMs on ToLeaP, the authors identify four major challenges impeding tool learning: (1) benchmark construction limitations (at least 10% of bad cases stem from inaccurate benchmark annotations/ground truth rather than true model failure), which in turn obscures (2) lack of autonomous learning -- increasing training data 100x without autonomy modeling yields only a 5% performance improvement, whereas simple autonomy modeling on under 1x the data (an open-sourced subset) achieves a 3% improvement, nearly matching the 100x result; (3) poor generalization -- ToolLLaMA-3.1-8B, despite mastering over 16,000 tools during training, still exhibits an error rate exceeding 25% on new tools from the same source, indicating shortcut learning rather than generalizable tool-use skill; (4) weak long-horizon task-solving -- manual analysis of LLaMA-3.1-8B and GPT-4o bad cases on the BFCL Multi-Turn benchmark finds over 70% of failures stem from missing key clues (for GPT-4o-1120 specifically, 71.1%/19.4%/30.1% break down across Type III/II/I errors). The authors then run preliminary experiments on four corresponding 'opportunities': DPO-based autonomous data selection reaches in 80 training steps performance that standard SFT only reaches after 100,000 steps and converges more smoothly, while adding low-value data late in training consistently degrades performance; rationale-based ('thinking') learning corrects over 50% of initial generalization bad cases; identifying and recalling key clues inverts (fixes) up to 60.9% of GPT-4o's initial long-horizon bad cases; and unified/real-world benchmark construction is shown to reduce evaluation noise, though the authors note further standardization work remains.</t>
         </is>
       </c>
       <c r="F301" s="5" t="n"/>
@@ -12662,7 +12678,7 @@
       <c r="H301" s="5" t="n"/>
       <c r="I301" s="5" t="inlineStr">
         <is>
-          <t>5fd47f3c351347de692aa41262acd331635f5879</t>
+          <t>a861c142222dd4f427a841f0b30252eb5ac71d5c</t>
         </is>
       </c>
     </row>
@@ -12672,7 +12688,7 @@
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>Cross-Agent Multimodal Provenance-Aware Framework for Robust Prompt Injection Defense in Large Language and Vision-Language Models</t>
+          <t>ToLeaP: Rethinking Development of Tool Learning with Large Language Models</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
@@ -12687,7 +12703,7 @@
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>An undefended configuration provides the 0.24 leakage baseline against the framework's 0.07. Comparison is against the system's own unprotected operation rather than against a competing multi-agent defense; no external framework is reimplemented, and the specific ablation contribution of each of the three mechanisms (attention masking, provenance propagation, output validation) is not separated in the extracted material.</t>
+          <t>The paper's own reproduced/original-paper results serve as baselines for validating reproduction fidelity (results colored blue/yellow/red by error margin: &lt;5%, 5-10%, &gt;10% deviation from originally reported numbers, with successful reproduction requiring at least two models fully in the blue tier). For the autonomy-opportunity experiments, standard full-dataset SFT training and models trained only on the publicly available ToolACE data serve as baselines against DPO-based autonomous data selection.</t>
         </is>
       </c>
       <c r="F302" s="5" t="n"/>
@@ -12695,7 +12711,7 @@
       <c r="H302" s="5" t="n"/>
       <c r="I302" s="5" t="inlineStr">
         <is>
-          <t>5fd47f3c351347de692aa41262acd331635f5879</t>
+          <t>a861c142222dd4f427a841f0b30252eb5ac71d5c</t>
         </is>
       </c>
     </row>
@@ -12705,7 +12721,7 @@
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>Cross-Agent Multimodal Provenance-Aware Framework for Robust Prompt Injection Defense in Large Language and Vision-Language Models</t>
+          <t>ToLeaP: Rethinking Development of Tool Learning with Large Language Models</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
@@ -12718,13 +12734,17 @@
           <t>freetext</t>
         </is>
       </c>
-      <c r="E303" s="2" t="n"/>
+      <c r="E303" s="2" t="inlineStr">
+        <is>
+          <t>N/A - non-adversarial. This is a benchmarking/meta-analysis paper (not concerned with adversarial attacks); the incidental failure mode of interest is systemic: LLMs' apparent tool-learning progress is confounded by benchmark artifacts (annotation errors, simulated rather than real environments, fragmented single-capability evaluation) that mask the true underlying deficits in autonomous learning, generalization to new tools, and long-horizon task execution.</t>
+        </is>
+      </c>
       <c r="F303" s="5" t="n"/>
       <c r="G303" s="5" t="n"/>
       <c r="H303" s="5" t="n"/>
       <c r="I303" s="5" t="inlineStr">
         <is>
-          <t>5fd47f3c351347de692aa41262acd331635f5879</t>
+          <t>a861c142222dd4f427a841f0b30252eb5ac71d5c</t>
         </is>
       </c>
     </row>
@@ -12734,7 +12754,7 @@
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>Cross-Agent Multimodal Provenance-Aware Framework for Robust Prompt Injection Defense in Large Language and Vision-Language Models</t>
+          <t>ToLeaP: Rethinking Development of Tool Learning with Large Language Models</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
@@ -12749,7 +12769,7 @@
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>No explicit limitations section surfaced. The principal interpretive caveats are metric definition and scope: cross-agent trust leakage is reported as a bare score (0.24 to 0.07) without a stated denominator or measurement protocol, so the magnitude cannot be translated into attack success terms or compared with other defenses; and detection-accuracy and execution-stability claims are asserted as experimentally supported without figures in the abstract-level material. The framework adds three agents plus a provenance ledger to every workflow, and no latency, cost or throughput overhead is reported - a material omission for a defense that inserts sanitization and validation on every inter-agent hop. No adaptive adversary is evaluated, which matters especially for provenance-based defenses since an attacker aware of trust metadata may target the labelling step itself. Evaluation targets LangChain/GraphChain-style workflows specifically, so generalization to other orchestration patterns is unestablished.</t>
+          <t>The paper does not contain an explicit 'Limitations' section; the closest analogs are scattered self-acknowledged constraints in the main text and Conclusion. In Section 3.1 the authors note they excluded Tier 3 benchmarks (e.g., APIBench, RestBench, MetaTool) entirely because reproduction was 'prohibitively hard' due to missing code, missing ground-truth labels, and unresponsive original authors, and that revising some benchmarks' source code to match updated online environments/tools/network settings was 'prohibitively expensive,' so those benchmarks were excluded from the one-click set. The Conclusion frames the four identified 'opportunities' as only preliminary/initial experiments ('we take an initial step... The preliminary experiments demonstrate their effectiveness, highlighting the need for further research and exploration'), explicitly deferring 'consolidation and expansion of our identified opportunities and their further validation in additional scenarios' to future work, and calling for further standardization of real-world benchmark design as an open problem the paper only partially addresses.</t>
         </is>
       </c>
       <c r="F304" s="5" t="n"/>
@@ -12757,7 +12777,7 @@
       <c r="H304" s="5" t="n"/>
       <c r="I304" s="5" t="inlineStr">
         <is>
-          <t>5fd47f3c351347de692aa41262acd331635f5879</t>
+          <t>a861c142222dd4f427a841f0b30252eb5ac71d5c</t>
         </is>
       </c>
     </row>
@@ -12767,7 +12787,7 @@
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>Cross-Agent Multimodal Provenance-Aware Framework for Robust Prompt Injection Defense in Large Language and Vision-Language Models</t>
+          <t>ToLeaP: Rethinking Development of Tool Learning with Large Language Models</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
@@ -12782,7 +12802,7 @@
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>Proposes a Cross-Agent Multimodal Provenance-Aware Defense Framework for prompt injection in LLM and Vision-Language Model agent graphs, addressing a threat the authors characterize as propagation rather than point compromise: hidden or malicious instructions embedded in text, images, metadata, or inter-agent messages can spread throughout an agent network built with LangChain- or GraphChain-style orchestration, triggering unintended behaviour, policy violation, or state corruption. The design sanitizes user- and agent-generated prompts and independently validates LLM output before delivery to downstream nodes, using three specialized agents - a text sanitizer, a visual sanitizer, and an output validator - synchronized by a provenance ledger that records modality, source and trust metadata across the agent network. The architecture then imposes ordered trust boundaries so an injected instruction cannot propagate through the workflow graph. Three concrete mechanisms implement this: trust-aware attention masking, propagation of provenance metadata through LangChain/GraphChain nodes, and validation of LLM outputs using end-to-end influence records. The multimodal dimension matters because the visual sanitizer addresses injection carried in images - a cross-modal channel underrepresented in this corpus's defense registry - and the provenance ledger's explicit modality field means an instruction's origin modality remains attached as it moves between agents. A multi-agent-channel defense spanning ingestion (sanitizers) and output validation.</t>
+          <t>ToLeaP is a large-scale meta-analysis and unified evaluation platform for tool learning with LLMs, motivated by the observation that the 33 existing tool-learning benchmarks fragment evaluation across four isolated capabilities (task planning, tool selection, tool calling, response generation), producing partial, sometimes misleading pictures of true tool-use competence and obscuring interdependencies between capabilities. The authors first triage all 33 benchmarks into three reproducibility tiers based on code/data availability and compatibility, ultimately integrating a subset into a standardized one-click evaluation framework (the ToLeaP platform) and separately collecting and reformatting 21 training datasets into a unified ShareGPT/LLaMA-Factory-compatible format. Using this platform, they run 15 representative proprietary and open-source LLMs across the integrated benchmarks and manually analyze over 3,000 bad cases spanning a broader pool of 41 LLMs to identify four root-cause challenges limiting tool-learning progress: benchmark construction flaws that mask true model deficits, lack of autonomous data-selection ability during training, poor generalization to unseen tools via shortcut learning, and weak long-horizon task-solving due to failure to identify and recall key contextual clues. For each challenge the paper conducts a corresponding preliminary intervention experiment (DPO-based autonomous data selection, rationale/thinking-based generalization training, key-clue identification/recall mechanisms, and steps toward more realistic benchmark construction), reporting substantial bad-case correction rates as evidence that these directions are promising avenues for future tool-learning research, though the paper positions all four interventions as exploratory rather than fully validated solutions.</t>
         </is>
       </c>
       <c r="F305" s="5" t="n"/>
@@ -12790,7 +12810,7 @@
       <c r="H305" s="5" t="n"/>
       <c r="I305" s="5" t="inlineStr">
         <is>
-          <t>5fd47f3c351347de692aa41262acd331635f5879</t>
+          <t>a861c142222dd4f427a841f0b30252eb5ac71d5c</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -12889,27 +12909,27 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>From Untrusted Input to Trusted Memory: A Systematic Study of Memory Poisoning Attacks in LLM Agents</t>
+          <t>SecInfer: Preventing Prompt Injection via Inference-time Scaling</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>attack / failure mechanism</t>
+          <t>defense / fix</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>UNNAMED: memory-poisoning attack taxonomy (6 classes incl. Conditional Command Insertion, Policy-Conformant Fact Injection, False Precedent Insertion)</t>
+          <t>SecInfer</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>memory</t>
+          <t>direct-input</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>persistence-backdoor</t>
+          <t>goal-hijack</t>
         </is>
       </c>
       <c r="G2" s="5" t="n"/>
@@ -12918,7 +12938,7 @@
       <c r="J2" s="5" t="n"/>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>469d4b8f7660de4bf1651a92bbc1ced997e631ec</t>
+          <t>5b3f710d1923323a0113f6db056aa712a04b0f13</t>
         </is>
       </c>
     </row>
@@ -12928,17 +12948,17 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Repair the Amplifier, Not the Symptom: Stable World-Model Correction for Agent Rollouts</t>
+          <t>Tensor Trust: Interpretable Prompt Injection Attacks from an Online Game</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>defense / fix</t>
+          <t>attack / failure mechanism</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>WM-SAR (World-Model Subgraph Amplification Repair)</t>
+          <t>Tensor Trust: prompt extraction / prompt hijacking</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -12948,7 +12968,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>goal-hijack</t>
         </is>
       </c>
       <c r="G3" s="5" t="n"/>
@@ -12957,7 +12977,7 @@
       <c r="J3" s="5" t="n"/>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>965c0cae557aed318e6305af2749aabb9b6a7051</t>
+          <t>e25b4bdfc3f5a8293ea6cd687a0203e446594188</t>
         </is>
       </c>
     </row>
@@ -12967,27 +12987,27 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Enhancing Retrieval-Augmented Large Vision Language Models via Knowledge Conflict Mitigation</t>
+          <t>Manipulating LLM Web Agents with Indirect Prompt Injection Attack via HTML Accessibility Tree</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>defense / fix</t>
+          <t>attack / failure mechanism</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>KCM (Knowledge Conflict Mitigation)</t>
+          <t>UNNAMED: HTML accessibility-tree universal adversarial trigger injection (TWUI)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>cross-modal</t>
+          <t>tool-output</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>silent-corruption</t>
+          <t>goal-hijack</t>
         </is>
       </c>
       <c r="G4" s="5" t="n"/>
@@ -12996,7 +13016,7 @@
       <c r="J4" s="5" t="n"/>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>452b4750bfc661f1a78a953f56ebdf2d34369a19</t>
+          <t>2b73f8dbb2af737fe707df3b2dcb21a9cea62db5</t>
         </is>
       </c>
     </row>
@@ -13006,7 +13026,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Uncovering Security Threats and Architecting Defenses in Autonomous Agents: A Case Study of OpenClaw</t>
+          <t>Memory as Action: Autonomous Context Curation for Long-Horizon Agentic Tasks</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -13016,17 +13036,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>FASA (zero-trust, full-lifecycle defense philosophy)</t>
+          <t>MemAct (Memory-as-Action) with Dynamic Context Policy Optimization</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>memory</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>goal-hijack</t>
+          <t>reasoning-corruption</t>
         </is>
       </c>
       <c r="G5" s="5" t="n"/>
@@ -13035,7 +13055,7 @@
       <c r="J5" s="5" t="n"/>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>ec338413be097a8f6de120397411e86952c475ca</t>
+          <t>5f0f0c762c094bb6e1deba3222331ee51b98d1fc</t>
         </is>
       </c>
     </row>
@@ -13045,7 +13065,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Agent Skills in the Wild: An Empirical Study of Security Vulnerabilities at Scale</t>
+          <t>PhantomLint: Principled Detection of Hidden LLM Prompts in Structured Documents</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -13055,12 +13075,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>SkillScan</t>
+          <t>PhantomLint</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>skill</t>
+          <t>cross-modal</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -13074,7 +13094,7 @@
       <c r="J6" s="5" t="n"/>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>017083cfa88785e0a5dbddf6b5027caa281bc881</t>
+          <t>5717e2bd544b999c678c6199e844f790459f7327</t>
         </is>
       </c>
     </row>
@@ -13084,22 +13104,22 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Overcoming the Retrieval Barrier: Indirect Prompt Injection in the Wild for LLM Systems</t>
+          <t>Can Indirect Prompt Injection Attacks Be Detected and Removed?</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>attack / failure mechanism</t>
+          <t>defense / fix</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>UNNAMED: retrieval-aware IPI (trigger-fragment decomposition attack)</t>
+          <t>UNNAMED: IPI detection + post-detection removal pipeline</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>RAG</t>
+          <t>tool-output</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -13113,7 +13133,7 @@
       <c r="J7" s="5" t="n"/>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>81eb760ebbe224ae52cd7aea8f7f2865e4134908</t>
+          <t>20723b734e2838c22f921a0fc343d32e1d6d84e7</t>
         </is>
       </c>
     </row>
@@ -13123,22 +13143,22 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Manipulating LLM Web Agents with Indirect Prompt Injection Attack via HTML Accessibility Tree</t>
+          <t>Secure Prompt Engineering Patterns for Cloud LLM Agents</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>attack / failure mechanism</t>
+          <t>defense / fix</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>UNNAMED: HTML accessibility-tree universal adversarial trigger injection (TWUI)</t>
+          <t>Secure Prompt Engineering Patterns (SPEP)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>direct-input</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -13152,7 +13172,7 @@
       <c r="J8" s="5" t="n"/>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>2b73f8dbb2af737fe707df3b2dcb21a9cea62db5</t>
+          <t>08e6079c73649ba405826d9ea5da1c18645fcdb6</t>
         </is>
       </c>
     </row>
@@ -13162,22 +13182,22 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Meta SecAlign: A Secure Foundation LLM Against Prompt Injection Attacks</t>
+          <t>Beware of Agentic Botnets: Scalable Untargeted Promptware Attacks via Universal and Transferable Adversarial HalluSquatting</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>defense / fix</t>
+          <t>attack / failure mechanism</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>SecAlign++ / Meta-SecAlign</t>
+          <t>Adversarial HalluSquatting</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>supply-chain</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -13191,331 +13211,19 @@
       <c r="J9" s="5" t="n"/>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>fc3d1be58cc8fe00f15923493a0b59db2c50004c</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>RAG-Induced Failures in Multi-Agent Large Language Model Debate</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>attack / failure mechanism</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>UNNAMED: RAG-manipulation attack on multi-agent debate consensus</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>RAG</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>reasoning-corruption</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>4f6bc1797993f1ff1ddb1fccb9111bc424fa2242</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>PlanFlip: Attacking Multi-Agent LLM Systems via Planning-Phase Prompt Injection</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>attack / failure mechanism</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>PlanFlip</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>multi-agent</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>goal-hijack</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>36dd2ed29b677eff1f4689a18040d3fae5c4278a</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>PlanFlip: Attacking Multi-Agent LLM Systems via Planning-Phase Prompt Injection</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>defense / fix</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>GoalAnchorCheck (D1) / CrossAgentConsensus (D2)</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>multi-agent</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>goal-hijack</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>36dd2ed29b677eff1f4689a18040d3fae5c4278a</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>SecureClaw: Clawing Back Control of LLM Agents</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>defense / fix</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>SecureClaw (dual-boundary: effect-sink authorization + read-boundary plaintext confinement)</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>tool-output</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>goal-hijack</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>cb002afee0f72bd9c25d00c192660df2290ae6ad</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>The Instruction Hierarchy: Training LLMs to Prioritize Privileged Instructions</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>defense / fix</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Instruction Hierarchy (privileged-instruction training)</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>direct-input</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>goal-hijack</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>f18e5a844c37e5342f8f3d409c74c1a9c91d1f8f</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Enhancing reliability in LLM-integrated robotic systems: A unified approach to security and safety</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>defense / fix</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>unified Prompt Assembling + State Management + Safety Validation framework</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>direct-input</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>goal-hijack</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>f8e7615c7c6d95ecf1737d845ee3eb713e297b5f</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>SkillVetBench: LLM-as-Judge for Multi-Dimensional Security Risk Evaluation in Open-Source LLM Agent Skills</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>defense / fix</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>SkillVetBench (LLM-as-Judge)</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>skill</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>goal-hijack</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="5" t="n"/>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>arxiv:2606.15899</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Cross-Agent Multimodal Provenance-Aware Framework for Robust Prompt Injection Defense in Large Language and Vision-Language Models</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>defense / fix</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>UNNAMED: Cross-Agent Multimodal Provenance-Aware Defense Framework (text/visual sanitizer agents + output validator + provenance ledger)</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>cross-modal</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>goal-hijack</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>5fd47f3c351347de692aa41262acd331635f5879</t>
+          <t>3120e577687f1ea6217cc0b546739aaa0295acbe</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation sqref="G2:G17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"yes,no,unclear"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"yes,no,unclear"</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"yes,no,unclear"</formula1>
     </dataValidation>
   </dataValidations>
